--- a/activity/M01A10/M01A10_Sinuosidad.xlsx
+++ b/activity/M01A10/M01A10_Sinuosidad.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.HCMC\activity\M01A10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B7F6C26-4DEF-4F2A-9C94-71C33B39A361}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BC1097A-C07D-40A2-8500-63C0B534CF33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{CB4A84EB-58A9-4828-A1EC-5E14AACD60D5}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{CB4A84EB-58A9-4828-A1EC-5E14AACD60D5}"/>
   </bookViews>
   <sheets>
     <sheet name="Calificacion" sheetId="12" r:id="rId1"/>
@@ -243,12 +243,6 @@
     </font>
     <font>
       <sz val="8"/>
-      <color theme="10"/>
-      <name val="Segoe UI Light"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -261,6 +255,12 @@
     </font>
     <font>
       <sz val="10"/>
+      <color rgb="FF0070C0"/>
+      <name val="Segoe UI Light"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <color rgb="FF0070C0"/>
       <name val="Segoe UI Light"/>
       <family val="2"/>
@@ -280,7 +280,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="19">
+  <borders count="18">
     <border>
       <left/>
       <right/>
@@ -452,15 +452,6 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top/>
       <bottom style="thin">
         <color indexed="64"/>
@@ -541,7 +532,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
@@ -624,17 +615,73 @@
     <xf numFmtId="2" fontId="5" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="1" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="165" fontId="10" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="2" fontId="6" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -645,73 +692,14 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="2" fontId="11" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="11" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="165" fontId="11" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="11" fillId="0" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="11" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="11" fillId="0" borderId="18" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -2123,25 +2111,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="F1" s="34" t="s">
+      <c r="F1" s="27" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="2" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B2" s="27" t="s">
+      <c r="B2" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="27"/>
-      <c r="D2" s="27"/>
-      <c r="E2" s="27"/>
-      <c r="F2" s="27"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="43"/>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B3" s="28"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="28"/>
-      <c r="F3" s="28"/>
+      <c r="B3" s="44"/>
+      <c r="C3" s="44"/>
+      <c r="D3" s="44"/>
+      <c r="E3" s="44"/>
+      <c r="F3" s="44"/>
     </row>
     <row r="4" spans="2:6" ht="30.75" x14ac:dyDescent="0.45">
       <c r="B4" s="19" t="s">
@@ -2164,14 +2152,14 @@
       <c r="B5" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="C5" s="38">
+      <c r="C5" s="29">
         <v>5</v>
       </c>
       <c r="D5" s="22">
         <f>Detalle!C30*C5/5</f>
         <v>0</v>
       </c>
-      <c r="E5" s="38"/>
+      <c r="E5" s="29"/>
       <c r="F5" s="25">
         <f>AVERAGE(D5:E5)</f>
         <v>0</v>
@@ -2181,14 +2169,14 @@
       <c r="B6" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="C6" s="38">
+      <c r="C6" s="29">
         <v>5</v>
       </c>
       <c r="D6" s="22">
         <f>Detalle!F30*C6/5</f>
         <v>0</v>
       </c>
-      <c r="E6" s="38"/>
+      <c r="E6" s="29"/>
       <c r="F6" s="25">
         <f t="shared" ref="F6:F18" si="0">AVERAGE(D6:E6)</f>
         <v>0</v>
@@ -2198,14 +2186,14 @@
       <c r="B7" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="38">
+      <c r="C7" s="29">
         <v>5</v>
       </c>
       <c r="D7" s="22">
         <f>Detalle!I30*C7/5</f>
         <v>0</v>
       </c>
-      <c r="E7" s="38"/>
+      <c r="E7" s="29"/>
       <c r="F7" s="25">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2215,14 +2203,14 @@
       <c r="B8" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="38">
+      <c r="C8" s="29">
         <v>5</v>
       </c>
       <c r="D8" s="22">
         <f>Detalle!L30*C8/5</f>
         <v>0</v>
       </c>
-      <c r="E8" s="38"/>
+      <c r="E8" s="29"/>
       <c r="F8" s="25">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2232,14 +2220,14 @@
       <c r="B9" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="38">
+      <c r="C9" s="29">
         <v>5</v>
       </c>
       <c r="D9" s="22">
         <f>Detalle!O30*C9/5</f>
         <v>0</v>
       </c>
-      <c r="E9" s="38"/>
+      <c r="E9" s="29"/>
       <c r="F9" s="25">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2249,14 +2237,14 @@
       <c r="B10" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="C10" s="38">
+      <c r="C10" s="29">
         <v>5</v>
       </c>
       <c r="D10" s="22">
         <f>Detalle!R30*C10/5</f>
         <v>0</v>
       </c>
-      <c r="E10" s="38"/>
+      <c r="E10" s="29"/>
       <c r="F10" s="25">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2266,14 +2254,14 @@
       <c r="B11" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="C11" s="38">
+      <c r="C11" s="29">
         <v>5</v>
       </c>
       <c r="D11" s="22">
         <f>Detalle!U30*C11/5</f>
         <v>0</v>
       </c>
-      <c r="E11" s="38"/>
+      <c r="E11" s="29"/>
       <c r="F11" s="25">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2283,14 +2271,14 @@
       <c r="B12" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="C12" s="38">
+      <c r="C12" s="29">
         <v>5</v>
       </c>
       <c r="D12" s="22">
         <f>Detalle!X30*C12/5</f>
         <v>0</v>
       </c>
-      <c r="E12" s="38"/>
+      <c r="E12" s="29"/>
       <c r="F12" s="25">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2300,14 +2288,14 @@
       <c r="B13" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="C13" s="38">
+      <c r="C13" s="29">
         <v>5</v>
       </c>
       <c r="D13" s="22">
         <f>Detalle!AA30*C13/5</f>
         <v>0</v>
       </c>
-      <c r="E13" s="38"/>
+      <c r="E13" s="29"/>
       <c r="F13" s="25">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2317,14 +2305,14 @@
       <c r="B14" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="C14" s="38">
+      <c r="C14" s="29">
         <v>5</v>
       </c>
       <c r="D14" s="22">
         <f>Detalle!AD30*C14/5</f>
         <v>0</v>
       </c>
-      <c r="E14" s="38"/>
+      <c r="E14" s="29"/>
       <c r="F14" s="25">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2334,14 +2322,14 @@
       <c r="B15" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="C15" s="38">
+      <c r="C15" s="29">
         <v>5</v>
       </c>
       <c r="D15" s="22">
         <f>Detalle!AG30*C15/5</f>
         <v>0</v>
       </c>
-      <c r="E15" s="38"/>
+      <c r="E15" s="29"/>
       <c r="F15" s="25">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2351,14 +2339,14 @@
       <c r="B16" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="C16" s="38">
+      <c r="C16" s="29">
         <v>5</v>
       </c>
       <c r="D16" s="22">
         <f>Detalle!AJ30*C16/5</f>
         <v>0</v>
       </c>
-      <c r="E16" s="38"/>
+      <c r="E16" s="29"/>
       <c r="F16" s="25">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2368,14 +2356,14 @@
       <c r="B17" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="C17" s="38">
+      <c r="C17" s="29">
         <v>5</v>
       </c>
       <c r="D17" s="22">
         <f>Detalle!AM30*C17/5</f>
         <v>0</v>
       </c>
-      <c r="E17" s="38"/>
+      <c r="E17" s="29"/>
       <c r="F17" s="25">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2385,35 +2373,35 @@
       <c r="B18" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C18" s="39">
+      <c r="C18" s="30">
         <v>5</v>
       </c>
       <c r="D18" s="23">
         <f>Detalle!AP30*C18/5</f>
         <v>0</v>
       </c>
-      <c r="E18" s="39"/>
+      <c r="E18" s="30"/>
       <c r="F18" s="26">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B19" s="36" t="str">
-        <f>HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.HCMC/blob/main/activity/",F1,"/Readme.md"),"Actividad en GitHub")</f>
-        <v>Actividad en GitHub</v>
-      </c>
-      <c r="C19" s="36"/>
-      <c r="D19" s="36"/>
-      <c r="E19" s="36"/>
-      <c r="F19" s="36"/>
+    <row r="19" spans="2:6" ht="15.4" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B19" s="52" t="str">
+        <f>HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.HCMC/blob/main/activity/",F1,"/Readme.md"),_xlfn.CONCAT("Ir a actividad ",F1," en GitHub."))</f>
+        <v>Ir a actividad M01A10 en GitHub.</v>
+      </c>
+      <c r="C19" s="52"/>
+      <c r="D19" s="52"/>
+      <c r="E19" s="52"/>
+      <c r="F19" s="52"/>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B20" s="37"/>
-      <c r="C20" s="37"/>
-      <c r="D20" s="37"/>
-      <c r="E20" s="37"/>
-      <c r="F20" s="37"/>
+      <c r="B20" s="52"/>
+      <c r="C20" s="52"/>
+      <c r="D20" s="52"/>
+      <c r="E20" s="52"/>
+      <c r="F20" s="52"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B21" s="24"/>
@@ -2423,13 +2411,15 @@
       <c r="F21" s="24"/>
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B23" s="35"/>
+      <c r="B23" s="28"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="3">
     <mergeCell ref="B2:F3"/>
+    <mergeCell ref="B19:F19"/>
+    <mergeCell ref="B20:F20"/>
   </mergeCells>
-  <phoneticPr fontId="9" type="noConversion"/>
+  <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
@@ -2526,96 +2516,96 @@
     </row>
     <row r="2" spans="1:44" s="3" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A2" s="6"/>
-      <c r="B2" s="29" t="s">
+      <c r="B2" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="31" t="str">
+      <c r="C2" s="47" t="str">
         <f>Calificacion!$B5</f>
         <v>Grupo 1</v>
       </c>
-      <c r="D2" s="32"/>
-      <c r="E2" s="33"/>
-      <c r="F2" s="31" t="str">
+      <c r="D2" s="48"/>
+      <c r="E2" s="49"/>
+      <c r="F2" s="47" t="str">
         <f>Calificacion!$B6</f>
         <v>Grupo 2</v>
       </c>
-      <c r="G2" s="32"/>
-      <c r="H2" s="33"/>
-      <c r="I2" s="31" t="str">
+      <c r="G2" s="48"/>
+      <c r="H2" s="49"/>
+      <c r="I2" s="47" t="str">
         <f>Calificacion!$B7</f>
         <v>Grupo 3</v>
       </c>
-      <c r="J2" s="32"/>
-      <c r="K2" s="33"/>
-      <c r="L2" s="31" t="str">
+      <c r="J2" s="48"/>
+      <c r="K2" s="49"/>
+      <c r="L2" s="47" t="str">
         <f>Calificacion!$B8</f>
         <v>Grupo 4</v>
       </c>
-      <c r="M2" s="32"/>
-      <c r="N2" s="33"/>
-      <c r="O2" s="31" t="str">
+      <c r="M2" s="48"/>
+      <c r="N2" s="49"/>
+      <c r="O2" s="47" t="str">
         <f>Calificacion!$B9</f>
         <v>Grupo 5</v>
       </c>
-      <c r="P2" s="32"/>
-      <c r="Q2" s="33"/>
-      <c r="R2" s="31" t="str">
+      <c r="P2" s="48"/>
+      <c r="Q2" s="49"/>
+      <c r="R2" s="47" t="str">
         <f>Calificacion!$B10</f>
         <v>Grupo 6</v>
       </c>
-      <c r="S2" s="32"/>
-      <c r="T2" s="33"/>
-      <c r="U2" s="31" t="str">
+      <c r="S2" s="48"/>
+      <c r="T2" s="49"/>
+      <c r="U2" s="47" t="str">
         <f>Calificacion!$B11</f>
         <v>Grupo 7</v>
       </c>
-      <c r="V2" s="32"/>
-      <c r="W2" s="33"/>
-      <c r="X2" s="31" t="str">
+      <c r="V2" s="48"/>
+      <c r="W2" s="49"/>
+      <c r="X2" s="47" t="str">
         <f>Calificacion!$B12</f>
         <v>Grupo 8</v>
       </c>
-      <c r="Y2" s="32"/>
-      <c r="Z2" s="33"/>
-      <c r="AA2" s="31" t="str">
+      <c r="Y2" s="48"/>
+      <c r="Z2" s="49"/>
+      <c r="AA2" s="47" t="str">
         <f>Calificacion!$B13</f>
         <v>Grupo 9</v>
       </c>
-      <c r="AB2" s="32"/>
-      <c r="AC2" s="33"/>
-      <c r="AD2" s="31" t="str">
+      <c r="AB2" s="48"/>
+      <c r="AC2" s="49"/>
+      <c r="AD2" s="47" t="str">
         <f>Calificacion!$B14</f>
         <v>Grupo 10</v>
       </c>
-      <c r="AE2" s="32"/>
-      <c r="AF2" s="33"/>
-      <c r="AG2" s="31" t="str">
+      <c r="AE2" s="48"/>
+      <c r="AF2" s="49"/>
+      <c r="AG2" s="47" t="str">
         <f>Calificacion!$B15</f>
         <v>Grupo 11</v>
       </c>
-      <c r="AH2" s="32"/>
-      <c r="AI2" s="33"/>
-      <c r="AJ2" s="31" t="str">
+      <c r="AH2" s="48"/>
+      <c r="AI2" s="49"/>
+      <c r="AJ2" s="47" t="str">
         <f>Calificacion!$B16</f>
         <v>Grupo 12</v>
       </c>
-      <c r="AK2" s="32"/>
-      <c r="AL2" s="33"/>
-      <c r="AM2" s="31" t="str">
+      <c r="AK2" s="48"/>
+      <c r="AL2" s="49"/>
+      <c r="AM2" s="47" t="str">
         <f>Calificacion!$B17</f>
         <v>Grupo 13</v>
       </c>
-      <c r="AN2" s="32"/>
-      <c r="AO2" s="33"/>
-      <c r="AP2" s="31" t="str">
+      <c r="AN2" s="48"/>
+      <c r="AO2" s="49"/>
+      <c r="AP2" s="47" t="str">
         <f>Calificacion!$B18</f>
         <v>Grupo 14</v>
       </c>
-      <c r="AQ2" s="32"/>
-      <c r="AR2" s="33"/>
+      <c r="AQ2" s="48"/>
+      <c r="AR2" s="49"/>
     </row>
     <row r="3" spans="1:44" x14ac:dyDescent="0.45">
-      <c r="B3" s="30"/>
+      <c r="B3" s="51"/>
       <c r="C3" s="7" t="s">
         <v>1</v>
       </c>
@@ -2747,1381 +2737,1381 @@
       <c r="B4" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="C4" s="40">
-        <v>0</v>
-      </c>
-      <c r="D4" s="41"/>
-      <c r="E4" s="42"/>
-      <c r="F4" s="40">
-        <v>0</v>
-      </c>
-      <c r="G4" s="41"/>
-      <c r="H4" s="42"/>
-      <c r="I4" s="40">
-        <v>0</v>
-      </c>
-      <c r="J4" s="41"/>
-      <c r="K4" s="42"/>
-      <c r="L4" s="40">
-        <v>0</v>
-      </c>
-      <c r="M4" s="41"/>
-      <c r="N4" s="42"/>
-      <c r="O4" s="40">
-        <v>0</v>
-      </c>
-      <c r="P4" s="41"/>
-      <c r="Q4" s="42"/>
-      <c r="R4" s="40">
-        <v>0</v>
-      </c>
-      <c r="S4" s="41"/>
-      <c r="T4" s="42"/>
-      <c r="U4" s="40">
-        <v>0</v>
-      </c>
-      <c r="V4" s="41"/>
-      <c r="W4" s="42"/>
-      <c r="X4" s="40">
-        <v>0</v>
-      </c>
-      <c r="Y4" s="41"/>
-      <c r="Z4" s="42"/>
-      <c r="AA4" s="40">
-        <v>0</v>
-      </c>
-      <c r="AB4" s="41"/>
-      <c r="AC4" s="42"/>
-      <c r="AD4" s="40">
-        <v>0</v>
-      </c>
-      <c r="AE4" s="41"/>
-      <c r="AF4" s="42"/>
-      <c r="AG4" s="40">
-        <v>0</v>
-      </c>
-      <c r="AH4" s="41"/>
-      <c r="AI4" s="42"/>
-      <c r="AJ4" s="40">
-        <v>0</v>
-      </c>
-      <c r="AK4" s="41"/>
-      <c r="AL4" s="42"/>
-      <c r="AM4" s="40">
-        <v>0</v>
-      </c>
-      <c r="AN4" s="41"/>
-      <c r="AO4" s="42"/>
-      <c r="AP4" s="40">
-        <v>0</v>
-      </c>
-      <c r="AQ4" s="41"/>
-      <c r="AR4" s="42"/>
+      <c r="C4" s="31">
+        <v>0</v>
+      </c>
+      <c r="D4" s="32"/>
+      <c r="E4" s="33"/>
+      <c r="F4" s="31">
+        <v>0</v>
+      </c>
+      <c r="G4" s="32"/>
+      <c r="H4" s="33"/>
+      <c r="I4" s="31">
+        <v>0</v>
+      </c>
+      <c r="J4" s="32"/>
+      <c r="K4" s="33"/>
+      <c r="L4" s="31">
+        <v>0</v>
+      </c>
+      <c r="M4" s="32"/>
+      <c r="N4" s="33"/>
+      <c r="O4" s="31">
+        <v>0</v>
+      </c>
+      <c r="P4" s="32"/>
+      <c r="Q4" s="33"/>
+      <c r="R4" s="31">
+        <v>0</v>
+      </c>
+      <c r="S4" s="32"/>
+      <c r="T4" s="33"/>
+      <c r="U4" s="31">
+        <v>0</v>
+      </c>
+      <c r="V4" s="32"/>
+      <c r="W4" s="33"/>
+      <c r="X4" s="31">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="32"/>
+      <c r="Z4" s="33"/>
+      <c r="AA4" s="31">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="32"/>
+      <c r="AC4" s="33"/>
+      <c r="AD4" s="31">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="32"/>
+      <c r="AF4" s="33"/>
+      <c r="AG4" s="31">
+        <v>0</v>
+      </c>
+      <c r="AH4" s="32"/>
+      <c r="AI4" s="33"/>
+      <c r="AJ4" s="31">
+        <v>0</v>
+      </c>
+      <c r="AK4" s="32"/>
+      <c r="AL4" s="33"/>
+      <c r="AM4" s="31">
+        <v>0</v>
+      </c>
+      <c r="AN4" s="32"/>
+      <c r="AO4" s="33"/>
+      <c r="AP4" s="31">
+        <v>0</v>
+      </c>
+      <c r="AQ4" s="32"/>
+      <c r="AR4" s="33"/>
     </row>
     <row r="5" spans="1:44" ht="30.75" x14ac:dyDescent="0.45">
       <c r="B5" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="40"/>
-      <c r="D5" s="41"/>
-      <c r="E5" s="42"/>
-      <c r="F5" s="40"/>
-      <c r="G5" s="41"/>
-      <c r="H5" s="42"/>
-      <c r="I5" s="40"/>
-      <c r="J5" s="41"/>
-      <c r="K5" s="42"/>
-      <c r="L5" s="40"/>
-      <c r="M5" s="41"/>
-      <c r="N5" s="42"/>
-      <c r="O5" s="40"/>
-      <c r="P5" s="41"/>
-      <c r="Q5" s="42"/>
-      <c r="R5" s="40"/>
-      <c r="S5" s="41"/>
-      <c r="T5" s="42"/>
-      <c r="U5" s="40"/>
-      <c r="V5" s="41"/>
-      <c r="W5" s="42"/>
-      <c r="X5" s="40"/>
-      <c r="Y5" s="41"/>
-      <c r="Z5" s="42"/>
-      <c r="AA5" s="40"/>
-      <c r="AB5" s="41"/>
-      <c r="AC5" s="42"/>
-      <c r="AD5" s="40"/>
-      <c r="AE5" s="41"/>
-      <c r="AF5" s="42"/>
-      <c r="AG5" s="40"/>
-      <c r="AH5" s="41"/>
-      <c r="AI5" s="42"/>
-      <c r="AJ5" s="40"/>
-      <c r="AK5" s="41"/>
-      <c r="AL5" s="42"/>
-      <c r="AM5" s="40"/>
-      <c r="AN5" s="41"/>
-      <c r="AO5" s="42"/>
-      <c r="AP5" s="40"/>
-      <c r="AQ5" s="41"/>
-      <c r="AR5" s="42"/>
+      <c r="C5" s="31"/>
+      <c r="D5" s="32"/>
+      <c r="E5" s="33"/>
+      <c r="F5" s="31"/>
+      <c r="G5" s="32"/>
+      <c r="H5" s="33"/>
+      <c r="I5" s="31"/>
+      <c r="J5" s="32"/>
+      <c r="K5" s="33"/>
+      <c r="L5" s="31"/>
+      <c r="M5" s="32"/>
+      <c r="N5" s="33"/>
+      <c r="O5" s="31"/>
+      <c r="P5" s="32"/>
+      <c r="Q5" s="33"/>
+      <c r="R5" s="31"/>
+      <c r="S5" s="32"/>
+      <c r="T5" s="33"/>
+      <c r="U5" s="31"/>
+      <c r="V5" s="32"/>
+      <c r="W5" s="33"/>
+      <c r="X5" s="31"/>
+      <c r="Y5" s="32"/>
+      <c r="Z5" s="33"/>
+      <c r="AA5" s="31"/>
+      <c r="AB5" s="32"/>
+      <c r="AC5" s="33"/>
+      <c r="AD5" s="31"/>
+      <c r="AE5" s="32"/>
+      <c r="AF5" s="33"/>
+      <c r="AG5" s="31"/>
+      <c r="AH5" s="32"/>
+      <c r="AI5" s="33"/>
+      <c r="AJ5" s="31"/>
+      <c r="AK5" s="32"/>
+      <c r="AL5" s="33"/>
+      <c r="AM5" s="31"/>
+      <c r="AN5" s="32"/>
+      <c r="AO5" s="33"/>
+      <c r="AP5" s="31"/>
+      <c r="AQ5" s="32"/>
+      <c r="AR5" s="33"/>
     </row>
     <row r="6" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B6" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="40"/>
-      <c r="D6" s="41"/>
-      <c r="E6" s="42"/>
-      <c r="F6" s="40"/>
-      <c r="G6" s="41"/>
-      <c r="H6" s="42"/>
-      <c r="I6" s="40"/>
-      <c r="J6" s="41"/>
-      <c r="K6" s="42"/>
-      <c r="L6" s="40"/>
-      <c r="M6" s="41"/>
-      <c r="N6" s="42"/>
-      <c r="O6" s="40"/>
-      <c r="P6" s="41"/>
-      <c r="Q6" s="42"/>
-      <c r="R6" s="40"/>
-      <c r="S6" s="41"/>
-      <c r="T6" s="42"/>
-      <c r="U6" s="40"/>
-      <c r="V6" s="41"/>
-      <c r="W6" s="42"/>
-      <c r="X6" s="40"/>
-      <c r="Y6" s="41"/>
-      <c r="Z6" s="42"/>
-      <c r="AA6" s="40"/>
-      <c r="AB6" s="41"/>
-      <c r="AC6" s="42"/>
-      <c r="AD6" s="40"/>
-      <c r="AE6" s="41"/>
-      <c r="AF6" s="42"/>
-      <c r="AG6" s="40"/>
-      <c r="AH6" s="41"/>
-      <c r="AI6" s="42"/>
-      <c r="AJ6" s="40"/>
-      <c r="AK6" s="41"/>
-      <c r="AL6" s="42"/>
-      <c r="AM6" s="40"/>
-      <c r="AN6" s="41"/>
-      <c r="AO6" s="42"/>
-      <c r="AP6" s="40"/>
-      <c r="AQ6" s="41"/>
-      <c r="AR6" s="42"/>
+      <c r="C6" s="31"/>
+      <c r="D6" s="32"/>
+      <c r="E6" s="33"/>
+      <c r="F6" s="31"/>
+      <c r="G6" s="32"/>
+      <c r="H6" s="33"/>
+      <c r="I6" s="31"/>
+      <c r="J6" s="32"/>
+      <c r="K6" s="33"/>
+      <c r="L6" s="31"/>
+      <c r="M6" s="32"/>
+      <c r="N6" s="33"/>
+      <c r="O6" s="31"/>
+      <c r="P6" s="32"/>
+      <c r="Q6" s="33"/>
+      <c r="R6" s="31"/>
+      <c r="S6" s="32"/>
+      <c r="T6" s="33"/>
+      <c r="U6" s="31"/>
+      <c r="V6" s="32"/>
+      <c r="W6" s="33"/>
+      <c r="X6" s="31"/>
+      <c r="Y6" s="32"/>
+      <c r="Z6" s="33"/>
+      <c r="AA6" s="31"/>
+      <c r="AB6" s="32"/>
+      <c r="AC6" s="33"/>
+      <c r="AD6" s="31"/>
+      <c r="AE6" s="32"/>
+      <c r="AF6" s="33"/>
+      <c r="AG6" s="31"/>
+      <c r="AH6" s="32"/>
+      <c r="AI6" s="33"/>
+      <c r="AJ6" s="31"/>
+      <c r="AK6" s="32"/>
+      <c r="AL6" s="33"/>
+      <c r="AM6" s="31"/>
+      <c r="AN6" s="32"/>
+      <c r="AO6" s="33"/>
+      <c r="AP6" s="31"/>
+      <c r="AQ6" s="32"/>
+      <c r="AR6" s="33"/>
     </row>
     <row r="7" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B7" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="40"/>
-      <c r="D7" s="43"/>
-      <c r="E7" s="42"/>
-      <c r="F7" s="40"/>
-      <c r="G7" s="43"/>
-      <c r="H7" s="42"/>
-      <c r="I7" s="40"/>
-      <c r="J7" s="43"/>
-      <c r="K7" s="42"/>
-      <c r="L7" s="40"/>
-      <c r="M7" s="43"/>
-      <c r="N7" s="42"/>
-      <c r="O7" s="40"/>
-      <c r="P7" s="43"/>
-      <c r="Q7" s="42"/>
-      <c r="R7" s="40"/>
-      <c r="S7" s="43"/>
-      <c r="T7" s="42"/>
-      <c r="U7" s="40"/>
-      <c r="V7" s="43"/>
-      <c r="W7" s="42"/>
-      <c r="X7" s="40"/>
-      <c r="Y7" s="43"/>
-      <c r="Z7" s="42"/>
-      <c r="AA7" s="40"/>
-      <c r="AB7" s="43"/>
-      <c r="AC7" s="42"/>
-      <c r="AD7" s="40"/>
-      <c r="AE7" s="43"/>
-      <c r="AF7" s="42"/>
-      <c r="AG7" s="40"/>
-      <c r="AH7" s="43"/>
-      <c r="AI7" s="42"/>
-      <c r="AJ7" s="40"/>
-      <c r="AK7" s="43"/>
-      <c r="AL7" s="42"/>
-      <c r="AM7" s="40"/>
-      <c r="AN7" s="43"/>
-      <c r="AO7" s="42"/>
-      <c r="AP7" s="40"/>
-      <c r="AQ7" s="43"/>
-      <c r="AR7" s="42"/>
+      <c r="C7" s="31"/>
+      <c r="D7" s="34"/>
+      <c r="E7" s="33"/>
+      <c r="F7" s="31"/>
+      <c r="G7" s="34"/>
+      <c r="H7" s="33"/>
+      <c r="I7" s="31"/>
+      <c r="J7" s="34"/>
+      <c r="K7" s="33"/>
+      <c r="L7" s="31"/>
+      <c r="M7" s="34"/>
+      <c r="N7" s="33"/>
+      <c r="O7" s="31"/>
+      <c r="P7" s="34"/>
+      <c r="Q7" s="33"/>
+      <c r="R7" s="31"/>
+      <c r="S7" s="34"/>
+      <c r="T7" s="33"/>
+      <c r="U7" s="31"/>
+      <c r="V7" s="34"/>
+      <c r="W7" s="33"/>
+      <c r="X7" s="31"/>
+      <c r="Y7" s="34"/>
+      <c r="Z7" s="33"/>
+      <c r="AA7" s="31"/>
+      <c r="AB7" s="34"/>
+      <c r="AC7" s="33"/>
+      <c r="AD7" s="31"/>
+      <c r="AE7" s="34"/>
+      <c r="AF7" s="33"/>
+      <c r="AG7" s="31"/>
+      <c r="AH7" s="34"/>
+      <c r="AI7" s="33"/>
+      <c r="AJ7" s="31"/>
+      <c r="AK7" s="34"/>
+      <c r="AL7" s="33"/>
+      <c r="AM7" s="31"/>
+      <c r="AN7" s="34"/>
+      <c r="AO7" s="33"/>
+      <c r="AP7" s="31"/>
+      <c r="AQ7" s="34"/>
+      <c r="AR7" s="33"/>
     </row>
     <row r="8" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B8" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="40"/>
-      <c r="D8" s="43"/>
-      <c r="E8" s="42"/>
-      <c r="F8" s="40"/>
-      <c r="G8" s="43"/>
-      <c r="H8" s="42"/>
-      <c r="I8" s="40"/>
-      <c r="J8" s="43"/>
-      <c r="K8" s="42"/>
-      <c r="L8" s="40"/>
-      <c r="M8" s="43"/>
-      <c r="N8" s="42"/>
-      <c r="O8" s="40"/>
-      <c r="P8" s="43"/>
-      <c r="Q8" s="42"/>
-      <c r="R8" s="40"/>
-      <c r="S8" s="43"/>
-      <c r="T8" s="42"/>
-      <c r="U8" s="40"/>
-      <c r="V8" s="43"/>
-      <c r="W8" s="42"/>
-      <c r="X8" s="40"/>
-      <c r="Y8" s="43"/>
-      <c r="Z8" s="42"/>
-      <c r="AA8" s="40"/>
-      <c r="AB8" s="43"/>
-      <c r="AC8" s="42"/>
-      <c r="AD8" s="40"/>
-      <c r="AE8" s="43"/>
-      <c r="AF8" s="42"/>
-      <c r="AG8" s="40"/>
-      <c r="AH8" s="43"/>
-      <c r="AI8" s="42"/>
-      <c r="AJ8" s="40"/>
-      <c r="AK8" s="43"/>
-      <c r="AL8" s="42"/>
-      <c r="AM8" s="40"/>
-      <c r="AN8" s="43"/>
-      <c r="AO8" s="42"/>
-      <c r="AP8" s="40"/>
-      <c r="AQ8" s="43"/>
-      <c r="AR8" s="42"/>
+      <c r="C8" s="31"/>
+      <c r="D8" s="34"/>
+      <c r="E8" s="33"/>
+      <c r="F8" s="31"/>
+      <c r="G8" s="34"/>
+      <c r="H8" s="33"/>
+      <c r="I8" s="31"/>
+      <c r="J8" s="34"/>
+      <c r="K8" s="33"/>
+      <c r="L8" s="31"/>
+      <c r="M8" s="34"/>
+      <c r="N8" s="33"/>
+      <c r="O8" s="31"/>
+      <c r="P8" s="34"/>
+      <c r="Q8" s="33"/>
+      <c r="R8" s="31"/>
+      <c r="S8" s="34"/>
+      <c r="T8" s="33"/>
+      <c r="U8" s="31"/>
+      <c r="V8" s="34"/>
+      <c r="W8" s="33"/>
+      <c r="X8" s="31"/>
+      <c r="Y8" s="34"/>
+      <c r="Z8" s="33"/>
+      <c r="AA8" s="31"/>
+      <c r="AB8" s="34"/>
+      <c r="AC8" s="33"/>
+      <c r="AD8" s="31"/>
+      <c r="AE8" s="34"/>
+      <c r="AF8" s="33"/>
+      <c r="AG8" s="31"/>
+      <c r="AH8" s="34"/>
+      <c r="AI8" s="33"/>
+      <c r="AJ8" s="31"/>
+      <c r="AK8" s="34"/>
+      <c r="AL8" s="33"/>
+      <c r="AM8" s="31"/>
+      <c r="AN8" s="34"/>
+      <c r="AO8" s="33"/>
+      <c r="AP8" s="31"/>
+      <c r="AQ8" s="34"/>
+      <c r="AR8" s="33"/>
     </row>
     <row r="9" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B9" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="40"/>
-      <c r="D9" s="41"/>
-      <c r="E9" s="42"/>
-      <c r="F9" s="40"/>
-      <c r="G9" s="41"/>
-      <c r="H9" s="42"/>
-      <c r="I9" s="40"/>
-      <c r="J9" s="41"/>
-      <c r="K9" s="42"/>
-      <c r="L9" s="40"/>
-      <c r="M9" s="41"/>
-      <c r="N9" s="42"/>
-      <c r="O9" s="40"/>
-      <c r="P9" s="41"/>
-      <c r="Q9" s="42"/>
-      <c r="R9" s="40"/>
-      <c r="S9" s="41"/>
-      <c r="T9" s="42"/>
-      <c r="U9" s="40"/>
-      <c r="V9" s="41"/>
-      <c r="W9" s="42"/>
-      <c r="X9" s="40"/>
-      <c r="Y9" s="41"/>
-      <c r="Z9" s="42"/>
-      <c r="AA9" s="40"/>
-      <c r="AB9" s="41"/>
-      <c r="AC9" s="42"/>
-      <c r="AD9" s="40"/>
-      <c r="AE9" s="41"/>
-      <c r="AF9" s="42"/>
-      <c r="AG9" s="40"/>
-      <c r="AH9" s="41"/>
-      <c r="AI9" s="42"/>
-      <c r="AJ9" s="40"/>
-      <c r="AK9" s="41"/>
-      <c r="AL9" s="42"/>
-      <c r="AM9" s="40"/>
-      <c r="AN9" s="41"/>
-      <c r="AO9" s="42"/>
-      <c r="AP9" s="40"/>
-      <c r="AQ9" s="41"/>
-      <c r="AR9" s="42"/>
+      <c r="C9" s="31"/>
+      <c r="D9" s="32"/>
+      <c r="E9" s="33"/>
+      <c r="F9" s="31"/>
+      <c r="G9" s="32"/>
+      <c r="H9" s="33"/>
+      <c r="I9" s="31"/>
+      <c r="J9" s="32"/>
+      <c r="K9" s="33"/>
+      <c r="L9" s="31"/>
+      <c r="M9" s="32"/>
+      <c r="N9" s="33"/>
+      <c r="O9" s="31"/>
+      <c r="P9" s="32"/>
+      <c r="Q9" s="33"/>
+      <c r="R9" s="31"/>
+      <c r="S9" s="32"/>
+      <c r="T9" s="33"/>
+      <c r="U9" s="31"/>
+      <c r="V9" s="32"/>
+      <c r="W9" s="33"/>
+      <c r="X9" s="31"/>
+      <c r="Y9" s="32"/>
+      <c r="Z9" s="33"/>
+      <c r="AA9" s="31"/>
+      <c r="AB9" s="32"/>
+      <c r="AC9" s="33"/>
+      <c r="AD9" s="31"/>
+      <c r="AE9" s="32"/>
+      <c r="AF9" s="33"/>
+      <c r="AG9" s="31"/>
+      <c r="AH9" s="32"/>
+      <c r="AI9" s="33"/>
+      <c r="AJ9" s="31"/>
+      <c r="AK9" s="32"/>
+      <c r="AL9" s="33"/>
+      <c r="AM9" s="31"/>
+      <c r="AN9" s="32"/>
+      <c r="AO9" s="33"/>
+      <c r="AP9" s="31"/>
+      <c r="AQ9" s="32"/>
+      <c r="AR9" s="33"/>
     </row>
     <row r="10" spans="1:44" ht="30.75" x14ac:dyDescent="0.45">
       <c r="B10" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="40"/>
-      <c r="D10" s="41"/>
-      <c r="E10" s="42"/>
-      <c r="F10" s="40"/>
-      <c r="G10" s="41"/>
-      <c r="H10" s="42"/>
-      <c r="I10" s="40"/>
-      <c r="J10" s="41"/>
-      <c r="K10" s="42"/>
-      <c r="L10" s="40"/>
-      <c r="M10" s="41"/>
-      <c r="N10" s="42"/>
-      <c r="O10" s="40"/>
-      <c r="P10" s="41"/>
-      <c r="Q10" s="42"/>
-      <c r="R10" s="40"/>
-      <c r="S10" s="41"/>
-      <c r="T10" s="42"/>
-      <c r="U10" s="40"/>
-      <c r="V10" s="41"/>
-      <c r="W10" s="42"/>
-      <c r="X10" s="40"/>
-      <c r="Y10" s="41"/>
-      <c r="Z10" s="42"/>
-      <c r="AA10" s="40"/>
-      <c r="AB10" s="41"/>
-      <c r="AC10" s="42"/>
-      <c r="AD10" s="40"/>
-      <c r="AE10" s="41"/>
-      <c r="AF10" s="42"/>
-      <c r="AG10" s="40"/>
-      <c r="AH10" s="41"/>
-      <c r="AI10" s="42"/>
-      <c r="AJ10" s="40"/>
-      <c r="AK10" s="41"/>
-      <c r="AL10" s="42"/>
-      <c r="AM10" s="40"/>
-      <c r="AN10" s="41"/>
-      <c r="AO10" s="42"/>
-      <c r="AP10" s="40"/>
-      <c r="AQ10" s="41"/>
-      <c r="AR10" s="42"/>
+      <c r="C10" s="31"/>
+      <c r="D10" s="32"/>
+      <c r="E10" s="33"/>
+      <c r="F10" s="31"/>
+      <c r="G10" s="32"/>
+      <c r="H10" s="33"/>
+      <c r="I10" s="31"/>
+      <c r="J10" s="32"/>
+      <c r="K10" s="33"/>
+      <c r="L10" s="31"/>
+      <c r="M10" s="32"/>
+      <c r="N10" s="33"/>
+      <c r="O10" s="31"/>
+      <c r="P10" s="32"/>
+      <c r="Q10" s="33"/>
+      <c r="R10" s="31"/>
+      <c r="S10" s="32"/>
+      <c r="T10" s="33"/>
+      <c r="U10" s="31"/>
+      <c r="V10" s="32"/>
+      <c r="W10" s="33"/>
+      <c r="X10" s="31"/>
+      <c r="Y10" s="32"/>
+      <c r="Z10" s="33"/>
+      <c r="AA10" s="31"/>
+      <c r="AB10" s="32"/>
+      <c r="AC10" s="33"/>
+      <c r="AD10" s="31"/>
+      <c r="AE10" s="32"/>
+      <c r="AF10" s="33"/>
+      <c r="AG10" s="31"/>
+      <c r="AH10" s="32"/>
+      <c r="AI10" s="33"/>
+      <c r="AJ10" s="31"/>
+      <c r="AK10" s="32"/>
+      <c r="AL10" s="33"/>
+      <c r="AM10" s="31"/>
+      <c r="AN10" s="32"/>
+      <c r="AO10" s="33"/>
+      <c r="AP10" s="31"/>
+      <c r="AQ10" s="32"/>
+      <c r="AR10" s="33"/>
     </row>
     <row r="11" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B11" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="C11" s="40"/>
-      <c r="D11" s="41"/>
-      <c r="E11" s="42"/>
-      <c r="F11" s="40"/>
-      <c r="G11" s="41"/>
-      <c r="H11" s="42"/>
-      <c r="I11" s="40"/>
-      <c r="J11" s="41"/>
-      <c r="K11" s="42"/>
-      <c r="L11" s="40"/>
-      <c r="M11" s="41"/>
-      <c r="N11" s="42"/>
-      <c r="O11" s="40"/>
-      <c r="P11" s="41"/>
-      <c r="Q11" s="42"/>
-      <c r="R11" s="40"/>
-      <c r="S11" s="41"/>
-      <c r="T11" s="42"/>
-      <c r="U11" s="40"/>
-      <c r="V11" s="41"/>
-      <c r="W11" s="42"/>
-      <c r="X11" s="40"/>
-      <c r="Y11" s="41"/>
-      <c r="Z11" s="42"/>
-      <c r="AA11" s="40"/>
-      <c r="AB11" s="41"/>
-      <c r="AC11" s="42"/>
-      <c r="AD11" s="40"/>
-      <c r="AE11" s="41"/>
-      <c r="AF11" s="42"/>
-      <c r="AG11" s="40"/>
-      <c r="AH11" s="41"/>
-      <c r="AI11" s="42"/>
-      <c r="AJ11" s="40"/>
-      <c r="AK11" s="41"/>
-      <c r="AL11" s="42"/>
-      <c r="AM11" s="40"/>
-      <c r="AN11" s="41"/>
-      <c r="AO11" s="42"/>
-      <c r="AP11" s="40"/>
-      <c r="AQ11" s="41"/>
-      <c r="AR11" s="42"/>
+      <c r="C11" s="31"/>
+      <c r="D11" s="32"/>
+      <c r="E11" s="33"/>
+      <c r="F11" s="31"/>
+      <c r="G11" s="32"/>
+      <c r="H11" s="33"/>
+      <c r="I11" s="31"/>
+      <c r="J11" s="32"/>
+      <c r="K11" s="33"/>
+      <c r="L11" s="31"/>
+      <c r="M11" s="32"/>
+      <c r="N11" s="33"/>
+      <c r="O11" s="31"/>
+      <c r="P11" s="32"/>
+      <c r="Q11" s="33"/>
+      <c r="R11" s="31"/>
+      <c r="S11" s="32"/>
+      <c r="T11" s="33"/>
+      <c r="U11" s="31"/>
+      <c r="V11" s="32"/>
+      <c r="W11" s="33"/>
+      <c r="X11" s="31"/>
+      <c r="Y11" s="32"/>
+      <c r="Z11" s="33"/>
+      <c r="AA11" s="31"/>
+      <c r="AB11" s="32"/>
+      <c r="AC11" s="33"/>
+      <c r="AD11" s="31"/>
+      <c r="AE11" s="32"/>
+      <c r="AF11" s="33"/>
+      <c r="AG11" s="31"/>
+      <c r="AH11" s="32"/>
+      <c r="AI11" s="33"/>
+      <c r="AJ11" s="31"/>
+      <c r="AK11" s="32"/>
+      <c r="AL11" s="33"/>
+      <c r="AM11" s="31"/>
+      <c r="AN11" s="32"/>
+      <c r="AO11" s="33"/>
+      <c r="AP11" s="31"/>
+      <c r="AQ11" s="32"/>
+      <c r="AR11" s="33"/>
     </row>
     <row r="12" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B12" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="40"/>
-      <c r="D12" s="41"/>
-      <c r="E12" s="42"/>
-      <c r="F12" s="40"/>
-      <c r="G12" s="41"/>
-      <c r="H12" s="42"/>
-      <c r="I12" s="40"/>
-      <c r="J12" s="41"/>
-      <c r="K12" s="42"/>
-      <c r="L12" s="40"/>
-      <c r="M12" s="41"/>
-      <c r="N12" s="42"/>
-      <c r="O12" s="40"/>
-      <c r="P12" s="41"/>
-      <c r="Q12" s="42"/>
-      <c r="R12" s="40"/>
-      <c r="S12" s="41"/>
-      <c r="T12" s="42"/>
-      <c r="U12" s="40"/>
-      <c r="V12" s="41"/>
-      <c r="W12" s="42"/>
-      <c r="X12" s="40"/>
-      <c r="Y12" s="41"/>
-      <c r="Z12" s="42"/>
-      <c r="AA12" s="40"/>
-      <c r="AB12" s="41"/>
-      <c r="AC12" s="42"/>
-      <c r="AD12" s="40"/>
-      <c r="AE12" s="41"/>
-      <c r="AF12" s="42"/>
-      <c r="AG12" s="40"/>
-      <c r="AH12" s="41"/>
-      <c r="AI12" s="42"/>
-      <c r="AJ12" s="40"/>
-      <c r="AK12" s="41"/>
-      <c r="AL12" s="42"/>
-      <c r="AM12" s="40"/>
-      <c r="AN12" s="41"/>
-      <c r="AO12" s="42"/>
-      <c r="AP12" s="40"/>
-      <c r="AQ12" s="41"/>
-      <c r="AR12" s="42"/>
+      <c r="C12" s="31"/>
+      <c r="D12" s="32"/>
+      <c r="E12" s="33"/>
+      <c r="F12" s="31"/>
+      <c r="G12" s="32"/>
+      <c r="H12" s="33"/>
+      <c r="I12" s="31"/>
+      <c r="J12" s="32"/>
+      <c r="K12" s="33"/>
+      <c r="L12" s="31"/>
+      <c r="M12" s="32"/>
+      <c r="N12" s="33"/>
+      <c r="O12" s="31"/>
+      <c r="P12" s="32"/>
+      <c r="Q12" s="33"/>
+      <c r="R12" s="31"/>
+      <c r="S12" s="32"/>
+      <c r="T12" s="33"/>
+      <c r="U12" s="31"/>
+      <c r="V12" s="32"/>
+      <c r="W12" s="33"/>
+      <c r="X12" s="31"/>
+      <c r="Y12" s="32"/>
+      <c r="Z12" s="33"/>
+      <c r="AA12" s="31"/>
+      <c r="AB12" s="32"/>
+      <c r="AC12" s="33"/>
+      <c r="AD12" s="31"/>
+      <c r="AE12" s="32"/>
+      <c r="AF12" s="33"/>
+      <c r="AG12" s="31"/>
+      <c r="AH12" s="32"/>
+      <c r="AI12" s="33"/>
+      <c r="AJ12" s="31"/>
+      <c r="AK12" s="32"/>
+      <c r="AL12" s="33"/>
+      <c r="AM12" s="31"/>
+      <c r="AN12" s="32"/>
+      <c r="AO12" s="33"/>
+      <c r="AP12" s="31"/>
+      <c r="AQ12" s="32"/>
+      <c r="AR12" s="33"/>
     </row>
     <row r="13" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B13" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="C13" s="40"/>
-      <c r="D13" s="41"/>
-      <c r="E13" s="42"/>
-      <c r="F13" s="40"/>
-      <c r="G13" s="41"/>
-      <c r="H13" s="42"/>
-      <c r="I13" s="40"/>
-      <c r="J13" s="41"/>
-      <c r="K13" s="42"/>
-      <c r="L13" s="40"/>
-      <c r="M13" s="41"/>
-      <c r="N13" s="42"/>
-      <c r="O13" s="40"/>
-      <c r="P13" s="41"/>
-      <c r="Q13" s="42"/>
-      <c r="R13" s="40"/>
-      <c r="S13" s="41"/>
-      <c r="T13" s="42"/>
-      <c r="U13" s="40"/>
-      <c r="V13" s="41"/>
-      <c r="W13" s="42"/>
-      <c r="X13" s="40"/>
-      <c r="Y13" s="41"/>
-      <c r="Z13" s="42"/>
-      <c r="AA13" s="40"/>
-      <c r="AB13" s="41"/>
-      <c r="AC13" s="42"/>
-      <c r="AD13" s="40"/>
-      <c r="AE13" s="41"/>
-      <c r="AF13" s="42"/>
-      <c r="AG13" s="40"/>
-      <c r="AH13" s="41"/>
-      <c r="AI13" s="42"/>
-      <c r="AJ13" s="40"/>
-      <c r="AK13" s="41"/>
-      <c r="AL13" s="42"/>
-      <c r="AM13" s="40"/>
-      <c r="AN13" s="41"/>
-      <c r="AO13" s="42"/>
-      <c r="AP13" s="40"/>
-      <c r="AQ13" s="41"/>
-      <c r="AR13" s="42"/>
+      <c r="C13" s="31"/>
+      <c r="D13" s="32"/>
+      <c r="E13" s="33"/>
+      <c r="F13" s="31"/>
+      <c r="G13" s="32"/>
+      <c r="H13" s="33"/>
+      <c r="I13" s="31"/>
+      <c r="J13" s="32"/>
+      <c r="K13" s="33"/>
+      <c r="L13" s="31"/>
+      <c r="M13" s="32"/>
+      <c r="N13" s="33"/>
+      <c r="O13" s="31"/>
+      <c r="P13" s="32"/>
+      <c r="Q13" s="33"/>
+      <c r="R13" s="31"/>
+      <c r="S13" s="32"/>
+      <c r="T13" s="33"/>
+      <c r="U13" s="31"/>
+      <c r="V13" s="32"/>
+      <c r="W13" s="33"/>
+      <c r="X13" s="31"/>
+      <c r="Y13" s="32"/>
+      <c r="Z13" s="33"/>
+      <c r="AA13" s="31"/>
+      <c r="AB13" s="32"/>
+      <c r="AC13" s="33"/>
+      <c r="AD13" s="31"/>
+      <c r="AE13" s="32"/>
+      <c r="AF13" s="33"/>
+      <c r="AG13" s="31"/>
+      <c r="AH13" s="32"/>
+      <c r="AI13" s="33"/>
+      <c r="AJ13" s="31"/>
+      <c r="AK13" s="32"/>
+      <c r="AL13" s="33"/>
+      <c r="AM13" s="31"/>
+      <c r="AN13" s="32"/>
+      <c r="AO13" s="33"/>
+      <c r="AP13" s="31"/>
+      <c r="AQ13" s="32"/>
+      <c r="AR13" s="33"/>
     </row>
     <row r="14" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B14" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="C14" s="40"/>
-      <c r="D14" s="43"/>
-      <c r="E14" s="42"/>
-      <c r="F14" s="40"/>
-      <c r="G14" s="43"/>
-      <c r="H14" s="42"/>
-      <c r="I14" s="40"/>
-      <c r="J14" s="43"/>
-      <c r="K14" s="42"/>
-      <c r="L14" s="40"/>
-      <c r="M14" s="43"/>
-      <c r="N14" s="42"/>
-      <c r="O14" s="40"/>
-      <c r="P14" s="43"/>
-      <c r="Q14" s="42"/>
-      <c r="R14" s="40"/>
-      <c r="S14" s="43"/>
-      <c r="T14" s="42"/>
-      <c r="U14" s="40"/>
-      <c r="V14" s="43"/>
-      <c r="W14" s="42"/>
-      <c r="X14" s="40"/>
-      <c r="Y14" s="43"/>
-      <c r="Z14" s="42"/>
-      <c r="AA14" s="40"/>
-      <c r="AB14" s="43"/>
-      <c r="AC14" s="42"/>
-      <c r="AD14" s="40"/>
-      <c r="AE14" s="43"/>
-      <c r="AF14" s="42"/>
-      <c r="AG14" s="40"/>
-      <c r="AH14" s="43"/>
-      <c r="AI14" s="42"/>
-      <c r="AJ14" s="40"/>
-      <c r="AK14" s="43"/>
-      <c r="AL14" s="42"/>
-      <c r="AM14" s="40"/>
-      <c r="AN14" s="43"/>
-      <c r="AO14" s="42"/>
-      <c r="AP14" s="40"/>
-      <c r="AQ14" s="43"/>
-      <c r="AR14" s="42"/>
+      <c r="C14" s="31"/>
+      <c r="D14" s="34"/>
+      <c r="E14" s="33"/>
+      <c r="F14" s="31"/>
+      <c r="G14" s="34"/>
+      <c r="H14" s="33"/>
+      <c r="I14" s="31"/>
+      <c r="J14" s="34"/>
+      <c r="K14" s="33"/>
+      <c r="L14" s="31"/>
+      <c r="M14" s="34"/>
+      <c r="N14" s="33"/>
+      <c r="O14" s="31"/>
+      <c r="P14" s="34"/>
+      <c r="Q14" s="33"/>
+      <c r="R14" s="31"/>
+      <c r="S14" s="34"/>
+      <c r="T14" s="33"/>
+      <c r="U14" s="31"/>
+      <c r="V14" s="34"/>
+      <c r="W14" s="33"/>
+      <c r="X14" s="31"/>
+      <c r="Y14" s="34"/>
+      <c r="Z14" s="33"/>
+      <c r="AA14" s="31"/>
+      <c r="AB14" s="34"/>
+      <c r="AC14" s="33"/>
+      <c r="AD14" s="31"/>
+      <c r="AE14" s="34"/>
+      <c r="AF14" s="33"/>
+      <c r="AG14" s="31"/>
+      <c r="AH14" s="34"/>
+      <c r="AI14" s="33"/>
+      <c r="AJ14" s="31"/>
+      <c r="AK14" s="34"/>
+      <c r="AL14" s="33"/>
+      <c r="AM14" s="31"/>
+      <c r="AN14" s="34"/>
+      <c r="AO14" s="33"/>
+      <c r="AP14" s="31"/>
+      <c r="AQ14" s="34"/>
+      <c r="AR14" s="33"/>
     </row>
     <row r="15" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B15" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="40"/>
-      <c r="D15" s="41"/>
-      <c r="E15" s="42"/>
-      <c r="F15" s="40"/>
-      <c r="G15" s="41"/>
-      <c r="H15" s="42"/>
-      <c r="I15" s="40"/>
-      <c r="J15" s="41"/>
-      <c r="K15" s="42"/>
-      <c r="L15" s="40"/>
-      <c r="M15" s="41"/>
-      <c r="N15" s="42"/>
-      <c r="O15" s="40"/>
-      <c r="P15" s="41"/>
-      <c r="Q15" s="42"/>
-      <c r="R15" s="40"/>
-      <c r="S15" s="41"/>
-      <c r="T15" s="42"/>
-      <c r="U15" s="40"/>
-      <c r="V15" s="41"/>
-      <c r="W15" s="42"/>
-      <c r="X15" s="40"/>
-      <c r="Y15" s="41"/>
-      <c r="Z15" s="42"/>
-      <c r="AA15" s="40"/>
-      <c r="AB15" s="41"/>
-      <c r="AC15" s="42"/>
-      <c r="AD15" s="40"/>
-      <c r="AE15" s="41"/>
-      <c r="AF15" s="42"/>
-      <c r="AG15" s="40"/>
-      <c r="AH15" s="41"/>
-      <c r="AI15" s="42"/>
-      <c r="AJ15" s="40"/>
-      <c r="AK15" s="41"/>
-      <c r="AL15" s="42"/>
-      <c r="AM15" s="40"/>
-      <c r="AN15" s="41"/>
-      <c r="AO15" s="42"/>
-      <c r="AP15" s="40"/>
-      <c r="AQ15" s="41"/>
-      <c r="AR15" s="42"/>
+      <c r="C15" s="31"/>
+      <c r="D15" s="32"/>
+      <c r="E15" s="33"/>
+      <c r="F15" s="31"/>
+      <c r="G15" s="32"/>
+      <c r="H15" s="33"/>
+      <c r="I15" s="31"/>
+      <c r="J15" s="32"/>
+      <c r="K15" s="33"/>
+      <c r="L15" s="31"/>
+      <c r="M15" s="32"/>
+      <c r="N15" s="33"/>
+      <c r="O15" s="31"/>
+      <c r="P15" s="32"/>
+      <c r="Q15" s="33"/>
+      <c r="R15" s="31"/>
+      <c r="S15" s="32"/>
+      <c r="T15" s="33"/>
+      <c r="U15" s="31"/>
+      <c r="V15" s="32"/>
+      <c r="W15" s="33"/>
+      <c r="X15" s="31"/>
+      <c r="Y15" s="32"/>
+      <c r="Z15" s="33"/>
+      <c r="AA15" s="31"/>
+      <c r="AB15" s="32"/>
+      <c r="AC15" s="33"/>
+      <c r="AD15" s="31"/>
+      <c r="AE15" s="32"/>
+      <c r="AF15" s="33"/>
+      <c r="AG15" s="31"/>
+      <c r="AH15" s="32"/>
+      <c r="AI15" s="33"/>
+      <c r="AJ15" s="31"/>
+      <c r="AK15" s="32"/>
+      <c r="AL15" s="33"/>
+      <c r="AM15" s="31"/>
+      <c r="AN15" s="32"/>
+      <c r="AO15" s="33"/>
+      <c r="AP15" s="31"/>
+      <c r="AQ15" s="32"/>
+      <c r="AR15" s="33"/>
     </row>
     <row r="16" spans="1:44" ht="30.75" x14ac:dyDescent="0.45">
       <c r="B16" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="C16" s="40"/>
-      <c r="D16" s="41"/>
-      <c r="E16" s="42"/>
-      <c r="F16" s="40"/>
-      <c r="G16" s="41"/>
-      <c r="H16" s="42"/>
-      <c r="I16" s="40"/>
-      <c r="J16" s="41"/>
-      <c r="K16" s="42"/>
-      <c r="L16" s="40"/>
-      <c r="M16" s="41"/>
-      <c r="N16" s="42"/>
-      <c r="O16" s="40"/>
-      <c r="P16" s="41"/>
-      <c r="Q16" s="42"/>
-      <c r="R16" s="40"/>
-      <c r="S16" s="41"/>
-      <c r="T16" s="42"/>
-      <c r="U16" s="40"/>
-      <c r="V16" s="41"/>
-      <c r="W16" s="42"/>
-      <c r="X16" s="40"/>
-      <c r="Y16" s="41"/>
-      <c r="Z16" s="42"/>
-      <c r="AA16" s="40"/>
-      <c r="AB16" s="41"/>
-      <c r="AC16" s="42"/>
-      <c r="AD16" s="40"/>
-      <c r="AE16" s="41"/>
-      <c r="AF16" s="42"/>
-      <c r="AG16" s="40"/>
-      <c r="AH16" s="41"/>
-      <c r="AI16" s="42"/>
-      <c r="AJ16" s="40"/>
-      <c r="AK16" s="41"/>
-      <c r="AL16" s="42"/>
-      <c r="AM16" s="40"/>
-      <c r="AN16" s="41"/>
-      <c r="AO16" s="42"/>
-      <c r="AP16" s="40"/>
-      <c r="AQ16" s="41"/>
-      <c r="AR16" s="42"/>
+      <c r="C16" s="31"/>
+      <c r="D16" s="32"/>
+      <c r="E16" s="33"/>
+      <c r="F16" s="31"/>
+      <c r="G16" s="32"/>
+      <c r="H16" s="33"/>
+      <c r="I16" s="31"/>
+      <c r="J16" s="32"/>
+      <c r="K16" s="33"/>
+      <c r="L16" s="31"/>
+      <c r="M16" s="32"/>
+      <c r="N16" s="33"/>
+      <c r="O16" s="31"/>
+      <c r="P16" s="32"/>
+      <c r="Q16" s="33"/>
+      <c r="R16" s="31"/>
+      <c r="S16" s="32"/>
+      <c r="T16" s="33"/>
+      <c r="U16" s="31"/>
+      <c r="V16" s="32"/>
+      <c r="W16" s="33"/>
+      <c r="X16" s="31"/>
+      <c r="Y16" s="32"/>
+      <c r="Z16" s="33"/>
+      <c r="AA16" s="31"/>
+      <c r="AB16" s="32"/>
+      <c r="AC16" s="33"/>
+      <c r="AD16" s="31"/>
+      <c r="AE16" s="32"/>
+      <c r="AF16" s="33"/>
+      <c r="AG16" s="31"/>
+      <c r="AH16" s="32"/>
+      <c r="AI16" s="33"/>
+      <c r="AJ16" s="31"/>
+      <c r="AK16" s="32"/>
+      <c r="AL16" s="33"/>
+      <c r="AM16" s="31"/>
+      <c r="AN16" s="32"/>
+      <c r="AO16" s="33"/>
+      <c r="AP16" s="31"/>
+      <c r="AQ16" s="32"/>
+      <c r="AR16" s="33"/>
     </row>
     <row r="17" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B17" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="C17" s="40"/>
-      <c r="D17" s="44"/>
-      <c r="E17" s="42"/>
-      <c r="F17" s="40"/>
-      <c r="G17" s="44"/>
-      <c r="H17" s="42"/>
-      <c r="I17" s="40"/>
-      <c r="J17" s="44"/>
-      <c r="K17" s="42"/>
-      <c r="L17" s="40"/>
-      <c r="M17" s="44"/>
-      <c r="N17" s="42"/>
-      <c r="O17" s="40"/>
-      <c r="P17" s="44"/>
-      <c r="Q17" s="42"/>
-      <c r="R17" s="40"/>
-      <c r="S17" s="44"/>
-      <c r="T17" s="42"/>
-      <c r="U17" s="40"/>
-      <c r="V17" s="44"/>
-      <c r="W17" s="42"/>
-      <c r="X17" s="40"/>
-      <c r="Y17" s="44"/>
-      <c r="Z17" s="42"/>
-      <c r="AA17" s="40"/>
-      <c r="AB17" s="44"/>
-      <c r="AC17" s="42"/>
-      <c r="AD17" s="40"/>
-      <c r="AE17" s="44"/>
-      <c r="AF17" s="42"/>
-      <c r="AG17" s="40"/>
-      <c r="AH17" s="44"/>
-      <c r="AI17" s="42"/>
-      <c r="AJ17" s="40"/>
-      <c r="AK17" s="44"/>
-      <c r="AL17" s="42"/>
-      <c r="AM17" s="40"/>
-      <c r="AN17" s="44"/>
-      <c r="AO17" s="42"/>
-      <c r="AP17" s="40"/>
-      <c r="AQ17" s="44"/>
-      <c r="AR17" s="42"/>
+      <c r="C17" s="31"/>
+      <c r="D17" s="35"/>
+      <c r="E17" s="33"/>
+      <c r="F17" s="31"/>
+      <c r="G17" s="35"/>
+      <c r="H17" s="33"/>
+      <c r="I17" s="31"/>
+      <c r="J17" s="35"/>
+      <c r="K17" s="33"/>
+      <c r="L17" s="31"/>
+      <c r="M17" s="35"/>
+      <c r="N17" s="33"/>
+      <c r="O17" s="31"/>
+      <c r="P17" s="35"/>
+      <c r="Q17" s="33"/>
+      <c r="R17" s="31"/>
+      <c r="S17" s="35"/>
+      <c r="T17" s="33"/>
+      <c r="U17" s="31"/>
+      <c r="V17" s="35"/>
+      <c r="W17" s="33"/>
+      <c r="X17" s="31"/>
+      <c r="Y17" s="35"/>
+      <c r="Z17" s="33"/>
+      <c r="AA17" s="31"/>
+      <c r="AB17" s="35"/>
+      <c r="AC17" s="33"/>
+      <c r="AD17" s="31"/>
+      <c r="AE17" s="35"/>
+      <c r="AF17" s="33"/>
+      <c r="AG17" s="31"/>
+      <c r="AH17" s="35"/>
+      <c r="AI17" s="33"/>
+      <c r="AJ17" s="31"/>
+      <c r="AK17" s="35"/>
+      <c r="AL17" s="33"/>
+      <c r="AM17" s="31"/>
+      <c r="AN17" s="35"/>
+      <c r="AO17" s="33"/>
+      <c r="AP17" s="31"/>
+      <c r="AQ17" s="35"/>
+      <c r="AR17" s="33"/>
     </row>
     <row r="18" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B18" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="C18" s="40"/>
-      <c r="D18" s="41"/>
-      <c r="E18" s="42"/>
-      <c r="F18" s="40"/>
-      <c r="G18" s="41"/>
-      <c r="H18" s="42"/>
-      <c r="I18" s="40"/>
-      <c r="J18" s="41"/>
-      <c r="K18" s="42"/>
-      <c r="L18" s="40"/>
-      <c r="M18" s="41"/>
-      <c r="N18" s="42"/>
-      <c r="O18" s="40"/>
-      <c r="P18" s="41"/>
-      <c r="Q18" s="42"/>
-      <c r="R18" s="40"/>
-      <c r="S18" s="41"/>
-      <c r="T18" s="42"/>
-      <c r="U18" s="40"/>
-      <c r="V18" s="41"/>
-      <c r="W18" s="42"/>
-      <c r="X18" s="40"/>
-      <c r="Y18" s="41"/>
-      <c r="Z18" s="42"/>
-      <c r="AA18" s="40"/>
-      <c r="AB18" s="41"/>
-      <c r="AC18" s="42"/>
-      <c r="AD18" s="40"/>
-      <c r="AE18" s="41"/>
-      <c r="AF18" s="42"/>
-      <c r="AG18" s="40"/>
-      <c r="AH18" s="41"/>
-      <c r="AI18" s="42"/>
-      <c r="AJ18" s="40"/>
-      <c r="AK18" s="41"/>
-      <c r="AL18" s="42"/>
-      <c r="AM18" s="40"/>
-      <c r="AN18" s="41"/>
-      <c r="AO18" s="42"/>
-      <c r="AP18" s="40"/>
-      <c r="AQ18" s="41"/>
-      <c r="AR18" s="42"/>
+      <c r="C18" s="31"/>
+      <c r="D18" s="32"/>
+      <c r="E18" s="33"/>
+      <c r="F18" s="31"/>
+      <c r="G18" s="32"/>
+      <c r="H18" s="33"/>
+      <c r="I18" s="31"/>
+      <c r="J18" s="32"/>
+      <c r="K18" s="33"/>
+      <c r="L18" s="31"/>
+      <c r="M18" s="32"/>
+      <c r="N18" s="33"/>
+      <c r="O18" s="31"/>
+      <c r="P18" s="32"/>
+      <c r="Q18" s="33"/>
+      <c r="R18" s="31"/>
+      <c r="S18" s="32"/>
+      <c r="T18" s="33"/>
+      <c r="U18" s="31"/>
+      <c r="V18" s="32"/>
+      <c r="W18" s="33"/>
+      <c r="X18" s="31"/>
+      <c r="Y18" s="32"/>
+      <c r="Z18" s="33"/>
+      <c r="AA18" s="31"/>
+      <c r="AB18" s="32"/>
+      <c r="AC18" s="33"/>
+      <c r="AD18" s="31"/>
+      <c r="AE18" s="32"/>
+      <c r="AF18" s="33"/>
+      <c r="AG18" s="31"/>
+      <c r="AH18" s="32"/>
+      <c r="AI18" s="33"/>
+      <c r="AJ18" s="31"/>
+      <c r="AK18" s="32"/>
+      <c r="AL18" s="33"/>
+      <c r="AM18" s="31"/>
+      <c r="AN18" s="32"/>
+      <c r="AO18" s="33"/>
+      <c r="AP18" s="31"/>
+      <c r="AQ18" s="32"/>
+      <c r="AR18" s="33"/>
     </row>
     <row r="19" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B19" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="C19" s="40"/>
-      <c r="D19" s="41"/>
-      <c r="E19" s="42"/>
-      <c r="F19" s="40"/>
-      <c r="G19" s="41"/>
-      <c r="H19" s="42"/>
-      <c r="I19" s="40"/>
-      <c r="J19" s="41"/>
-      <c r="K19" s="42"/>
-      <c r="L19" s="40"/>
-      <c r="M19" s="41"/>
-      <c r="N19" s="42"/>
-      <c r="O19" s="40"/>
-      <c r="P19" s="41"/>
-      <c r="Q19" s="42"/>
-      <c r="R19" s="40"/>
-      <c r="S19" s="41"/>
-      <c r="T19" s="42"/>
-      <c r="U19" s="40"/>
-      <c r="V19" s="41"/>
-      <c r="W19" s="42"/>
-      <c r="X19" s="40"/>
-      <c r="Y19" s="41"/>
-      <c r="Z19" s="42"/>
-      <c r="AA19" s="40"/>
-      <c r="AB19" s="41"/>
-      <c r="AC19" s="42"/>
-      <c r="AD19" s="40"/>
-      <c r="AE19" s="41"/>
-      <c r="AF19" s="42"/>
-      <c r="AG19" s="40"/>
-      <c r="AH19" s="41"/>
-      <c r="AI19" s="42"/>
-      <c r="AJ19" s="40"/>
-      <c r="AK19" s="41"/>
-      <c r="AL19" s="42"/>
-      <c r="AM19" s="40"/>
-      <c r="AN19" s="41"/>
-      <c r="AO19" s="42"/>
-      <c r="AP19" s="40"/>
-      <c r="AQ19" s="41"/>
-      <c r="AR19" s="42"/>
+      <c r="C19" s="31"/>
+      <c r="D19" s="32"/>
+      <c r="E19" s="33"/>
+      <c r="F19" s="31"/>
+      <c r="G19" s="32"/>
+      <c r="H19" s="33"/>
+      <c r="I19" s="31"/>
+      <c r="J19" s="32"/>
+      <c r="K19" s="33"/>
+      <c r="L19" s="31"/>
+      <c r="M19" s="32"/>
+      <c r="N19" s="33"/>
+      <c r="O19" s="31"/>
+      <c r="P19" s="32"/>
+      <c r="Q19" s="33"/>
+      <c r="R19" s="31"/>
+      <c r="S19" s="32"/>
+      <c r="T19" s="33"/>
+      <c r="U19" s="31"/>
+      <c r="V19" s="32"/>
+      <c r="W19" s="33"/>
+      <c r="X19" s="31"/>
+      <c r="Y19" s="32"/>
+      <c r="Z19" s="33"/>
+      <c r="AA19" s="31"/>
+      <c r="AB19" s="32"/>
+      <c r="AC19" s="33"/>
+      <c r="AD19" s="31"/>
+      <c r="AE19" s="32"/>
+      <c r="AF19" s="33"/>
+      <c r="AG19" s="31"/>
+      <c r="AH19" s="32"/>
+      <c r="AI19" s="33"/>
+      <c r="AJ19" s="31"/>
+      <c r="AK19" s="32"/>
+      <c r="AL19" s="33"/>
+      <c r="AM19" s="31"/>
+      <c r="AN19" s="32"/>
+      <c r="AO19" s="33"/>
+      <c r="AP19" s="31"/>
+      <c r="AQ19" s="32"/>
+      <c r="AR19" s="33"/>
     </row>
     <row r="20" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B20" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="C20" s="40"/>
-      <c r="D20" s="46" t="e">
+      <c r="C20" s="31"/>
+      <c r="D20" s="37" t="e">
         <f>D18/D19</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E20" s="45"/>
-      <c r="F20" s="40"/>
-      <c r="G20" s="46" t="e">
+      <c r="E20" s="36"/>
+      <c r="F20" s="31"/>
+      <c r="G20" s="37" t="e">
         <f>G18/G19</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="H20" s="45"/>
-      <c r="I20" s="40"/>
-      <c r="J20" s="46" t="e">
+      <c r="H20" s="36"/>
+      <c r="I20" s="31"/>
+      <c r="J20" s="37" t="e">
         <f>J18/J19</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K20" s="45"/>
-      <c r="L20" s="40"/>
-      <c r="M20" s="46" t="e">
+      <c r="K20" s="36"/>
+      <c r="L20" s="31"/>
+      <c r="M20" s="37" t="e">
         <f>M18/M19</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="N20" s="45"/>
-      <c r="O20" s="40"/>
-      <c r="P20" s="46" t="e">
+      <c r="N20" s="36"/>
+      <c r="O20" s="31"/>
+      <c r="P20" s="37" t="e">
         <f>P18/P19</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q20" s="45"/>
-      <c r="R20" s="40"/>
-      <c r="S20" s="46" t="e">
+      <c r="Q20" s="36"/>
+      <c r="R20" s="31"/>
+      <c r="S20" s="37" t="e">
         <f>S18/S19</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="T20" s="45"/>
-      <c r="U20" s="40"/>
-      <c r="V20" s="46" t="e">
+      <c r="T20" s="36"/>
+      <c r="U20" s="31"/>
+      <c r="V20" s="37" t="e">
         <f>V18/V19</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="W20" s="45"/>
-      <c r="X20" s="40"/>
-      <c r="Y20" s="46" t="e">
+      <c r="W20" s="36"/>
+      <c r="X20" s="31"/>
+      <c r="Y20" s="37" t="e">
         <f>Y18/Y19</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Z20" s="45"/>
-      <c r="AA20" s="40"/>
-      <c r="AB20" s="46" t="e">
+      <c r="Z20" s="36"/>
+      <c r="AA20" s="31"/>
+      <c r="AB20" s="37" t="e">
         <f>AB18/AB19</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AC20" s="45"/>
-      <c r="AD20" s="40"/>
-      <c r="AE20" s="46" t="e">
+      <c r="AC20" s="36"/>
+      <c r="AD20" s="31"/>
+      <c r="AE20" s="37" t="e">
         <f>AE18/AE19</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AF20" s="45"/>
-      <c r="AG20" s="40"/>
-      <c r="AH20" s="46" t="e">
+      <c r="AF20" s="36"/>
+      <c r="AG20" s="31"/>
+      <c r="AH20" s="37" t="e">
         <f>AH18/AH19</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AI20" s="45"/>
-      <c r="AJ20" s="40"/>
-      <c r="AK20" s="46" t="e">
+      <c r="AI20" s="36"/>
+      <c r="AJ20" s="31"/>
+      <c r="AK20" s="37" t="e">
         <f>AK18/AK19</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AL20" s="45"/>
-      <c r="AM20" s="40"/>
-      <c r="AN20" s="46" t="e">
+      <c r="AL20" s="36"/>
+      <c r="AM20" s="31"/>
+      <c r="AN20" s="37" t="e">
         <f>AN18/AN19</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AO20" s="45"/>
-      <c r="AP20" s="40"/>
-      <c r="AQ20" s="46" t="e">
+      <c r="AO20" s="36"/>
+      <c r="AP20" s="31"/>
+      <c r="AQ20" s="37" t="e">
         <f>AQ18/AQ19</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AR20" s="45"/>
+      <c r="AR20" s="36"/>
     </row>
     <row r="21" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B21" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="C21" s="40"/>
-      <c r="D21" s="41"/>
-      <c r="E21" s="42"/>
-      <c r="F21" s="40"/>
-      <c r="G21" s="41"/>
-      <c r="H21" s="42"/>
-      <c r="I21" s="40"/>
-      <c r="J21" s="41"/>
-      <c r="K21" s="42"/>
-      <c r="L21" s="40"/>
-      <c r="M21" s="41"/>
-      <c r="N21" s="42"/>
-      <c r="O21" s="40"/>
-      <c r="P21" s="41"/>
-      <c r="Q21" s="42"/>
-      <c r="R21" s="40"/>
-      <c r="S21" s="41"/>
-      <c r="T21" s="42"/>
-      <c r="U21" s="40"/>
-      <c r="V21" s="41"/>
-      <c r="W21" s="42"/>
-      <c r="X21" s="40"/>
-      <c r="Y21" s="41"/>
-      <c r="Z21" s="42"/>
-      <c r="AA21" s="40"/>
-      <c r="AB21" s="41"/>
-      <c r="AC21" s="42"/>
-      <c r="AD21" s="40"/>
-      <c r="AE21" s="41"/>
-      <c r="AF21" s="42"/>
-      <c r="AG21" s="40"/>
-      <c r="AH21" s="41"/>
-      <c r="AI21" s="42"/>
-      <c r="AJ21" s="40"/>
-      <c r="AK21" s="41"/>
-      <c r="AL21" s="42"/>
-      <c r="AM21" s="40"/>
-      <c r="AN21" s="41"/>
-      <c r="AO21" s="42"/>
-      <c r="AP21" s="40"/>
-      <c r="AQ21" s="41"/>
-      <c r="AR21" s="42"/>
+      <c r="C21" s="31"/>
+      <c r="D21" s="32"/>
+      <c r="E21" s="33"/>
+      <c r="F21" s="31"/>
+      <c r="G21" s="32"/>
+      <c r="H21" s="33"/>
+      <c r="I21" s="31"/>
+      <c r="J21" s="32"/>
+      <c r="K21" s="33"/>
+      <c r="L21" s="31"/>
+      <c r="M21" s="32"/>
+      <c r="N21" s="33"/>
+      <c r="O21" s="31"/>
+      <c r="P21" s="32"/>
+      <c r="Q21" s="33"/>
+      <c r="R21" s="31"/>
+      <c r="S21" s="32"/>
+      <c r="T21" s="33"/>
+      <c r="U21" s="31"/>
+      <c r="V21" s="32"/>
+      <c r="W21" s="33"/>
+      <c r="X21" s="31"/>
+      <c r="Y21" s="32"/>
+      <c r="Z21" s="33"/>
+      <c r="AA21" s="31"/>
+      <c r="AB21" s="32"/>
+      <c r="AC21" s="33"/>
+      <c r="AD21" s="31"/>
+      <c r="AE21" s="32"/>
+      <c r="AF21" s="33"/>
+      <c r="AG21" s="31"/>
+      <c r="AH21" s="32"/>
+      <c r="AI21" s="33"/>
+      <c r="AJ21" s="31"/>
+      <c r="AK21" s="32"/>
+      <c r="AL21" s="33"/>
+      <c r="AM21" s="31"/>
+      <c r="AN21" s="32"/>
+      <c r="AO21" s="33"/>
+      <c r="AP21" s="31"/>
+      <c r="AQ21" s="32"/>
+      <c r="AR21" s="33"/>
     </row>
     <row r="22" spans="1:44" ht="61.5" x14ac:dyDescent="0.45">
       <c r="B22" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="C22" s="40"/>
-      <c r="D22" s="43"/>
-      <c r="E22" s="42"/>
-      <c r="F22" s="40"/>
-      <c r="G22" s="43"/>
-      <c r="H22" s="42"/>
-      <c r="I22" s="40"/>
-      <c r="J22" s="43"/>
-      <c r="K22" s="42"/>
-      <c r="L22" s="40"/>
-      <c r="M22" s="43"/>
-      <c r="N22" s="42"/>
-      <c r="O22" s="40"/>
-      <c r="P22" s="43"/>
-      <c r="Q22" s="42"/>
-      <c r="R22" s="40"/>
-      <c r="S22" s="43"/>
-      <c r="T22" s="42"/>
-      <c r="U22" s="40"/>
-      <c r="V22" s="43"/>
-      <c r="W22" s="42"/>
-      <c r="X22" s="40"/>
-      <c r="Y22" s="43"/>
-      <c r="Z22" s="42"/>
-      <c r="AA22" s="40"/>
-      <c r="AB22" s="43"/>
-      <c r="AC22" s="42"/>
-      <c r="AD22" s="40"/>
-      <c r="AE22" s="43"/>
-      <c r="AF22" s="42"/>
-      <c r="AG22" s="40"/>
-      <c r="AH22" s="43"/>
-      <c r="AI22" s="42"/>
-      <c r="AJ22" s="40"/>
-      <c r="AK22" s="43"/>
-      <c r="AL22" s="42"/>
-      <c r="AM22" s="40"/>
-      <c r="AN22" s="43"/>
-      <c r="AO22" s="42"/>
-      <c r="AP22" s="40"/>
-      <c r="AQ22" s="43"/>
-      <c r="AR22" s="42"/>
+      <c r="C22" s="31"/>
+      <c r="D22" s="34"/>
+      <c r="E22" s="33"/>
+      <c r="F22" s="31"/>
+      <c r="G22" s="34"/>
+      <c r="H22" s="33"/>
+      <c r="I22" s="31"/>
+      <c r="J22" s="34"/>
+      <c r="K22" s="33"/>
+      <c r="L22" s="31"/>
+      <c r="M22" s="34"/>
+      <c r="N22" s="33"/>
+      <c r="O22" s="31"/>
+      <c r="P22" s="34"/>
+      <c r="Q22" s="33"/>
+      <c r="R22" s="31"/>
+      <c r="S22" s="34"/>
+      <c r="T22" s="33"/>
+      <c r="U22" s="31"/>
+      <c r="V22" s="34"/>
+      <c r="W22" s="33"/>
+      <c r="X22" s="31"/>
+      <c r="Y22" s="34"/>
+      <c r="Z22" s="33"/>
+      <c r="AA22" s="31"/>
+      <c r="AB22" s="34"/>
+      <c r="AC22" s="33"/>
+      <c r="AD22" s="31"/>
+      <c r="AE22" s="34"/>
+      <c r="AF22" s="33"/>
+      <c r="AG22" s="31"/>
+      <c r="AH22" s="34"/>
+      <c r="AI22" s="33"/>
+      <c r="AJ22" s="31"/>
+      <c r="AK22" s="34"/>
+      <c r="AL22" s="33"/>
+      <c r="AM22" s="31"/>
+      <c r="AN22" s="34"/>
+      <c r="AO22" s="33"/>
+      <c r="AP22" s="31"/>
+      <c r="AQ22" s="34"/>
+      <c r="AR22" s="33"/>
     </row>
     <row r="23" spans="1:44" ht="30.75" x14ac:dyDescent="0.45">
       <c r="B23" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="C23" s="40"/>
-      <c r="D23" s="43"/>
-      <c r="E23" s="42"/>
-      <c r="F23" s="40"/>
-      <c r="G23" s="43"/>
-      <c r="H23" s="42"/>
-      <c r="I23" s="40"/>
-      <c r="J23" s="43"/>
-      <c r="K23" s="42"/>
-      <c r="L23" s="40"/>
-      <c r="M23" s="43"/>
-      <c r="N23" s="42"/>
-      <c r="O23" s="40"/>
-      <c r="P23" s="43"/>
-      <c r="Q23" s="42"/>
-      <c r="R23" s="40"/>
-      <c r="S23" s="43"/>
-      <c r="T23" s="42"/>
-      <c r="U23" s="40"/>
-      <c r="V23" s="43"/>
-      <c r="W23" s="42"/>
-      <c r="X23" s="40"/>
-      <c r="Y23" s="43"/>
-      <c r="Z23" s="42"/>
-      <c r="AA23" s="40"/>
-      <c r="AB23" s="43"/>
-      <c r="AC23" s="42"/>
-      <c r="AD23" s="40"/>
-      <c r="AE23" s="43"/>
-      <c r="AF23" s="42"/>
-      <c r="AG23" s="40"/>
-      <c r="AH23" s="43"/>
-      <c r="AI23" s="42"/>
-      <c r="AJ23" s="40"/>
-      <c r="AK23" s="43"/>
-      <c r="AL23" s="42"/>
-      <c r="AM23" s="40"/>
-      <c r="AN23" s="43"/>
-      <c r="AO23" s="42"/>
-      <c r="AP23" s="40"/>
-      <c r="AQ23" s="43"/>
-      <c r="AR23" s="42"/>
+      <c r="C23" s="31"/>
+      <c r="D23" s="34"/>
+      <c r="E23" s="33"/>
+      <c r="F23" s="31"/>
+      <c r="G23" s="34"/>
+      <c r="H23" s="33"/>
+      <c r="I23" s="31"/>
+      <c r="J23" s="34"/>
+      <c r="K23" s="33"/>
+      <c r="L23" s="31"/>
+      <c r="M23" s="34"/>
+      <c r="N23" s="33"/>
+      <c r="O23" s="31"/>
+      <c r="P23" s="34"/>
+      <c r="Q23" s="33"/>
+      <c r="R23" s="31"/>
+      <c r="S23" s="34"/>
+      <c r="T23" s="33"/>
+      <c r="U23" s="31"/>
+      <c r="V23" s="34"/>
+      <c r="W23" s="33"/>
+      <c r="X23" s="31"/>
+      <c r="Y23" s="34"/>
+      <c r="Z23" s="33"/>
+      <c r="AA23" s="31"/>
+      <c r="AB23" s="34"/>
+      <c r="AC23" s="33"/>
+      <c r="AD23" s="31"/>
+      <c r="AE23" s="34"/>
+      <c r="AF23" s="33"/>
+      <c r="AG23" s="31"/>
+      <c r="AH23" s="34"/>
+      <c r="AI23" s="33"/>
+      <c r="AJ23" s="31"/>
+      <c r="AK23" s="34"/>
+      <c r="AL23" s="33"/>
+      <c r="AM23" s="31"/>
+      <c r="AN23" s="34"/>
+      <c r="AO23" s="33"/>
+      <c r="AP23" s="31"/>
+      <c r="AQ23" s="34"/>
+      <c r="AR23" s="33"/>
     </row>
     <row r="24" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B24" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="C24" s="40"/>
-      <c r="D24" s="41"/>
-      <c r="E24" s="42"/>
-      <c r="F24" s="40"/>
-      <c r="G24" s="41"/>
-      <c r="H24" s="42"/>
-      <c r="I24" s="40"/>
-      <c r="J24" s="41"/>
-      <c r="K24" s="42"/>
-      <c r="L24" s="40"/>
-      <c r="M24" s="41"/>
-      <c r="N24" s="42"/>
-      <c r="O24" s="40"/>
-      <c r="P24" s="41"/>
-      <c r="Q24" s="42"/>
-      <c r="R24" s="40"/>
-      <c r="S24" s="41"/>
-      <c r="T24" s="42"/>
-      <c r="U24" s="40"/>
-      <c r="V24" s="41"/>
-      <c r="W24" s="42"/>
-      <c r="X24" s="40"/>
-      <c r="Y24" s="41"/>
-      <c r="Z24" s="42"/>
-      <c r="AA24" s="40"/>
-      <c r="AB24" s="41"/>
-      <c r="AC24" s="42"/>
-      <c r="AD24" s="40"/>
-      <c r="AE24" s="41"/>
-      <c r="AF24" s="42"/>
-      <c r="AG24" s="40"/>
-      <c r="AH24" s="41"/>
-      <c r="AI24" s="42"/>
-      <c r="AJ24" s="40"/>
-      <c r="AK24" s="41"/>
-      <c r="AL24" s="42"/>
-      <c r="AM24" s="40"/>
-      <c r="AN24" s="41"/>
-      <c r="AO24" s="42"/>
-      <c r="AP24" s="40"/>
-      <c r="AQ24" s="41"/>
-      <c r="AR24" s="42"/>
+      <c r="C24" s="31"/>
+      <c r="D24" s="32"/>
+      <c r="E24" s="33"/>
+      <c r="F24" s="31"/>
+      <c r="G24" s="32"/>
+      <c r="H24" s="33"/>
+      <c r="I24" s="31"/>
+      <c r="J24" s="32"/>
+      <c r="K24" s="33"/>
+      <c r="L24" s="31"/>
+      <c r="M24" s="32"/>
+      <c r="N24" s="33"/>
+      <c r="O24" s="31"/>
+      <c r="P24" s="32"/>
+      <c r="Q24" s="33"/>
+      <c r="R24" s="31"/>
+      <c r="S24" s="32"/>
+      <c r="T24" s="33"/>
+      <c r="U24" s="31"/>
+      <c r="V24" s="32"/>
+      <c r="W24" s="33"/>
+      <c r="X24" s="31"/>
+      <c r="Y24" s="32"/>
+      <c r="Z24" s="33"/>
+      <c r="AA24" s="31"/>
+      <c r="AB24" s="32"/>
+      <c r="AC24" s="33"/>
+      <c r="AD24" s="31"/>
+      <c r="AE24" s="32"/>
+      <c r="AF24" s="33"/>
+      <c r="AG24" s="31"/>
+      <c r="AH24" s="32"/>
+      <c r="AI24" s="33"/>
+      <c r="AJ24" s="31"/>
+      <c r="AK24" s="32"/>
+      <c r="AL24" s="33"/>
+      <c r="AM24" s="31"/>
+      <c r="AN24" s="32"/>
+      <c r="AO24" s="33"/>
+      <c r="AP24" s="31"/>
+      <c r="AQ24" s="32"/>
+      <c r="AR24" s="33"/>
     </row>
     <row r="25" spans="1:44" ht="48.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B25" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="C25" s="40"/>
-      <c r="D25" s="41"/>
-      <c r="E25" s="42"/>
-      <c r="F25" s="40"/>
-      <c r="G25" s="41"/>
-      <c r="H25" s="42"/>
-      <c r="I25" s="40"/>
-      <c r="J25" s="41"/>
-      <c r="K25" s="42"/>
-      <c r="L25" s="40"/>
-      <c r="M25" s="41"/>
-      <c r="N25" s="42"/>
-      <c r="O25" s="40"/>
-      <c r="P25" s="41"/>
-      <c r="Q25" s="42"/>
-      <c r="R25" s="40"/>
-      <c r="S25" s="41"/>
-      <c r="T25" s="42"/>
-      <c r="U25" s="40"/>
-      <c r="V25" s="41"/>
-      <c r="W25" s="42"/>
-      <c r="X25" s="40"/>
-      <c r="Y25" s="41"/>
-      <c r="Z25" s="42"/>
-      <c r="AA25" s="40"/>
-      <c r="AB25" s="41"/>
-      <c r="AC25" s="42"/>
-      <c r="AD25" s="40"/>
-      <c r="AE25" s="41"/>
-      <c r="AF25" s="42"/>
-      <c r="AG25" s="40"/>
-      <c r="AH25" s="41"/>
-      <c r="AI25" s="42"/>
-      <c r="AJ25" s="40"/>
-      <c r="AK25" s="41"/>
-      <c r="AL25" s="42"/>
-      <c r="AM25" s="40"/>
-      <c r="AN25" s="41"/>
-      <c r="AO25" s="42"/>
-      <c r="AP25" s="40"/>
-      <c r="AQ25" s="41"/>
-      <c r="AR25" s="42"/>
+      <c r="C25" s="31"/>
+      <c r="D25" s="32"/>
+      <c r="E25" s="33"/>
+      <c r="F25" s="31"/>
+      <c r="G25" s="32"/>
+      <c r="H25" s="33"/>
+      <c r="I25" s="31"/>
+      <c r="J25" s="32"/>
+      <c r="K25" s="33"/>
+      <c r="L25" s="31"/>
+      <c r="M25" s="32"/>
+      <c r="N25" s="33"/>
+      <c r="O25" s="31"/>
+      <c r="P25" s="32"/>
+      <c r="Q25" s="33"/>
+      <c r="R25" s="31"/>
+      <c r="S25" s="32"/>
+      <c r="T25" s="33"/>
+      <c r="U25" s="31"/>
+      <c r="V25" s="32"/>
+      <c r="W25" s="33"/>
+      <c r="X25" s="31"/>
+      <c r="Y25" s="32"/>
+      <c r="Z25" s="33"/>
+      <c r="AA25" s="31"/>
+      <c r="AB25" s="32"/>
+      <c r="AC25" s="33"/>
+      <c r="AD25" s="31"/>
+      <c r="AE25" s="32"/>
+      <c r="AF25" s="33"/>
+      <c r="AG25" s="31"/>
+      <c r="AH25" s="32"/>
+      <c r="AI25" s="33"/>
+      <c r="AJ25" s="31"/>
+      <c r="AK25" s="32"/>
+      <c r="AL25" s="33"/>
+      <c r="AM25" s="31"/>
+      <c r="AN25" s="32"/>
+      <c r="AO25" s="33"/>
+      <c r="AP25" s="31"/>
+      <c r="AQ25" s="32"/>
+      <c r="AR25" s="33"/>
     </row>
     <row r="26" spans="1:44" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B26" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="C26" s="40"/>
-      <c r="D26" s="41"/>
-      <c r="E26" s="42"/>
-      <c r="F26" s="40"/>
-      <c r="G26" s="41"/>
-      <c r="H26" s="42"/>
-      <c r="I26" s="40"/>
-      <c r="J26" s="41"/>
-      <c r="K26" s="42"/>
-      <c r="L26" s="40"/>
-      <c r="M26" s="41"/>
-      <c r="N26" s="42"/>
-      <c r="O26" s="40"/>
-      <c r="P26" s="41"/>
-      <c r="Q26" s="42"/>
-      <c r="R26" s="40"/>
-      <c r="S26" s="41"/>
-      <c r="T26" s="42"/>
-      <c r="U26" s="40"/>
-      <c r="V26" s="41"/>
-      <c r="W26" s="42"/>
-      <c r="X26" s="40"/>
-      <c r="Y26" s="41"/>
-      <c r="Z26" s="42"/>
-      <c r="AA26" s="40"/>
-      <c r="AB26" s="41"/>
-      <c r="AC26" s="42"/>
-      <c r="AD26" s="40"/>
-      <c r="AE26" s="41"/>
-      <c r="AF26" s="42"/>
-      <c r="AG26" s="40"/>
-      <c r="AH26" s="41"/>
-      <c r="AI26" s="42"/>
-      <c r="AJ26" s="40"/>
-      <c r="AK26" s="41"/>
-      <c r="AL26" s="42"/>
-      <c r="AM26" s="40"/>
-      <c r="AN26" s="41"/>
-      <c r="AO26" s="42"/>
-      <c r="AP26" s="40"/>
-      <c r="AQ26" s="41"/>
-      <c r="AR26" s="42"/>
+      <c r="C26" s="31"/>
+      <c r="D26" s="32"/>
+      <c r="E26" s="33"/>
+      <c r="F26" s="31"/>
+      <c r="G26" s="32"/>
+      <c r="H26" s="33"/>
+      <c r="I26" s="31"/>
+      <c r="J26" s="32"/>
+      <c r="K26" s="33"/>
+      <c r="L26" s="31"/>
+      <c r="M26" s="32"/>
+      <c r="N26" s="33"/>
+      <c r="O26" s="31"/>
+      <c r="P26" s="32"/>
+      <c r="Q26" s="33"/>
+      <c r="R26" s="31"/>
+      <c r="S26" s="32"/>
+      <c r="T26" s="33"/>
+      <c r="U26" s="31"/>
+      <c r="V26" s="32"/>
+      <c r="W26" s="33"/>
+      <c r="X26" s="31"/>
+      <c r="Y26" s="32"/>
+      <c r="Z26" s="33"/>
+      <c r="AA26" s="31"/>
+      <c r="AB26" s="32"/>
+      <c r="AC26" s="33"/>
+      <c r="AD26" s="31"/>
+      <c r="AE26" s="32"/>
+      <c r="AF26" s="33"/>
+      <c r="AG26" s="31"/>
+      <c r="AH26" s="32"/>
+      <c r="AI26" s="33"/>
+      <c r="AJ26" s="31"/>
+      <c r="AK26" s="32"/>
+      <c r="AL26" s="33"/>
+      <c r="AM26" s="31"/>
+      <c r="AN26" s="32"/>
+      <c r="AO26" s="33"/>
+      <c r="AP26" s="31"/>
+      <c r="AQ26" s="32"/>
+      <c r="AR26" s="33"/>
     </row>
     <row r="27" spans="1:44" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B27" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="C27" s="40"/>
-      <c r="D27" s="41"/>
-      <c r="E27" s="42"/>
-      <c r="F27" s="40"/>
-      <c r="G27" s="41"/>
-      <c r="H27" s="42"/>
-      <c r="I27" s="40"/>
-      <c r="J27" s="41"/>
-      <c r="K27" s="42"/>
-      <c r="L27" s="40"/>
-      <c r="M27" s="41"/>
-      <c r="N27" s="42"/>
-      <c r="O27" s="40"/>
-      <c r="P27" s="41"/>
-      <c r="Q27" s="42"/>
-      <c r="R27" s="40"/>
-      <c r="S27" s="41"/>
-      <c r="T27" s="42"/>
-      <c r="U27" s="40"/>
-      <c r="V27" s="41"/>
-      <c r="W27" s="42"/>
-      <c r="X27" s="40"/>
-      <c r="Y27" s="41"/>
-      <c r="Z27" s="42"/>
-      <c r="AA27" s="40"/>
-      <c r="AB27" s="41"/>
-      <c r="AC27" s="42"/>
-      <c r="AD27" s="40"/>
-      <c r="AE27" s="41"/>
-      <c r="AF27" s="42"/>
-      <c r="AG27" s="40"/>
-      <c r="AH27" s="41"/>
-      <c r="AI27" s="42"/>
-      <c r="AJ27" s="40"/>
-      <c r="AK27" s="41"/>
-      <c r="AL27" s="42"/>
-      <c r="AM27" s="40"/>
-      <c r="AN27" s="41"/>
-      <c r="AO27" s="42"/>
-      <c r="AP27" s="40"/>
-      <c r="AQ27" s="41"/>
-      <c r="AR27" s="42"/>
+      <c r="C27" s="31"/>
+      <c r="D27" s="32"/>
+      <c r="E27" s="33"/>
+      <c r="F27" s="31"/>
+      <c r="G27" s="32"/>
+      <c r="H27" s="33"/>
+      <c r="I27" s="31"/>
+      <c r="J27" s="32"/>
+      <c r="K27" s="33"/>
+      <c r="L27" s="31"/>
+      <c r="M27" s="32"/>
+      <c r="N27" s="33"/>
+      <c r="O27" s="31"/>
+      <c r="P27" s="32"/>
+      <c r="Q27" s="33"/>
+      <c r="R27" s="31"/>
+      <c r="S27" s="32"/>
+      <c r="T27" s="33"/>
+      <c r="U27" s="31"/>
+      <c r="V27" s="32"/>
+      <c r="W27" s="33"/>
+      <c r="X27" s="31"/>
+      <c r="Y27" s="32"/>
+      <c r="Z27" s="33"/>
+      <c r="AA27" s="31"/>
+      <c r="AB27" s="32"/>
+      <c r="AC27" s="33"/>
+      <c r="AD27" s="31"/>
+      <c r="AE27" s="32"/>
+      <c r="AF27" s="33"/>
+      <c r="AG27" s="31"/>
+      <c r="AH27" s="32"/>
+      <c r="AI27" s="33"/>
+      <c r="AJ27" s="31"/>
+      <c r="AK27" s="32"/>
+      <c r="AL27" s="33"/>
+      <c r="AM27" s="31"/>
+      <c r="AN27" s="32"/>
+      <c r="AO27" s="33"/>
+      <c r="AP27" s="31"/>
+      <c r="AQ27" s="32"/>
+      <c r="AR27" s="33"/>
     </row>
     <row r="28" spans="1:44" ht="76.900000000000006" x14ac:dyDescent="0.45">
       <c r="B28" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="C28" s="40"/>
-      <c r="D28" s="41"/>
-      <c r="E28" s="42"/>
-      <c r="F28" s="40"/>
-      <c r="G28" s="41"/>
-      <c r="H28" s="42"/>
-      <c r="I28" s="40"/>
-      <c r="J28" s="41"/>
-      <c r="K28" s="42"/>
-      <c r="L28" s="40"/>
-      <c r="M28" s="41"/>
-      <c r="N28" s="42"/>
-      <c r="O28" s="40"/>
-      <c r="P28" s="41"/>
-      <c r="Q28" s="42"/>
-      <c r="R28" s="40"/>
-      <c r="S28" s="41"/>
-      <c r="T28" s="42"/>
-      <c r="U28" s="40"/>
-      <c r="V28" s="41"/>
-      <c r="W28" s="42"/>
-      <c r="X28" s="40"/>
-      <c r="Y28" s="41"/>
-      <c r="Z28" s="42"/>
-      <c r="AA28" s="40"/>
-      <c r="AB28" s="41"/>
-      <c r="AC28" s="42"/>
-      <c r="AD28" s="40"/>
-      <c r="AE28" s="41"/>
-      <c r="AF28" s="42"/>
-      <c r="AG28" s="40"/>
-      <c r="AH28" s="41"/>
-      <c r="AI28" s="42"/>
-      <c r="AJ28" s="40"/>
-      <c r="AK28" s="41"/>
-      <c r="AL28" s="42"/>
-      <c r="AM28" s="40"/>
-      <c r="AN28" s="41"/>
-      <c r="AO28" s="42"/>
-      <c r="AP28" s="40"/>
-      <c r="AQ28" s="41"/>
-      <c r="AR28" s="42"/>
+      <c r="C28" s="31"/>
+      <c r="D28" s="32"/>
+      <c r="E28" s="33"/>
+      <c r="F28" s="31"/>
+      <c r="G28" s="32"/>
+      <c r="H28" s="33"/>
+      <c r="I28" s="31"/>
+      <c r="J28" s="32"/>
+      <c r="K28" s="33"/>
+      <c r="L28" s="31"/>
+      <c r="M28" s="32"/>
+      <c r="N28" s="33"/>
+      <c r="O28" s="31"/>
+      <c r="P28" s="32"/>
+      <c r="Q28" s="33"/>
+      <c r="R28" s="31"/>
+      <c r="S28" s="32"/>
+      <c r="T28" s="33"/>
+      <c r="U28" s="31"/>
+      <c r="V28" s="32"/>
+      <c r="W28" s="33"/>
+      <c r="X28" s="31"/>
+      <c r="Y28" s="32"/>
+      <c r="Z28" s="33"/>
+      <c r="AA28" s="31"/>
+      <c r="AB28" s="32"/>
+      <c r="AC28" s="33"/>
+      <c r="AD28" s="31"/>
+      <c r="AE28" s="32"/>
+      <c r="AF28" s="33"/>
+      <c r="AG28" s="31"/>
+      <c r="AH28" s="32"/>
+      <c r="AI28" s="33"/>
+      <c r="AJ28" s="31"/>
+      <c r="AK28" s="32"/>
+      <c r="AL28" s="33"/>
+      <c r="AM28" s="31"/>
+      <c r="AN28" s="32"/>
+      <c r="AO28" s="33"/>
+      <c r="AP28" s="31"/>
+      <c r="AQ28" s="32"/>
+      <c r="AR28" s="33"/>
     </row>
     <row r="29" spans="1:44" x14ac:dyDescent="0.45">
-      <c r="B29" s="47"/>
-      <c r="C29" s="48"/>
-      <c r="D29" s="49"/>
-      <c r="E29" s="50"/>
-      <c r="F29" s="48"/>
-      <c r="G29" s="49"/>
-      <c r="H29" s="50"/>
-      <c r="I29" s="48"/>
-      <c r="J29" s="49"/>
-      <c r="K29" s="50"/>
-      <c r="L29" s="48"/>
-      <c r="M29" s="49"/>
-      <c r="N29" s="50"/>
-      <c r="O29" s="48"/>
-      <c r="P29" s="49"/>
-      <c r="Q29" s="50"/>
-      <c r="R29" s="48"/>
-      <c r="S29" s="49"/>
-      <c r="T29" s="50"/>
-      <c r="U29" s="48"/>
-      <c r="V29" s="49"/>
-      <c r="W29" s="50"/>
-      <c r="X29" s="48"/>
-      <c r="Y29" s="49"/>
-      <c r="Z29" s="50"/>
-      <c r="AA29" s="48"/>
-      <c r="AB29" s="49"/>
-      <c r="AC29" s="50"/>
-      <c r="AD29" s="48"/>
-      <c r="AE29" s="49"/>
-      <c r="AF29" s="50"/>
-      <c r="AG29" s="48"/>
-      <c r="AH29" s="49"/>
-      <c r="AI29" s="50"/>
-      <c r="AJ29" s="48"/>
-      <c r="AK29" s="49"/>
-      <c r="AL29" s="50"/>
-      <c r="AM29" s="48"/>
-      <c r="AN29" s="49"/>
-      <c r="AO29" s="50"/>
-      <c r="AP29" s="48"/>
-      <c r="AQ29" s="49"/>
-      <c r="AR29" s="50"/>
+      <c r="B29" s="38"/>
+      <c r="C29" s="39"/>
+      <c r="D29" s="40"/>
+      <c r="E29" s="41"/>
+      <c r="F29" s="39"/>
+      <c r="G29" s="40"/>
+      <c r="H29" s="41"/>
+      <c r="I29" s="39"/>
+      <c r="J29" s="40"/>
+      <c r="K29" s="41"/>
+      <c r="L29" s="39"/>
+      <c r="M29" s="40"/>
+      <c r="N29" s="41"/>
+      <c r="O29" s="39"/>
+      <c r="P29" s="40"/>
+      <c r="Q29" s="41"/>
+      <c r="R29" s="39"/>
+      <c r="S29" s="40"/>
+      <c r="T29" s="41"/>
+      <c r="U29" s="39"/>
+      <c r="V29" s="40"/>
+      <c r="W29" s="41"/>
+      <c r="X29" s="39"/>
+      <c r="Y29" s="40"/>
+      <c r="Z29" s="41"/>
+      <c r="AA29" s="39"/>
+      <c r="AB29" s="40"/>
+      <c r="AC29" s="41"/>
+      <c r="AD29" s="39"/>
+      <c r="AE29" s="40"/>
+      <c r="AF29" s="41"/>
+      <c r="AG29" s="39"/>
+      <c r="AH29" s="40"/>
+      <c r="AI29" s="41"/>
+      <c r="AJ29" s="39"/>
+      <c r="AK29" s="40"/>
+      <c r="AL29" s="41"/>
+      <c r="AM29" s="39"/>
+      <c r="AN29" s="40"/>
+      <c r="AO29" s="41"/>
+      <c r="AP29" s="39"/>
+      <c r="AQ29" s="40"/>
+      <c r="AR29" s="41"/>
     </row>
     <row r="30" spans="1:44" s="2" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A30" s="1"/>
-      <c r="B30" s="51" t="s">
+      <c r="B30" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="C30" s="52">
+      <c r="C30" s="45">
         <f>AVERAGE(C4:C29)</f>
         <v>0</v>
       </c>
-      <c r="D30" s="52"/>
-      <c r="E30" s="53"/>
-      <c r="F30" s="52">
+      <c r="D30" s="45"/>
+      <c r="E30" s="46"/>
+      <c r="F30" s="45">
         <f>AVERAGE(F4:F29)</f>
         <v>0</v>
       </c>
-      <c r="G30" s="52"/>
-      <c r="H30" s="53"/>
-      <c r="I30" s="52">
+      <c r="G30" s="45"/>
+      <c r="H30" s="46"/>
+      <c r="I30" s="45">
         <f>AVERAGE(I4:I29)</f>
         <v>0</v>
       </c>
-      <c r="J30" s="52"/>
-      <c r="K30" s="53"/>
-      <c r="L30" s="52">
+      <c r="J30" s="45"/>
+      <c r="K30" s="46"/>
+      <c r="L30" s="45">
         <f>AVERAGE(L4:L29)</f>
         <v>0</v>
       </c>
-      <c r="M30" s="52"/>
-      <c r="N30" s="53"/>
-      <c r="O30" s="52">
+      <c r="M30" s="45"/>
+      <c r="N30" s="46"/>
+      <c r="O30" s="45">
         <f>AVERAGE(O4:O29)</f>
         <v>0</v>
       </c>
-      <c r="P30" s="52"/>
-      <c r="Q30" s="53"/>
-      <c r="R30" s="52">
+      <c r="P30" s="45"/>
+      <c r="Q30" s="46"/>
+      <c r="R30" s="45">
         <f>AVERAGE(R4:R29)</f>
         <v>0</v>
       </c>
-      <c r="S30" s="52"/>
-      <c r="T30" s="53"/>
-      <c r="U30" s="52">
+      <c r="S30" s="45"/>
+      <c r="T30" s="46"/>
+      <c r="U30" s="45">
         <f>AVERAGE(U4:U29)</f>
         <v>0</v>
       </c>
-      <c r="V30" s="52"/>
-      <c r="W30" s="53"/>
-      <c r="X30" s="52">
+      <c r="V30" s="45"/>
+      <c r="W30" s="46"/>
+      <c r="X30" s="45">
         <f>AVERAGE(X4:X29)</f>
         <v>0</v>
       </c>
-      <c r="Y30" s="52"/>
-      <c r="Z30" s="53"/>
-      <c r="AA30" s="52">
+      <c r="Y30" s="45"/>
+      <c r="Z30" s="46"/>
+      <c r="AA30" s="45">
         <f>AVERAGE(AA4:AA29)</f>
         <v>0</v>
       </c>
-      <c r="AB30" s="52"/>
-      <c r="AC30" s="53"/>
-      <c r="AD30" s="52">
+      <c r="AB30" s="45"/>
+      <c r="AC30" s="46"/>
+      <c r="AD30" s="45">
         <f>AVERAGE(AD4:AD29)</f>
         <v>0</v>
       </c>
-      <c r="AE30" s="52"/>
-      <c r="AF30" s="53"/>
-      <c r="AG30" s="52">
+      <c r="AE30" s="45"/>
+      <c r="AF30" s="46"/>
+      <c r="AG30" s="45">
         <f>AVERAGE(AG4:AG29)</f>
         <v>0</v>
       </c>
-      <c r="AH30" s="52"/>
-      <c r="AI30" s="53"/>
-      <c r="AJ30" s="52">
+      <c r="AH30" s="45"/>
+      <c r="AI30" s="46"/>
+      <c r="AJ30" s="45">
         <f>AVERAGE(AJ4:AJ29)</f>
         <v>0</v>
       </c>
-      <c r="AK30" s="52"/>
-      <c r="AL30" s="53"/>
-      <c r="AM30" s="52">
+      <c r="AK30" s="45"/>
+      <c r="AL30" s="46"/>
+      <c r="AM30" s="45">
         <f>AVERAGE(AM4:AM29)</f>
         <v>0</v>
       </c>
-      <c r="AN30" s="52"/>
-      <c r="AO30" s="53"/>
-      <c r="AP30" s="52">
+      <c r="AN30" s="45"/>
+      <c r="AO30" s="46"/>
+      <c r="AP30" s="45">
         <f>AVERAGE(AP4:AP29)</f>
         <v>0</v>
       </c>
-      <c r="AQ30" s="52"/>
-      <c r="AR30" s="53"/>
+      <c r="AQ30" s="45"/>
+      <c r="AR30" s="46"/>
     </row>
     <row r="31" spans="1:44" s="6" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B31" s="15"/>
@@ -5745,19 +5735,6 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="R30:T30"/>
-    <mergeCell ref="U30:W30"/>
-    <mergeCell ref="AM30:AO30"/>
-    <mergeCell ref="X30:Z30"/>
-    <mergeCell ref="AA30:AC30"/>
-    <mergeCell ref="AD30:AF30"/>
-    <mergeCell ref="AG30:AI30"/>
-    <mergeCell ref="AJ30:AL30"/>
-    <mergeCell ref="L2:N2"/>
-    <mergeCell ref="I2:K2"/>
-    <mergeCell ref="I30:K30"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="O30:Q30"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="AP2:AR2"/>
     <mergeCell ref="AP30:AR30"/>
@@ -5774,6 +5751,19 @@
     <mergeCell ref="F2:H2"/>
     <mergeCell ref="U2:W2"/>
     <mergeCell ref="R2:T2"/>
+    <mergeCell ref="L2:N2"/>
+    <mergeCell ref="I2:K2"/>
+    <mergeCell ref="I30:K30"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="O30:Q30"/>
+    <mergeCell ref="R30:T30"/>
+    <mergeCell ref="U30:W30"/>
+    <mergeCell ref="AM30:AO30"/>
+    <mergeCell ref="X30:Z30"/>
+    <mergeCell ref="AA30:AC30"/>
+    <mergeCell ref="AD30:AF30"/>
+    <mergeCell ref="AG30:AI30"/>
+    <mergeCell ref="AJ30:AL30"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/activity/M01A10/M01A10_Sinuosidad.xlsx
+++ b/activity/M01A10/M01A10_Sinuosidad.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.HCMC\activity\M01A10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BC1097A-C07D-40A2-8500-63C0B534CF33}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4771DAF5-17FB-47CF-938C-3B51B5971EA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{CB4A84EB-58A9-4828-A1EC-5E14AACD60D5}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{CB4A84EB-58A9-4828-A1EC-5E14AACD60D5}"/>
   </bookViews>
   <sheets>
     <sheet name="Calificacion" sheetId="12" r:id="rId1"/>
@@ -621,12 +621,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="2" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
       <protection locked="0"/>
@@ -677,11 +671,14 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -692,14 +689,17 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="2" fontId="6" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="2" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -805,11 +805,11 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Calificacion!$D$4</c:f>
+              <c:f>Calificacion!$F$4</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Calificación Instructor</c:v>
+                  <c:v>Calificación final</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -821,12 +821,7 @@
               </a:schemeClr>
             </a:solidFill>
             <a:ln>
-              <a:solidFill>
-                <a:schemeClr val="bg1">
-                  <a:lumMod val="95000"/>
-                  <a:alpha val="50000"/>
-                </a:schemeClr>
-              </a:solidFill>
+              <a:noFill/>
             </a:ln>
             <a:effectLst/>
           </c:spPr>
@@ -840,13 +835,13 @@
               <a:effectLst/>
             </c:spPr>
             <c:txPr>
-              <a:bodyPr rot="-5400000" spcFirstLastPara="1" vertOverflow="ellipsis" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
                 <a:spAutoFit/>
               </a:bodyPr>
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                  <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                     <a:solidFill>
                       <a:sysClr val="windowText" lastClr="000000"/>
                     </a:solidFill>
@@ -858,7 +853,6 @@
                 <a:endParaRPr lang="es-CO"/>
               </a:p>
             </c:txPr>
-            <c:dLblPos val="inBase"/>
             <c:showLegendKey val="0"/>
             <c:showVal val="1"/>
             <c:showCatName val="0"/>
@@ -868,7 +862,21 @@
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:showLeaderLines val="0"/>
+                <c15:showLeaderLines val="1"/>
+                <c15:leaderLines>
+                  <c:spPr>
+                    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="35000"/>
+                          <a:lumOff val="65000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:round/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c15:leaderLines>
               </c:ext>
             </c:extLst>
           </c:dLbls>
@@ -897,7 +905,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Calificacion!$D$5:$D$9</c:f>
+              <c:f>Calificacion!$F$5:$F$9</c:f>
               <c:numCache>
                 <c:formatCode>0.00</c:formatCode>
                 <c:ptCount val="5"/>
@@ -2116,20 +2124,20 @@
       </c>
     </row>
     <row r="2" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B2" s="43" t="s">
+      <c r="B2" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="43"/>
-      <c r="D2" s="43"/>
-      <c r="E2" s="43"/>
-      <c r="F2" s="43"/>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B3" s="44"/>
-      <c r="C3" s="44"/>
-      <c r="D3" s="44"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="44"/>
+      <c r="B3" s="42"/>
+      <c r="C3" s="42"/>
+      <c r="D3" s="42"/>
+      <c r="E3" s="42"/>
+      <c r="F3" s="42"/>
     </row>
     <row r="4" spans="2:6" ht="30.75" x14ac:dyDescent="0.45">
       <c r="B4" s="19" t="s">
@@ -2152,14 +2160,14 @@
       <c r="B5" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="C5" s="29">
+      <c r="C5" s="51">
         <v>5</v>
       </c>
       <c r="D5" s="22">
         <f>Detalle!C30*C5/5</f>
         <v>0</v>
       </c>
-      <c r="E5" s="29"/>
+      <c r="E5" s="51"/>
       <c r="F5" s="25">
         <f>AVERAGE(D5:E5)</f>
         <v>0</v>
@@ -2169,14 +2177,14 @@
       <c r="B6" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="C6" s="29">
+      <c r="C6" s="51">
         <v>5</v>
       </c>
       <c r="D6" s="22">
         <f>Detalle!F30*C6/5</f>
         <v>0</v>
       </c>
-      <c r="E6" s="29"/>
+      <c r="E6" s="51"/>
       <c r="F6" s="25">
         <f t="shared" ref="F6:F18" si="0">AVERAGE(D6:E6)</f>
         <v>0</v>
@@ -2186,14 +2194,14 @@
       <c r="B7" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="C7" s="29">
+      <c r="C7" s="51">
         <v>5</v>
       </c>
       <c r="D7" s="22">
         <f>Detalle!I30*C7/5</f>
         <v>0</v>
       </c>
-      <c r="E7" s="29"/>
+      <c r="E7" s="51"/>
       <c r="F7" s="25">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2203,14 +2211,14 @@
       <c r="B8" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="C8" s="29">
+      <c r="C8" s="51">
         <v>5</v>
       </c>
       <c r="D8" s="22">
         <f>Detalle!L30*C8/5</f>
         <v>0</v>
       </c>
-      <c r="E8" s="29"/>
+      <c r="E8" s="51"/>
       <c r="F8" s="25">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2220,14 +2228,14 @@
       <c r="B9" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="29">
+      <c r="C9" s="51">
         <v>5</v>
       </c>
       <c r="D9" s="22">
         <f>Detalle!O30*C9/5</f>
         <v>0</v>
       </c>
-      <c r="E9" s="29"/>
+      <c r="E9" s="51"/>
       <c r="F9" s="25">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2237,14 +2245,14 @@
       <c r="B10" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="C10" s="29">
+      <c r="C10" s="51">
         <v>5</v>
       </c>
       <c r="D10" s="22">
         <f>Detalle!R30*C10/5</f>
         <v>0</v>
       </c>
-      <c r="E10" s="29"/>
+      <c r="E10" s="51"/>
       <c r="F10" s="25">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2254,14 +2262,14 @@
       <c r="B11" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="C11" s="29">
+      <c r="C11" s="51">
         <v>5</v>
       </c>
       <c r="D11" s="22">
         <f>Detalle!U30*C11/5</f>
         <v>0</v>
       </c>
-      <c r="E11" s="29"/>
+      <c r="E11" s="51"/>
       <c r="F11" s="25">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2271,14 +2279,14 @@
       <c r="B12" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="C12" s="29">
+      <c r="C12" s="51">
         <v>5</v>
       </c>
       <c r="D12" s="22">
         <f>Detalle!X30*C12/5</f>
         <v>0</v>
       </c>
-      <c r="E12" s="29"/>
+      <c r="E12" s="51"/>
       <c r="F12" s="25">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2288,14 +2296,14 @@
       <c r="B13" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="C13" s="29">
+      <c r="C13" s="51">
         <v>5</v>
       </c>
       <c r="D13" s="22">
         <f>Detalle!AA30*C13/5</f>
         <v>0</v>
       </c>
-      <c r="E13" s="29"/>
+      <c r="E13" s="51"/>
       <c r="F13" s="25">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2305,14 +2313,14 @@
       <c r="B14" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="C14" s="29">
+      <c r="C14" s="51">
         <v>5</v>
       </c>
       <c r="D14" s="22">
         <f>Detalle!AD30*C14/5</f>
         <v>0</v>
       </c>
-      <c r="E14" s="29"/>
+      <c r="E14" s="51"/>
       <c r="F14" s="25">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2322,14 +2330,14 @@
       <c r="B15" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="C15" s="29">
+      <c r="C15" s="51">
         <v>5</v>
       </c>
       <c r="D15" s="22">
         <f>Detalle!AG30*C15/5</f>
         <v>0</v>
       </c>
-      <c r="E15" s="29"/>
+      <c r="E15" s="51"/>
       <c r="F15" s="25">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2339,14 +2347,14 @@
       <c r="B16" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="C16" s="29">
+      <c r="C16" s="51">
         <v>5</v>
       </c>
       <c r="D16" s="22">
         <f>Detalle!AJ30*C16/5</f>
         <v>0</v>
       </c>
-      <c r="E16" s="29"/>
+      <c r="E16" s="51"/>
       <c r="F16" s="25">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2356,14 +2364,14 @@
       <c r="B17" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="C17" s="29">
+      <c r="C17" s="51">
         <v>5</v>
       </c>
       <c r="D17" s="22">
         <f>Detalle!AM30*C17/5</f>
         <v>0</v>
       </c>
-      <c r="E17" s="29"/>
+      <c r="E17" s="51"/>
       <c r="F17" s="25">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2373,35 +2381,35 @@
       <c r="B18" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C18" s="30">
+      <c r="C18" s="52">
         <v>5</v>
       </c>
       <c r="D18" s="23">
         <f>Detalle!AP30*C18/5</f>
         <v>0</v>
       </c>
-      <c r="E18" s="30"/>
+      <c r="E18" s="52"/>
       <c r="F18" s="26">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="2:6" ht="15.4" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B19" s="52" t="str">
+      <c r="B19" s="43" t="str">
         <f>HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.HCMC/blob/main/activity/",F1,"/Readme.md"),_xlfn.CONCAT("Ir a actividad ",F1," en GitHub."))</f>
         <v>Ir a actividad M01A10 en GitHub.</v>
       </c>
-      <c r="C19" s="52"/>
-      <c r="D19" s="52"/>
-      <c r="E19" s="52"/>
-      <c r="F19" s="52"/>
+      <c r="C19" s="43"/>
+      <c r="D19" s="43"/>
+      <c r="E19" s="43"/>
+      <c r="F19" s="43"/>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B20" s="52"/>
-      <c r="C20" s="52"/>
-      <c r="D20" s="52"/>
-      <c r="E20" s="52"/>
-      <c r="F20" s="52"/>
+      <c r="B20" s="43"/>
+      <c r="C20" s="43"/>
+      <c r="D20" s="43"/>
+      <c r="E20" s="43"/>
+      <c r="F20" s="43"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B21" s="24"/>
@@ -2516,96 +2524,96 @@
     </row>
     <row r="2" spans="1:44" s="3" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A2" s="6"/>
-      <c r="B2" s="50" t="s">
+      <c r="B2" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="47" t="str">
+      <c r="C2" s="46" t="str">
         <f>Calificacion!$B5</f>
         <v>Grupo 1</v>
       </c>
-      <c r="D2" s="48"/>
-      <c r="E2" s="49"/>
-      <c r="F2" s="47" t="str">
+      <c r="D2" s="47"/>
+      <c r="E2" s="48"/>
+      <c r="F2" s="46" t="str">
         <f>Calificacion!$B6</f>
         <v>Grupo 2</v>
       </c>
-      <c r="G2" s="48"/>
-      <c r="H2" s="49"/>
-      <c r="I2" s="47" t="str">
+      <c r="G2" s="47"/>
+      <c r="H2" s="48"/>
+      <c r="I2" s="46" t="str">
         <f>Calificacion!$B7</f>
         <v>Grupo 3</v>
       </c>
-      <c r="J2" s="48"/>
-      <c r="K2" s="49"/>
-      <c r="L2" s="47" t="str">
+      <c r="J2" s="47"/>
+      <c r="K2" s="48"/>
+      <c r="L2" s="46" t="str">
         <f>Calificacion!$B8</f>
         <v>Grupo 4</v>
       </c>
-      <c r="M2" s="48"/>
-      <c r="N2" s="49"/>
-      <c r="O2" s="47" t="str">
+      <c r="M2" s="47"/>
+      <c r="N2" s="48"/>
+      <c r="O2" s="46" t="str">
         <f>Calificacion!$B9</f>
         <v>Grupo 5</v>
       </c>
-      <c r="P2" s="48"/>
-      <c r="Q2" s="49"/>
-      <c r="R2" s="47" t="str">
+      <c r="P2" s="47"/>
+      <c r="Q2" s="48"/>
+      <c r="R2" s="46" t="str">
         <f>Calificacion!$B10</f>
         <v>Grupo 6</v>
       </c>
-      <c r="S2" s="48"/>
-      <c r="T2" s="49"/>
-      <c r="U2" s="47" t="str">
+      <c r="S2" s="47"/>
+      <c r="T2" s="48"/>
+      <c r="U2" s="46" t="str">
         <f>Calificacion!$B11</f>
         <v>Grupo 7</v>
       </c>
-      <c r="V2" s="48"/>
-      <c r="W2" s="49"/>
-      <c r="X2" s="47" t="str">
+      <c r="V2" s="47"/>
+      <c r="W2" s="48"/>
+      <c r="X2" s="46" t="str">
         <f>Calificacion!$B12</f>
         <v>Grupo 8</v>
       </c>
-      <c r="Y2" s="48"/>
-      <c r="Z2" s="49"/>
-      <c r="AA2" s="47" t="str">
+      <c r="Y2" s="47"/>
+      <c r="Z2" s="48"/>
+      <c r="AA2" s="46" t="str">
         <f>Calificacion!$B13</f>
         <v>Grupo 9</v>
       </c>
-      <c r="AB2" s="48"/>
-      <c r="AC2" s="49"/>
-      <c r="AD2" s="47" t="str">
+      <c r="AB2" s="47"/>
+      <c r="AC2" s="48"/>
+      <c r="AD2" s="46" t="str">
         <f>Calificacion!$B14</f>
         <v>Grupo 10</v>
       </c>
-      <c r="AE2" s="48"/>
-      <c r="AF2" s="49"/>
-      <c r="AG2" s="47" t="str">
+      <c r="AE2" s="47"/>
+      <c r="AF2" s="48"/>
+      <c r="AG2" s="46" t="str">
         <f>Calificacion!$B15</f>
         <v>Grupo 11</v>
       </c>
-      <c r="AH2" s="48"/>
-      <c r="AI2" s="49"/>
-      <c r="AJ2" s="47" t="str">
+      <c r="AH2" s="47"/>
+      <c r="AI2" s="48"/>
+      <c r="AJ2" s="46" t="str">
         <f>Calificacion!$B16</f>
         <v>Grupo 12</v>
       </c>
-      <c r="AK2" s="48"/>
-      <c r="AL2" s="49"/>
-      <c r="AM2" s="47" t="str">
+      <c r="AK2" s="47"/>
+      <c r="AL2" s="48"/>
+      <c r="AM2" s="46" t="str">
         <f>Calificacion!$B17</f>
         <v>Grupo 13</v>
       </c>
-      <c r="AN2" s="48"/>
-      <c r="AO2" s="49"/>
-      <c r="AP2" s="47" t="str">
+      <c r="AN2" s="47"/>
+      <c r="AO2" s="48"/>
+      <c r="AP2" s="46" t="str">
         <f>Calificacion!$B18</f>
         <v>Grupo 14</v>
       </c>
-      <c r="AQ2" s="48"/>
-      <c r="AR2" s="49"/>
+      <c r="AQ2" s="47"/>
+      <c r="AR2" s="48"/>
     </row>
     <row r="3" spans="1:44" x14ac:dyDescent="0.45">
-      <c r="B3" s="51"/>
+      <c r="B3" s="45"/>
       <c r="C3" s="7" t="s">
         <v>1</v>
       </c>
@@ -2737,1381 +2745,1381 @@
       <c r="B4" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="C4" s="31">
-        <v>0</v>
-      </c>
-      <c r="D4" s="32"/>
-      <c r="E4" s="33"/>
-      <c r="F4" s="31">
-        <v>0</v>
-      </c>
-      <c r="G4" s="32"/>
-      <c r="H4" s="33"/>
-      <c r="I4" s="31">
-        <v>0</v>
-      </c>
-      <c r="J4" s="32"/>
-      <c r="K4" s="33"/>
-      <c r="L4" s="31">
-        <v>0</v>
-      </c>
-      <c r="M4" s="32"/>
-      <c r="N4" s="33"/>
-      <c r="O4" s="31">
-        <v>0</v>
-      </c>
-      <c r="P4" s="32"/>
-      <c r="Q4" s="33"/>
-      <c r="R4" s="31">
-        <v>0</v>
-      </c>
-      <c r="S4" s="32"/>
-      <c r="T4" s="33"/>
-      <c r="U4" s="31">
-        <v>0</v>
-      </c>
-      <c r="V4" s="32"/>
-      <c r="W4" s="33"/>
-      <c r="X4" s="31">
-        <v>0</v>
-      </c>
-      <c r="Y4" s="32"/>
-      <c r="Z4" s="33"/>
-      <c r="AA4" s="31">
-        <v>0</v>
-      </c>
-      <c r="AB4" s="32"/>
-      <c r="AC4" s="33"/>
-      <c r="AD4" s="31">
-        <v>0</v>
-      </c>
-      <c r="AE4" s="32"/>
-      <c r="AF4" s="33"/>
-      <c r="AG4" s="31">
-        <v>0</v>
-      </c>
-      <c r="AH4" s="32"/>
-      <c r="AI4" s="33"/>
-      <c r="AJ4" s="31">
-        <v>0</v>
-      </c>
-      <c r="AK4" s="32"/>
-      <c r="AL4" s="33"/>
-      <c r="AM4" s="31">
-        <v>0</v>
-      </c>
-      <c r="AN4" s="32"/>
-      <c r="AO4" s="33"/>
-      <c r="AP4" s="31">
-        <v>0</v>
-      </c>
-      <c r="AQ4" s="32"/>
-      <c r="AR4" s="33"/>
+      <c r="C4" s="29">
+        <v>0</v>
+      </c>
+      <c r="D4" s="30"/>
+      <c r="E4" s="31"/>
+      <c r="F4" s="29">
+        <v>0</v>
+      </c>
+      <c r="G4" s="30"/>
+      <c r="H4" s="31"/>
+      <c r="I4" s="29">
+        <v>0</v>
+      </c>
+      <c r="J4" s="30"/>
+      <c r="K4" s="31"/>
+      <c r="L4" s="29">
+        <v>0</v>
+      </c>
+      <c r="M4" s="30"/>
+      <c r="N4" s="31"/>
+      <c r="O4" s="29">
+        <v>0</v>
+      </c>
+      <c r="P4" s="30"/>
+      <c r="Q4" s="31"/>
+      <c r="R4" s="29">
+        <v>0</v>
+      </c>
+      <c r="S4" s="30"/>
+      <c r="T4" s="31"/>
+      <c r="U4" s="29">
+        <v>0</v>
+      </c>
+      <c r="V4" s="30"/>
+      <c r="W4" s="31"/>
+      <c r="X4" s="29">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="30"/>
+      <c r="Z4" s="31"/>
+      <c r="AA4" s="29">
+        <v>0</v>
+      </c>
+      <c r="AB4" s="30"/>
+      <c r="AC4" s="31"/>
+      <c r="AD4" s="29">
+        <v>0</v>
+      </c>
+      <c r="AE4" s="30"/>
+      <c r="AF4" s="31"/>
+      <c r="AG4" s="29">
+        <v>0</v>
+      </c>
+      <c r="AH4" s="30"/>
+      <c r="AI4" s="31"/>
+      <c r="AJ4" s="29">
+        <v>0</v>
+      </c>
+      <c r="AK4" s="30"/>
+      <c r="AL4" s="31"/>
+      <c r="AM4" s="29">
+        <v>0</v>
+      </c>
+      <c r="AN4" s="30"/>
+      <c r="AO4" s="31"/>
+      <c r="AP4" s="29">
+        <v>0</v>
+      </c>
+      <c r="AQ4" s="30"/>
+      <c r="AR4" s="31"/>
     </row>
     <row r="5" spans="1:44" ht="30.75" x14ac:dyDescent="0.45">
       <c r="B5" s="17" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="31"/>
-      <c r="D5" s="32"/>
-      <c r="E5" s="33"/>
-      <c r="F5" s="31"/>
-      <c r="G5" s="32"/>
-      <c r="H5" s="33"/>
-      <c r="I5" s="31"/>
-      <c r="J5" s="32"/>
-      <c r="K5" s="33"/>
-      <c r="L5" s="31"/>
-      <c r="M5" s="32"/>
-      <c r="N5" s="33"/>
-      <c r="O5" s="31"/>
-      <c r="P5" s="32"/>
-      <c r="Q5" s="33"/>
-      <c r="R5" s="31"/>
-      <c r="S5" s="32"/>
-      <c r="T5" s="33"/>
-      <c r="U5" s="31"/>
-      <c r="V5" s="32"/>
-      <c r="W5" s="33"/>
-      <c r="X5" s="31"/>
-      <c r="Y5" s="32"/>
-      <c r="Z5" s="33"/>
-      <c r="AA5" s="31"/>
-      <c r="AB5" s="32"/>
-      <c r="AC5" s="33"/>
-      <c r="AD5" s="31"/>
-      <c r="AE5" s="32"/>
-      <c r="AF5" s="33"/>
-      <c r="AG5" s="31"/>
-      <c r="AH5" s="32"/>
-      <c r="AI5" s="33"/>
-      <c r="AJ5" s="31"/>
-      <c r="AK5" s="32"/>
-      <c r="AL5" s="33"/>
-      <c r="AM5" s="31"/>
-      <c r="AN5" s="32"/>
-      <c r="AO5" s="33"/>
-      <c r="AP5" s="31"/>
-      <c r="AQ5" s="32"/>
-      <c r="AR5" s="33"/>
+      <c r="C5" s="29"/>
+      <c r="D5" s="30"/>
+      <c r="E5" s="31"/>
+      <c r="F5" s="29"/>
+      <c r="G5" s="30"/>
+      <c r="H5" s="31"/>
+      <c r="I5" s="29"/>
+      <c r="J5" s="30"/>
+      <c r="K5" s="31"/>
+      <c r="L5" s="29"/>
+      <c r="M5" s="30"/>
+      <c r="N5" s="31"/>
+      <c r="O5" s="29"/>
+      <c r="P5" s="30"/>
+      <c r="Q5" s="31"/>
+      <c r="R5" s="29"/>
+      <c r="S5" s="30"/>
+      <c r="T5" s="31"/>
+      <c r="U5" s="29"/>
+      <c r="V5" s="30"/>
+      <c r="W5" s="31"/>
+      <c r="X5" s="29"/>
+      <c r="Y5" s="30"/>
+      <c r="Z5" s="31"/>
+      <c r="AA5" s="29"/>
+      <c r="AB5" s="30"/>
+      <c r="AC5" s="31"/>
+      <c r="AD5" s="29"/>
+      <c r="AE5" s="30"/>
+      <c r="AF5" s="31"/>
+      <c r="AG5" s="29"/>
+      <c r="AH5" s="30"/>
+      <c r="AI5" s="31"/>
+      <c r="AJ5" s="29"/>
+      <c r="AK5" s="30"/>
+      <c r="AL5" s="31"/>
+      <c r="AM5" s="29"/>
+      <c r="AN5" s="30"/>
+      <c r="AO5" s="31"/>
+      <c r="AP5" s="29"/>
+      <c r="AQ5" s="30"/>
+      <c r="AR5" s="31"/>
     </row>
     <row r="6" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B6" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="31"/>
-      <c r="D6" s="32"/>
-      <c r="E6" s="33"/>
-      <c r="F6" s="31"/>
-      <c r="G6" s="32"/>
-      <c r="H6" s="33"/>
-      <c r="I6" s="31"/>
-      <c r="J6" s="32"/>
-      <c r="K6" s="33"/>
-      <c r="L6" s="31"/>
-      <c r="M6" s="32"/>
-      <c r="N6" s="33"/>
-      <c r="O6" s="31"/>
-      <c r="P6" s="32"/>
-      <c r="Q6" s="33"/>
-      <c r="R6" s="31"/>
-      <c r="S6" s="32"/>
-      <c r="T6" s="33"/>
-      <c r="U6" s="31"/>
-      <c r="V6" s="32"/>
-      <c r="W6" s="33"/>
-      <c r="X6" s="31"/>
-      <c r="Y6" s="32"/>
-      <c r="Z6" s="33"/>
-      <c r="AA6" s="31"/>
-      <c r="AB6" s="32"/>
-      <c r="AC6" s="33"/>
-      <c r="AD6" s="31"/>
-      <c r="AE6" s="32"/>
-      <c r="AF6" s="33"/>
-      <c r="AG6" s="31"/>
-      <c r="AH6" s="32"/>
-      <c r="AI6" s="33"/>
-      <c r="AJ6" s="31"/>
-      <c r="AK6" s="32"/>
-      <c r="AL6" s="33"/>
-      <c r="AM6" s="31"/>
-      <c r="AN6" s="32"/>
-      <c r="AO6" s="33"/>
-      <c r="AP6" s="31"/>
-      <c r="AQ6" s="32"/>
-      <c r="AR6" s="33"/>
+      <c r="C6" s="29"/>
+      <c r="D6" s="30"/>
+      <c r="E6" s="31"/>
+      <c r="F6" s="29"/>
+      <c r="G6" s="30"/>
+      <c r="H6" s="31"/>
+      <c r="I6" s="29"/>
+      <c r="J6" s="30"/>
+      <c r="K6" s="31"/>
+      <c r="L6" s="29"/>
+      <c r="M6" s="30"/>
+      <c r="N6" s="31"/>
+      <c r="O6" s="29"/>
+      <c r="P6" s="30"/>
+      <c r="Q6" s="31"/>
+      <c r="R6" s="29"/>
+      <c r="S6" s="30"/>
+      <c r="T6" s="31"/>
+      <c r="U6" s="29"/>
+      <c r="V6" s="30"/>
+      <c r="W6" s="31"/>
+      <c r="X6" s="29"/>
+      <c r="Y6" s="30"/>
+      <c r="Z6" s="31"/>
+      <c r="AA6" s="29"/>
+      <c r="AB6" s="30"/>
+      <c r="AC6" s="31"/>
+      <c r="AD6" s="29"/>
+      <c r="AE6" s="30"/>
+      <c r="AF6" s="31"/>
+      <c r="AG6" s="29"/>
+      <c r="AH6" s="30"/>
+      <c r="AI6" s="31"/>
+      <c r="AJ6" s="29"/>
+      <c r="AK6" s="30"/>
+      <c r="AL6" s="31"/>
+      <c r="AM6" s="29"/>
+      <c r="AN6" s="30"/>
+      <c r="AO6" s="31"/>
+      <c r="AP6" s="29"/>
+      <c r="AQ6" s="30"/>
+      <c r="AR6" s="31"/>
     </row>
     <row r="7" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B7" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="C7" s="31"/>
-      <c r="D7" s="34"/>
-      <c r="E7" s="33"/>
-      <c r="F7" s="31"/>
-      <c r="G7" s="34"/>
-      <c r="H7" s="33"/>
-      <c r="I7" s="31"/>
-      <c r="J7" s="34"/>
-      <c r="K7" s="33"/>
-      <c r="L7" s="31"/>
-      <c r="M7" s="34"/>
-      <c r="N7" s="33"/>
-      <c r="O7" s="31"/>
-      <c r="P7" s="34"/>
-      <c r="Q7" s="33"/>
-      <c r="R7" s="31"/>
-      <c r="S7" s="34"/>
-      <c r="T7" s="33"/>
-      <c r="U7" s="31"/>
-      <c r="V7" s="34"/>
-      <c r="W7" s="33"/>
-      <c r="X7" s="31"/>
-      <c r="Y7" s="34"/>
-      <c r="Z7" s="33"/>
-      <c r="AA7" s="31"/>
-      <c r="AB7" s="34"/>
-      <c r="AC7" s="33"/>
-      <c r="AD7" s="31"/>
-      <c r="AE7" s="34"/>
-      <c r="AF7" s="33"/>
-      <c r="AG7" s="31"/>
-      <c r="AH7" s="34"/>
-      <c r="AI7" s="33"/>
-      <c r="AJ7" s="31"/>
-      <c r="AK7" s="34"/>
-      <c r="AL7" s="33"/>
-      <c r="AM7" s="31"/>
-      <c r="AN7" s="34"/>
-      <c r="AO7" s="33"/>
-      <c r="AP7" s="31"/>
-      <c r="AQ7" s="34"/>
-      <c r="AR7" s="33"/>
+      <c r="C7" s="29"/>
+      <c r="D7" s="32"/>
+      <c r="E7" s="31"/>
+      <c r="F7" s="29"/>
+      <c r="G7" s="32"/>
+      <c r="H7" s="31"/>
+      <c r="I7" s="29"/>
+      <c r="J7" s="32"/>
+      <c r="K7" s="31"/>
+      <c r="L7" s="29"/>
+      <c r="M7" s="32"/>
+      <c r="N7" s="31"/>
+      <c r="O7" s="29"/>
+      <c r="P7" s="32"/>
+      <c r="Q7" s="31"/>
+      <c r="R7" s="29"/>
+      <c r="S7" s="32"/>
+      <c r="T7" s="31"/>
+      <c r="U7" s="29"/>
+      <c r="V7" s="32"/>
+      <c r="W7" s="31"/>
+      <c r="X7" s="29"/>
+      <c r="Y7" s="32"/>
+      <c r="Z7" s="31"/>
+      <c r="AA7" s="29"/>
+      <c r="AB7" s="32"/>
+      <c r="AC7" s="31"/>
+      <c r="AD7" s="29"/>
+      <c r="AE7" s="32"/>
+      <c r="AF7" s="31"/>
+      <c r="AG7" s="29"/>
+      <c r="AH7" s="32"/>
+      <c r="AI7" s="31"/>
+      <c r="AJ7" s="29"/>
+      <c r="AK7" s="32"/>
+      <c r="AL7" s="31"/>
+      <c r="AM7" s="29"/>
+      <c r="AN7" s="32"/>
+      <c r="AO7" s="31"/>
+      <c r="AP7" s="29"/>
+      <c r="AQ7" s="32"/>
+      <c r="AR7" s="31"/>
     </row>
     <row r="8" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B8" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="31"/>
-      <c r="D8" s="34"/>
-      <c r="E8" s="33"/>
-      <c r="F8" s="31"/>
-      <c r="G8" s="34"/>
-      <c r="H8" s="33"/>
-      <c r="I8" s="31"/>
-      <c r="J8" s="34"/>
-      <c r="K8" s="33"/>
-      <c r="L8" s="31"/>
-      <c r="M8" s="34"/>
-      <c r="N8" s="33"/>
-      <c r="O8" s="31"/>
-      <c r="P8" s="34"/>
-      <c r="Q8" s="33"/>
-      <c r="R8" s="31"/>
-      <c r="S8" s="34"/>
-      <c r="T8" s="33"/>
-      <c r="U8" s="31"/>
-      <c r="V8" s="34"/>
-      <c r="W8" s="33"/>
-      <c r="X8" s="31"/>
-      <c r="Y8" s="34"/>
-      <c r="Z8" s="33"/>
-      <c r="AA8" s="31"/>
-      <c r="AB8" s="34"/>
-      <c r="AC8" s="33"/>
-      <c r="AD8" s="31"/>
-      <c r="AE8" s="34"/>
-      <c r="AF8" s="33"/>
-      <c r="AG8" s="31"/>
-      <c r="AH8" s="34"/>
-      <c r="AI8" s="33"/>
-      <c r="AJ8" s="31"/>
-      <c r="AK8" s="34"/>
-      <c r="AL8" s="33"/>
-      <c r="AM8" s="31"/>
-      <c r="AN8" s="34"/>
-      <c r="AO8" s="33"/>
-      <c r="AP8" s="31"/>
-      <c r="AQ8" s="34"/>
-      <c r="AR8" s="33"/>
+      <c r="C8" s="29"/>
+      <c r="D8" s="32"/>
+      <c r="E8" s="31"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="32"/>
+      <c r="H8" s="31"/>
+      <c r="I8" s="29"/>
+      <c r="J8" s="32"/>
+      <c r="K8" s="31"/>
+      <c r="L8" s="29"/>
+      <c r="M8" s="32"/>
+      <c r="N8" s="31"/>
+      <c r="O8" s="29"/>
+      <c r="P8" s="32"/>
+      <c r="Q8" s="31"/>
+      <c r="R8" s="29"/>
+      <c r="S8" s="32"/>
+      <c r="T8" s="31"/>
+      <c r="U8" s="29"/>
+      <c r="V8" s="32"/>
+      <c r="W8" s="31"/>
+      <c r="X8" s="29"/>
+      <c r="Y8" s="32"/>
+      <c r="Z8" s="31"/>
+      <c r="AA8" s="29"/>
+      <c r="AB8" s="32"/>
+      <c r="AC8" s="31"/>
+      <c r="AD8" s="29"/>
+      <c r="AE8" s="32"/>
+      <c r="AF8" s="31"/>
+      <c r="AG8" s="29"/>
+      <c r="AH8" s="32"/>
+      <c r="AI8" s="31"/>
+      <c r="AJ8" s="29"/>
+      <c r="AK8" s="32"/>
+      <c r="AL8" s="31"/>
+      <c r="AM8" s="29"/>
+      <c r="AN8" s="32"/>
+      <c r="AO8" s="31"/>
+      <c r="AP8" s="29"/>
+      <c r="AQ8" s="32"/>
+      <c r="AR8" s="31"/>
     </row>
     <row r="9" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B9" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="31"/>
-      <c r="D9" s="32"/>
-      <c r="E9" s="33"/>
-      <c r="F9" s="31"/>
-      <c r="G9" s="32"/>
-      <c r="H9" s="33"/>
-      <c r="I9" s="31"/>
-      <c r="J9" s="32"/>
-      <c r="K9" s="33"/>
-      <c r="L9" s="31"/>
-      <c r="M9" s="32"/>
-      <c r="N9" s="33"/>
-      <c r="O9" s="31"/>
-      <c r="P9" s="32"/>
-      <c r="Q9" s="33"/>
-      <c r="R9" s="31"/>
-      <c r="S9" s="32"/>
-      <c r="T9" s="33"/>
-      <c r="U9" s="31"/>
-      <c r="V9" s="32"/>
-      <c r="W9" s="33"/>
-      <c r="X9" s="31"/>
-      <c r="Y9" s="32"/>
-      <c r="Z9" s="33"/>
-      <c r="AA9" s="31"/>
-      <c r="AB9" s="32"/>
-      <c r="AC9" s="33"/>
-      <c r="AD9" s="31"/>
-      <c r="AE9" s="32"/>
-      <c r="AF9" s="33"/>
-      <c r="AG9" s="31"/>
-      <c r="AH9" s="32"/>
-      <c r="AI9" s="33"/>
-      <c r="AJ9" s="31"/>
-      <c r="AK9" s="32"/>
-      <c r="AL9" s="33"/>
-      <c r="AM9" s="31"/>
-      <c r="AN9" s="32"/>
-      <c r="AO9" s="33"/>
-      <c r="AP9" s="31"/>
-      <c r="AQ9" s="32"/>
-      <c r="AR9" s="33"/>
+      <c r="C9" s="29"/>
+      <c r="D9" s="30"/>
+      <c r="E9" s="31"/>
+      <c r="F9" s="29"/>
+      <c r="G9" s="30"/>
+      <c r="H9" s="31"/>
+      <c r="I9" s="29"/>
+      <c r="J9" s="30"/>
+      <c r="K9" s="31"/>
+      <c r="L9" s="29"/>
+      <c r="M9" s="30"/>
+      <c r="N9" s="31"/>
+      <c r="O9" s="29"/>
+      <c r="P9" s="30"/>
+      <c r="Q9" s="31"/>
+      <c r="R9" s="29"/>
+      <c r="S9" s="30"/>
+      <c r="T9" s="31"/>
+      <c r="U9" s="29"/>
+      <c r="V9" s="30"/>
+      <c r="W9" s="31"/>
+      <c r="X9" s="29"/>
+      <c r="Y9" s="30"/>
+      <c r="Z9" s="31"/>
+      <c r="AA9" s="29"/>
+      <c r="AB9" s="30"/>
+      <c r="AC9" s="31"/>
+      <c r="AD9" s="29"/>
+      <c r="AE9" s="30"/>
+      <c r="AF9" s="31"/>
+      <c r="AG9" s="29"/>
+      <c r="AH9" s="30"/>
+      <c r="AI9" s="31"/>
+      <c r="AJ9" s="29"/>
+      <c r="AK9" s="30"/>
+      <c r="AL9" s="31"/>
+      <c r="AM9" s="29"/>
+      <c r="AN9" s="30"/>
+      <c r="AO9" s="31"/>
+      <c r="AP9" s="29"/>
+      <c r="AQ9" s="30"/>
+      <c r="AR9" s="31"/>
     </row>
     <row r="10" spans="1:44" ht="30.75" x14ac:dyDescent="0.45">
       <c r="B10" s="17" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="31"/>
-      <c r="D10" s="32"/>
-      <c r="E10" s="33"/>
-      <c r="F10" s="31"/>
-      <c r="G10" s="32"/>
-      <c r="H10" s="33"/>
-      <c r="I10" s="31"/>
-      <c r="J10" s="32"/>
-      <c r="K10" s="33"/>
-      <c r="L10" s="31"/>
-      <c r="M10" s="32"/>
-      <c r="N10" s="33"/>
-      <c r="O10" s="31"/>
-      <c r="P10" s="32"/>
-      <c r="Q10" s="33"/>
-      <c r="R10" s="31"/>
-      <c r="S10" s="32"/>
-      <c r="T10" s="33"/>
-      <c r="U10" s="31"/>
-      <c r="V10" s="32"/>
-      <c r="W10" s="33"/>
-      <c r="X10" s="31"/>
-      <c r="Y10" s="32"/>
-      <c r="Z10" s="33"/>
-      <c r="AA10" s="31"/>
-      <c r="AB10" s="32"/>
-      <c r="AC10" s="33"/>
-      <c r="AD10" s="31"/>
-      <c r="AE10" s="32"/>
-      <c r="AF10" s="33"/>
-      <c r="AG10" s="31"/>
-      <c r="AH10" s="32"/>
-      <c r="AI10" s="33"/>
-      <c r="AJ10" s="31"/>
-      <c r="AK10" s="32"/>
-      <c r="AL10" s="33"/>
-      <c r="AM10" s="31"/>
-      <c r="AN10" s="32"/>
-      <c r="AO10" s="33"/>
-      <c r="AP10" s="31"/>
-      <c r="AQ10" s="32"/>
-      <c r="AR10" s="33"/>
+      <c r="C10" s="29"/>
+      <c r="D10" s="30"/>
+      <c r="E10" s="31"/>
+      <c r="F10" s="29"/>
+      <c r="G10" s="30"/>
+      <c r="H10" s="31"/>
+      <c r="I10" s="29"/>
+      <c r="J10" s="30"/>
+      <c r="K10" s="31"/>
+      <c r="L10" s="29"/>
+      <c r="M10" s="30"/>
+      <c r="N10" s="31"/>
+      <c r="O10" s="29"/>
+      <c r="P10" s="30"/>
+      <c r="Q10" s="31"/>
+      <c r="R10" s="29"/>
+      <c r="S10" s="30"/>
+      <c r="T10" s="31"/>
+      <c r="U10" s="29"/>
+      <c r="V10" s="30"/>
+      <c r="W10" s="31"/>
+      <c r="X10" s="29"/>
+      <c r="Y10" s="30"/>
+      <c r="Z10" s="31"/>
+      <c r="AA10" s="29"/>
+      <c r="AB10" s="30"/>
+      <c r="AC10" s="31"/>
+      <c r="AD10" s="29"/>
+      <c r="AE10" s="30"/>
+      <c r="AF10" s="31"/>
+      <c r="AG10" s="29"/>
+      <c r="AH10" s="30"/>
+      <c r="AI10" s="31"/>
+      <c r="AJ10" s="29"/>
+      <c r="AK10" s="30"/>
+      <c r="AL10" s="31"/>
+      <c r="AM10" s="29"/>
+      <c r="AN10" s="30"/>
+      <c r="AO10" s="31"/>
+      <c r="AP10" s="29"/>
+      <c r="AQ10" s="30"/>
+      <c r="AR10" s="31"/>
     </row>
     <row r="11" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B11" s="18" t="s">
         <v>42</v>
       </c>
-      <c r="C11" s="31"/>
-      <c r="D11" s="32"/>
-      <c r="E11" s="33"/>
-      <c r="F11" s="31"/>
-      <c r="G11" s="32"/>
-      <c r="H11" s="33"/>
-      <c r="I11" s="31"/>
-      <c r="J11" s="32"/>
-      <c r="K11" s="33"/>
-      <c r="L11" s="31"/>
-      <c r="M11" s="32"/>
-      <c r="N11" s="33"/>
-      <c r="O11" s="31"/>
-      <c r="P11" s="32"/>
-      <c r="Q11" s="33"/>
-      <c r="R11" s="31"/>
-      <c r="S11" s="32"/>
-      <c r="T11" s="33"/>
-      <c r="U11" s="31"/>
-      <c r="V11" s="32"/>
-      <c r="W11" s="33"/>
-      <c r="X11" s="31"/>
-      <c r="Y11" s="32"/>
-      <c r="Z11" s="33"/>
-      <c r="AA11" s="31"/>
-      <c r="AB11" s="32"/>
-      <c r="AC11" s="33"/>
-      <c r="AD11" s="31"/>
-      <c r="AE11" s="32"/>
-      <c r="AF11" s="33"/>
-      <c r="AG11" s="31"/>
-      <c r="AH11" s="32"/>
-      <c r="AI11" s="33"/>
-      <c r="AJ11" s="31"/>
-      <c r="AK11" s="32"/>
-      <c r="AL11" s="33"/>
-      <c r="AM11" s="31"/>
-      <c r="AN11" s="32"/>
-      <c r="AO11" s="33"/>
-      <c r="AP11" s="31"/>
-      <c r="AQ11" s="32"/>
-      <c r="AR11" s="33"/>
+      <c r="C11" s="29"/>
+      <c r="D11" s="30"/>
+      <c r="E11" s="31"/>
+      <c r="F11" s="29"/>
+      <c r="G11" s="30"/>
+      <c r="H11" s="31"/>
+      <c r="I11" s="29"/>
+      <c r="J11" s="30"/>
+      <c r="K11" s="31"/>
+      <c r="L11" s="29"/>
+      <c r="M11" s="30"/>
+      <c r="N11" s="31"/>
+      <c r="O11" s="29"/>
+      <c r="P11" s="30"/>
+      <c r="Q11" s="31"/>
+      <c r="R11" s="29"/>
+      <c r="S11" s="30"/>
+      <c r="T11" s="31"/>
+      <c r="U11" s="29"/>
+      <c r="V11" s="30"/>
+      <c r="W11" s="31"/>
+      <c r="X11" s="29"/>
+      <c r="Y11" s="30"/>
+      <c r="Z11" s="31"/>
+      <c r="AA11" s="29"/>
+      <c r="AB11" s="30"/>
+      <c r="AC11" s="31"/>
+      <c r="AD11" s="29"/>
+      <c r="AE11" s="30"/>
+      <c r="AF11" s="31"/>
+      <c r="AG11" s="29"/>
+      <c r="AH11" s="30"/>
+      <c r="AI11" s="31"/>
+      <c r="AJ11" s="29"/>
+      <c r="AK11" s="30"/>
+      <c r="AL11" s="31"/>
+      <c r="AM11" s="29"/>
+      <c r="AN11" s="30"/>
+      <c r="AO11" s="31"/>
+      <c r="AP11" s="29"/>
+      <c r="AQ11" s="30"/>
+      <c r="AR11" s="31"/>
     </row>
     <row r="12" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B12" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="31"/>
-      <c r="D12" s="32"/>
-      <c r="E12" s="33"/>
-      <c r="F12" s="31"/>
-      <c r="G12" s="32"/>
-      <c r="H12" s="33"/>
-      <c r="I12" s="31"/>
-      <c r="J12" s="32"/>
-      <c r="K12" s="33"/>
-      <c r="L12" s="31"/>
-      <c r="M12" s="32"/>
-      <c r="N12" s="33"/>
-      <c r="O12" s="31"/>
-      <c r="P12" s="32"/>
-      <c r="Q12" s="33"/>
-      <c r="R12" s="31"/>
-      <c r="S12" s="32"/>
-      <c r="T12" s="33"/>
-      <c r="U12" s="31"/>
-      <c r="V12" s="32"/>
-      <c r="W12" s="33"/>
-      <c r="X12" s="31"/>
-      <c r="Y12" s="32"/>
-      <c r="Z12" s="33"/>
-      <c r="AA12" s="31"/>
-      <c r="AB12" s="32"/>
-      <c r="AC12" s="33"/>
-      <c r="AD12" s="31"/>
-      <c r="AE12" s="32"/>
-      <c r="AF12" s="33"/>
-      <c r="AG12" s="31"/>
-      <c r="AH12" s="32"/>
-      <c r="AI12" s="33"/>
-      <c r="AJ12" s="31"/>
-      <c r="AK12" s="32"/>
-      <c r="AL12" s="33"/>
-      <c r="AM12" s="31"/>
-      <c r="AN12" s="32"/>
-      <c r="AO12" s="33"/>
-      <c r="AP12" s="31"/>
-      <c r="AQ12" s="32"/>
-      <c r="AR12" s="33"/>
+      <c r="C12" s="29"/>
+      <c r="D12" s="30"/>
+      <c r="E12" s="31"/>
+      <c r="F12" s="29"/>
+      <c r="G12" s="30"/>
+      <c r="H12" s="31"/>
+      <c r="I12" s="29"/>
+      <c r="J12" s="30"/>
+      <c r="K12" s="31"/>
+      <c r="L12" s="29"/>
+      <c r="M12" s="30"/>
+      <c r="N12" s="31"/>
+      <c r="O12" s="29"/>
+      <c r="P12" s="30"/>
+      <c r="Q12" s="31"/>
+      <c r="R12" s="29"/>
+      <c r="S12" s="30"/>
+      <c r="T12" s="31"/>
+      <c r="U12" s="29"/>
+      <c r="V12" s="30"/>
+      <c r="W12" s="31"/>
+      <c r="X12" s="29"/>
+      <c r="Y12" s="30"/>
+      <c r="Z12" s="31"/>
+      <c r="AA12" s="29"/>
+      <c r="AB12" s="30"/>
+      <c r="AC12" s="31"/>
+      <c r="AD12" s="29"/>
+      <c r="AE12" s="30"/>
+      <c r="AF12" s="31"/>
+      <c r="AG12" s="29"/>
+      <c r="AH12" s="30"/>
+      <c r="AI12" s="31"/>
+      <c r="AJ12" s="29"/>
+      <c r="AK12" s="30"/>
+      <c r="AL12" s="31"/>
+      <c r="AM12" s="29"/>
+      <c r="AN12" s="30"/>
+      <c r="AO12" s="31"/>
+      <c r="AP12" s="29"/>
+      <c r="AQ12" s="30"/>
+      <c r="AR12" s="31"/>
     </row>
     <row r="13" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B13" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="C13" s="31"/>
-      <c r="D13" s="32"/>
-      <c r="E13" s="33"/>
-      <c r="F13" s="31"/>
-      <c r="G13" s="32"/>
-      <c r="H13" s="33"/>
-      <c r="I13" s="31"/>
-      <c r="J13" s="32"/>
-      <c r="K13" s="33"/>
-      <c r="L13" s="31"/>
-      <c r="M13" s="32"/>
-      <c r="N13" s="33"/>
-      <c r="O13" s="31"/>
-      <c r="P13" s="32"/>
-      <c r="Q13" s="33"/>
-      <c r="R13" s="31"/>
-      <c r="S13" s="32"/>
-      <c r="T13" s="33"/>
-      <c r="U13" s="31"/>
-      <c r="V13" s="32"/>
-      <c r="W13" s="33"/>
-      <c r="X13" s="31"/>
-      <c r="Y13" s="32"/>
-      <c r="Z13" s="33"/>
-      <c r="AA13" s="31"/>
-      <c r="AB13" s="32"/>
-      <c r="AC13" s="33"/>
-      <c r="AD13" s="31"/>
-      <c r="AE13" s="32"/>
-      <c r="AF13" s="33"/>
-      <c r="AG13" s="31"/>
-      <c r="AH13" s="32"/>
-      <c r="AI13" s="33"/>
-      <c r="AJ13" s="31"/>
-      <c r="AK13" s="32"/>
-      <c r="AL13" s="33"/>
-      <c r="AM13" s="31"/>
-      <c r="AN13" s="32"/>
-      <c r="AO13" s="33"/>
-      <c r="AP13" s="31"/>
-      <c r="AQ13" s="32"/>
-      <c r="AR13" s="33"/>
+      <c r="C13" s="29"/>
+      <c r="D13" s="30"/>
+      <c r="E13" s="31"/>
+      <c r="F13" s="29"/>
+      <c r="G13" s="30"/>
+      <c r="H13" s="31"/>
+      <c r="I13" s="29"/>
+      <c r="J13" s="30"/>
+      <c r="K13" s="31"/>
+      <c r="L13" s="29"/>
+      <c r="M13" s="30"/>
+      <c r="N13" s="31"/>
+      <c r="O13" s="29"/>
+      <c r="P13" s="30"/>
+      <c r="Q13" s="31"/>
+      <c r="R13" s="29"/>
+      <c r="S13" s="30"/>
+      <c r="T13" s="31"/>
+      <c r="U13" s="29"/>
+      <c r="V13" s="30"/>
+      <c r="W13" s="31"/>
+      <c r="X13" s="29"/>
+      <c r="Y13" s="30"/>
+      <c r="Z13" s="31"/>
+      <c r="AA13" s="29"/>
+      <c r="AB13" s="30"/>
+      <c r="AC13" s="31"/>
+      <c r="AD13" s="29"/>
+      <c r="AE13" s="30"/>
+      <c r="AF13" s="31"/>
+      <c r="AG13" s="29"/>
+      <c r="AH13" s="30"/>
+      <c r="AI13" s="31"/>
+      <c r="AJ13" s="29"/>
+      <c r="AK13" s="30"/>
+      <c r="AL13" s="31"/>
+      <c r="AM13" s="29"/>
+      <c r="AN13" s="30"/>
+      <c r="AO13" s="31"/>
+      <c r="AP13" s="29"/>
+      <c r="AQ13" s="30"/>
+      <c r="AR13" s="31"/>
     </row>
     <row r="14" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B14" s="18" t="s">
         <v>13</v>
       </c>
-      <c r="C14" s="31"/>
-      <c r="D14" s="34"/>
-      <c r="E14" s="33"/>
-      <c r="F14" s="31"/>
-      <c r="G14" s="34"/>
-      <c r="H14" s="33"/>
-      <c r="I14" s="31"/>
-      <c r="J14" s="34"/>
-      <c r="K14" s="33"/>
-      <c r="L14" s="31"/>
-      <c r="M14" s="34"/>
-      <c r="N14" s="33"/>
-      <c r="O14" s="31"/>
-      <c r="P14" s="34"/>
-      <c r="Q14" s="33"/>
-      <c r="R14" s="31"/>
-      <c r="S14" s="34"/>
-      <c r="T14" s="33"/>
-      <c r="U14" s="31"/>
-      <c r="V14" s="34"/>
-      <c r="W14" s="33"/>
-      <c r="X14" s="31"/>
-      <c r="Y14" s="34"/>
-      <c r="Z14" s="33"/>
-      <c r="AA14" s="31"/>
-      <c r="AB14" s="34"/>
-      <c r="AC14" s="33"/>
-      <c r="AD14" s="31"/>
-      <c r="AE14" s="34"/>
-      <c r="AF14" s="33"/>
-      <c r="AG14" s="31"/>
-      <c r="AH14" s="34"/>
-      <c r="AI14" s="33"/>
-      <c r="AJ14" s="31"/>
-      <c r="AK14" s="34"/>
-      <c r="AL14" s="33"/>
-      <c r="AM14" s="31"/>
-      <c r="AN14" s="34"/>
-      <c r="AO14" s="33"/>
-      <c r="AP14" s="31"/>
-      <c r="AQ14" s="34"/>
-      <c r="AR14" s="33"/>
+      <c r="C14" s="29"/>
+      <c r="D14" s="32"/>
+      <c r="E14" s="31"/>
+      <c r="F14" s="29"/>
+      <c r="G14" s="32"/>
+      <c r="H14" s="31"/>
+      <c r="I14" s="29"/>
+      <c r="J14" s="32"/>
+      <c r="K14" s="31"/>
+      <c r="L14" s="29"/>
+      <c r="M14" s="32"/>
+      <c r="N14" s="31"/>
+      <c r="O14" s="29"/>
+      <c r="P14" s="32"/>
+      <c r="Q14" s="31"/>
+      <c r="R14" s="29"/>
+      <c r="S14" s="32"/>
+      <c r="T14" s="31"/>
+      <c r="U14" s="29"/>
+      <c r="V14" s="32"/>
+      <c r="W14" s="31"/>
+      <c r="X14" s="29"/>
+      <c r="Y14" s="32"/>
+      <c r="Z14" s="31"/>
+      <c r="AA14" s="29"/>
+      <c r="AB14" s="32"/>
+      <c r="AC14" s="31"/>
+      <c r="AD14" s="29"/>
+      <c r="AE14" s="32"/>
+      <c r="AF14" s="31"/>
+      <c r="AG14" s="29"/>
+      <c r="AH14" s="32"/>
+      <c r="AI14" s="31"/>
+      <c r="AJ14" s="29"/>
+      <c r="AK14" s="32"/>
+      <c r="AL14" s="31"/>
+      <c r="AM14" s="29"/>
+      <c r="AN14" s="32"/>
+      <c r="AO14" s="31"/>
+      <c r="AP14" s="29"/>
+      <c r="AQ14" s="32"/>
+      <c r="AR14" s="31"/>
     </row>
     <row r="15" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B15" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="31"/>
-      <c r="D15" s="32"/>
-      <c r="E15" s="33"/>
-      <c r="F15" s="31"/>
-      <c r="G15" s="32"/>
-      <c r="H15" s="33"/>
-      <c r="I15" s="31"/>
-      <c r="J15" s="32"/>
-      <c r="K15" s="33"/>
-      <c r="L15" s="31"/>
-      <c r="M15" s="32"/>
-      <c r="N15" s="33"/>
-      <c r="O15" s="31"/>
-      <c r="P15" s="32"/>
-      <c r="Q15" s="33"/>
-      <c r="R15" s="31"/>
-      <c r="S15" s="32"/>
-      <c r="T15" s="33"/>
-      <c r="U15" s="31"/>
-      <c r="V15" s="32"/>
-      <c r="W15" s="33"/>
-      <c r="X15" s="31"/>
-      <c r="Y15" s="32"/>
-      <c r="Z15" s="33"/>
-      <c r="AA15" s="31"/>
-      <c r="AB15" s="32"/>
-      <c r="AC15" s="33"/>
-      <c r="AD15" s="31"/>
-      <c r="AE15" s="32"/>
-      <c r="AF15" s="33"/>
-      <c r="AG15" s="31"/>
-      <c r="AH15" s="32"/>
-      <c r="AI15" s="33"/>
-      <c r="AJ15" s="31"/>
-      <c r="AK15" s="32"/>
-      <c r="AL15" s="33"/>
-      <c r="AM15" s="31"/>
-      <c r="AN15" s="32"/>
-      <c r="AO15" s="33"/>
-      <c r="AP15" s="31"/>
-      <c r="AQ15" s="32"/>
-      <c r="AR15" s="33"/>
+      <c r="C15" s="29"/>
+      <c r="D15" s="30"/>
+      <c r="E15" s="31"/>
+      <c r="F15" s="29"/>
+      <c r="G15" s="30"/>
+      <c r="H15" s="31"/>
+      <c r="I15" s="29"/>
+      <c r="J15" s="30"/>
+      <c r="K15" s="31"/>
+      <c r="L15" s="29"/>
+      <c r="M15" s="30"/>
+      <c r="N15" s="31"/>
+      <c r="O15" s="29"/>
+      <c r="P15" s="30"/>
+      <c r="Q15" s="31"/>
+      <c r="R15" s="29"/>
+      <c r="S15" s="30"/>
+      <c r="T15" s="31"/>
+      <c r="U15" s="29"/>
+      <c r="V15" s="30"/>
+      <c r="W15" s="31"/>
+      <c r="X15" s="29"/>
+      <c r="Y15" s="30"/>
+      <c r="Z15" s="31"/>
+      <c r="AA15" s="29"/>
+      <c r="AB15" s="30"/>
+      <c r="AC15" s="31"/>
+      <c r="AD15" s="29"/>
+      <c r="AE15" s="30"/>
+      <c r="AF15" s="31"/>
+      <c r="AG15" s="29"/>
+      <c r="AH15" s="30"/>
+      <c r="AI15" s="31"/>
+      <c r="AJ15" s="29"/>
+      <c r="AK15" s="30"/>
+      <c r="AL15" s="31"/>
+      <c r="AM15" s="29"/>
+      <c r="AN15" s="30"/>
+      <c r="AO15" s="31"/>
+      <c r="AP15" s="29"/>
+      <c r="AQ15" s="30"/>
+      <c r="AR15" s="31"/>
     </row>
     <row r="16" spans="1:44" ht="30.75" x14ac:dyDescent="0.45">
       <c r="B16" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="C16" s="31"/>
-      <c r="D16" s="32"/>
-      <c r="E16" s="33"/>
-      <c r="F16" s="31"/>
-      <c r="G16" s="32"/>
-      <c r="H16" s="33"/>
-      <c r="I16" s="31"/>
-      <c r="J16" s="32"/>
-      <c r="K16" s="33"/>
-      <c r="L16" s="31"/>
-      <c r="M16" s="32"/>
-      <c r="N16" s="33"/>
-      <c r="O16" s="31"/>
-      <c r="P16" s="32"/>
-      <c r="Q16" s="33"/>
-      <c r="R16" s="31"/>
-      <c r="S16" s="32"/>
-      <c r="T16" s="33"/>
-      <c r="U16" s="31"/>
-      <c r="V16" s="32"/>
-      <c r="W16" s="33"/>
-      <c r="X16" s="31"/>
-      <c r="Y16" s="32"/>
-      <c r="Z16" s="33"/>
-      <c r="AA16" s="31"/>
-      <c r="AB16" s="32"/>
-      <c r="AC16" s="33"/>
-      <c r="AD16" s="31"/>
-      <c r="AE16" s="32"/>
-      <c r="AF16" s="33"/>
-      <c r="AG16" s="31"/>
-      <c r="AH16" s="32"/>
-      <c r="AI16" s="33"/>
-      <c r="AJ16" s="31"/>
-      <c r="AK16" s="32"/>
-      <c r="AL16" s="33"/>
-      <c r="AM16" s="31"/>
-      <c r="AN16" s="32"/>
-      <c r="AO16" s="33"/>
-      <c r="AP16" s="31"/>
-      <c r="AQ16" s="32"/>
-      <c r="AR16" s="33"/>
+      <c r="C16" s="29"/>
+      <c r="D16" s="30"/>
+      <c r="E16" s="31"/>
+      <c r="F16" s="29"/>
+      <c r="G16" s="30"/>
+      <c r="H16" s="31"/>
+      <c r="I16" s="29"/>
+      <c r="J16" s="30"/>
+      <c r="K16" s="31"/>
+      <c r="L16" s="29"/>
+      <c r="M16" s="30"/>
+      <c r="N16" s="31"/>
+      <c r="O16" s="29"/>
+      <c r="P16" s="30"/>
+      <c r="Q16" s="31"/>
+      <c r="R16" s="29"/>
+      <c r="S16" s="30"/>
+      <c r="T16" s="31"/>
+      <c r="U16" s="29"/>
+      <c r="V16" s="30"/>
+      <c r="W16" s="31"/>
+      <c r="X16" s="29"/>
+      <c r="Y16" s="30"/>
+      <c r="Z16" s="31"/>
+      <c r="AA16" s="29"/>
+      <c r="AB16" s="30"/>
+      <c r="AC16" s="31"/>
+      <c r="AD16" s="29"/>
+      <c r="AE16" s="30"/>
+      <c r="AF16" s="31"/>
+      <c r="AG16" s="29"/>
+      <c r="AH16" s="30"/>
+      <c r="AI16" s="31"/>
+      <c r="AJ16" s="29"/>
+      <c r="AK16" s="30"/>
+      <c r="AL16" s="31"/>
+      <c r="AM16" s="29"/>
+      <c r="AN16" s="30"/>
+      <c r="AO16" s="31"/>
+      <c r="AP16" s="29"/>
+      <c r="AQ16" s="30"/>
+      <c r="AR16" s="31"/>
     </row>
     <row r="17" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B17" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="C17" s="31"/>
-      <c r="D17" s="35"/>
-      <c r="E17" s="33"/>
-      <c r="F17" s="31"/>
-      <c r="G17" s="35"/>
-      <c r="H17" s="33"/>
-      <c r="I17" s="31"/>
-      <c r="J17" s="35"/>
-      <c r="K17" s="33"/>
-      <c r="L17" s="31"/>
-      <c r="M17" s="35"/>
-      <c r="N17" s="33"/>
-      <c r="O17" s="31"/>
-      <c r="P17" s="35"/>
-      <c r="Q17" s="33"/>
-      <c r="R17" s="31"/>
-      <c r="S17" s="35"/>
-      <c r="T17" s="33"/>
-      <c r="U17" s="31"/>
-      <c r="V17" s="35"/>
-      <c r="W17" s="33"/>
-      <c r="X17" s="31"/>
-      <c r="Y17" s="35"/>
-      <c r="Z17" s="33"/>
-      <c r="AA17" s="31"/>
-      <c r="AB17" s="35"/>
-      <c r="AC17" s="33"/>
-      <c r="AD17" s="31"/>
-      <c r="AE17" s="35"/>
-      <c r="AF17" s="33"/>
-      <c r="AG17" s="31"/>
-      <c r="AH17" s="35"/>
-      <c r="AI17" s="33"/>
-      <c r="AJ17" s="31"/>
-      <c r="AK17" s="35"/>
-      <c r="AL17" s="33"/>
-      <c r="AM17" s="31"/>
-      <c r="AN17" s="35"/>
-      <c r="AO17" s="33"/>
-      <c r="AP17" s="31"/>
-      <c r="AQ17" s="35"/>
-      <c r="AR17" s="33"/>
+      <c r="C17" s="29"/>
+      <c r="D17" s="33"/>
+      <c r="E17" s="31"/>
+      <c r="F17" s="29"/>
+      <c r="G17" s="33"/>
+      <c r="H17" s="31"/>
+      <c r="I17" s="29"/>
+      <c r="J17" s="33"/>
+      <c r="K17" s="31"/>
+      <c r="L17" s="29"/>
+      <c r="M17" s="33"/>
+      <c r="N17" s="31"/>
+      <c r="O17" s="29"/>
+      <c r="P17" s="33"/>
+      <c r="Q17" s="31"/>
+      <c r="R17" s="29"/>
+      <c r="S17" s="33"/>
+      <c r="T17" s="31"/>
+      <c r="U17" s="29"/>
+      <c r="V17" s="33"/>
+      <c r="W17" s="31"/>
+      <c r="X17" s="29"/>
+      <c r="Y17" s="33"/>
+      <c r="Z17" s="31"/>
+      <c r="AA17" s="29"/>
+      <c r="AB17" s="33"/>
+      <c r="AC17" s="31"/>
+      <c r="AD17" s="29"/>
+      <c r="AE17" s="33"/>
+      <c r="AF17" s="31"/>
+      <c r="AG17" s="29"/>
+      <c r="AH17" s="33"/>
+      <c r="AI17" s="31"/>
+      <c r="AJ17" s="29"/>
+      <c r="AK17" s="33"/>
+      <c r="AL17" s="31"/>
+      <c r="AM17" s="29"/>
+      <c r="AN17" s="33"/>
+      <c r="AO17" s="31"/>
+      <c r="AP17" s="29"/>
+      <c r="AQ17" s="33"/>
+      <c r="AR17" s="31"/>
     </row>
     <row r="18" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B18" s="18" t="s">
         <v>18</v>
       </c>
-      <c r="C18" s="31"/>
-      <c r="D18" s="32"/>
-      <c r="E18" s="33"/>
-      <c r="F18" s="31"/>
-      <c r="G18" s="32"/>
-      <c r="H18" s="33"/>
-      <c r="I18" s="31"/>
-      <c r="J18" s="32"/>
-      <c r="K18" s="33"/>
-      <c r="L18" s="31"/>
-      <c r="M18" s="32"/>
-      <c r="N18" s="33"/>
-      <c r="O18" s="31"/>
-      <c r="P18" s="32"/>
-      <c r="Q18" s="33"/>
-      <c r="R18" s="31"/>
-      <c r="S18" s="32"/>
-      <c r="T18" s="33"/>
-      <c r="U18" s="31"/>
-      <c r="V18" s="32"/>
-      <c r="W18" s="33"/>
-      <c r="X18" s="31"/>
-      <c r="Y18" s="32"/>
-      <c r="Z18" s="33"/>
-      <c r="AA18" s="31"/>
-      <c r="AB18" s="32"/>
-      <c r="AC18" s="33"/>
-      <c r="AD18" s="31"/>
-      <c r="AE18" s="32"/>
-      <c r="AF18" s="33"/>
-      <c r="AG18" s="31"/>
-      <c r="AH18" s="32"/>
-      <c r="AI18" s="33"/>
-      <c r="AJ18" s="31"/>
-      <c r="AK18" s="32"/>
-      <c r="AL18" s="33"/>
-      <c r="AM18" s="31"/>
-      <c r="AN18" s="32"/>
-      <c r="AO18" s="33"/>
-      <c r="AP18" s="31"/>
-      <c r="AQ18" s="32"/>
-      <c r="AR18" s="33"/>
+      <c r="C18" s="29"/>
+      <c r="D18" s="30"/>
+      <c r="E18" s="31"/>
+      <c r="F18" s="29"/>
+      <c r="G18" s="30"/>
+      <c r="H18" s="31"/>
+      <c r="I18" s="29"/>
+      <c r="J18" s="30"/>
+      <c r="K18" s="31"/>
+      <c r="L18" s="29"/>
+      <c r="M18" s="30"/>
+      <c r="N18" s="31"/>
+      <c r="O18" s="29"/>
+      <c r="P18" s="30"/>
+      <c r="Q18" s="31"/>
+      <c r="R18" s="29"/>
+      <c r="S18" s="30"/>
+      <c r="T18" s="31"/>
+      <c r="U18" s="29"/>
+      <c r="V18" s="30"/>
+      <c r="W18" s="31"/>
+      <c r="X18" s="29"/>
+      <c r="Y18" s="30"/>
+      <c r="Z18" s="31"/>
+      <c r="AA18" s="29"/>
+      <c r="AB18" s="30"/>
+      <c r="AC18" s="31"/>
+      <c r="AD18" s="29"/>
+      <c r="AE18" s="30"/>
+      <c r="AF18" s="31"/>
+      <c r="AG18" s="29"/>
+      <c r="AH18" s="30"/>
+      <c r="AI18" s="31"/>
+      <c r="AJ18" s="29"/>
+      <c r="AK18" s="30"/>
+      <c r="AL18" s="31"/>
+      <c r="AM18" s="29"/>
+      <c r="AN18" s="30"/>
+      <c r="AO18" s="31"/>
+      <c r="AP18" s="29"/>
+      <c r="AQ18" s="30"/>
+      <c r="AR18" s="31"/>
     </row>
     <row r="19" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B19" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="C19" s="31"/>
-      <c r="D19" s="32"/>
-      <c r="E19" s="33"/>
-      <c r="F19" s="31"/>
-      <c r="G19" s="32"/>
-      <c r="H19" s="33"/>
-      <c r="I19" s="31"/>
-      <c r="J19" s="32"/>
-      <c r="K19" s="33"/>
-      <c r="L19" s="31"/>
-      <c r="M19" s="32"/>
-      <c r="N19" s="33"/>
-      <c r="O19" s="31"/>
-      <c r="P19" s="32"/>
-      <c r="Q19" s="33"/>
-      <c r="R19" s="31"/>
-      <c r="S19" s="32"/>
-      <c r="T19" s="33"/>
-      <c r="U19" s="31"/>
-      <c r="V19" s="32"/>
-      <c r="W19" s="33"/>
-      <c r="X19" s="31"/>
-      <c r="Y19" s="32"/>
-      <c r="Z19" s="33"/>
-      <c r="AA19" s="31"/>
-      <c r="AB19" s="32"/>
-      <c r="AC19" s="33"/>
-      <c r="AD19" s="31"/>
-      <c r="AE19" s="32"/>
-      <c r="AF19" s="33"/>
-      <c r="AG19" s="31"/>
-      <c r="AH19" s="32"/>
-      <c r="AI19" s="33"/>
-      <c r="AJ19" s="31"/>
-      <c r="AK19" s="32"/>
-      <c r="AL19" s="33"/>
-      <c r="AM19" s="31"/>
-      <c r="AN19" s="32"/>
-      <c r="AO19" s="33"/>
-      <c r="AP19" s="31"/>
-      <c r="AQ19" s="32"/>
-      <c r="AR19" s="33"/>
+      <c r="C19" s="29"/>
+      <c r="D19" s="30"/>
+      <c r="E19" s="31"/>
+      <c r="F19" s="29"/>
+      <c r="G19" s="30"/>
+      <c r="H19" s="31"/>
+      <c r="I19" s="29"/>
+      <c r="J19" s="30"/>
+      <c r="K19" s="31"/>
+      <c r="L19" s="29"/>
+      <c r="M19" s="30"/>
+      <c r="N19" s="31"/>
+      <c r="O19" s="29"/>
+      <c r="P19" s="30"/>
+      <c r="Q19" s="31"/>
+      <c r="R19" s="29"/>
+      <c r="S19" s="30"/>
+      <c r="T19" s="31"/>
+      <c r="U19" s="29"/>
+      <c r="V19" s="30"/>
+      <c r="W19" s="31"/>
+      <c r="X19" s="29"/>
+      <c r="Y19" s="30"/>
+      <c r="Z19" s="31"/>
+      <c r="AA19" s="29"/>
+      <c r="AB19" s="30"/>
+      <c r="AC19" s="31"/>
+      <c r="AD19" s="29"/>
+      <c r="AE19" s="30"/>
+      <c r="AF19" s="31"/>
+      <c r="AG19" s="29"/>
+      <c r="AH19" s="30"/>
+      <c r="AI19" s="31"/>
+      <c r="AJ19" s="29"/>
+      <c r="AK19" s="30"/>
+      <c r="AL19" s="31"/>
+      <c r="AM19" s="29"/>
+      <c r="AN19" s="30"/>
+      <c r="AO19" s="31"/>
+      <c r="AP19" s="29"/>
+      <c r="AQ19" s="30"/>
+      <c r="AR19" s="31"/>
     </row>
     <row r="20" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B20" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="C20" s="31"/>
-      <c r="D20" s="37" t="e">
+      <c r="C20" s="29"/>
+      <c r="D20" s="35" t="e">
         <f>D18/D19</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="E20" s="36"/>
-      <c r="F20" s="31"/>
-      <c r="G20" s="37" t="e">
+      <c r="E20" s="34"/>
+      <c r="F20" s="29"/>
+      <c r="G20" s="35" t="e">
         <f>G18/G19</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="H20" s="36"/>
-      <c r="I20" s="31"/>
-      <c r="J20" s="37" t="e">
+      <c r="H20" s="34"/>
+      <c r="I20" s="29"/>
+      <c r="J20" s="35" t="e">
         <f>J18/J19</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="K20" s="36"/>
-      <c r="L20" s="31"/>
-      <c r="M20" s="37" t="e">
+      <c r="K20" s="34"/>
+      <c r="L20" s="29"/>
+      <c r="M20" s="35" t="e">
         <f>M18/M19</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="N20" s="36"/>
-      <c r="O20" s="31"/>
-      <c r="P20" s="37" t="e">
+      <c r="N20" s="34"/>
+      <c r="O20" s="29"/>
+      <c r="P20" s="35" t="e">
         <f>P18/P19</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Q20" s="36"/>
-      <c r="R20" s="31"/>
-      <c r="S20" s="37" t="e">
+      <c r="Q20" s="34"/>
+      <c r="R20" s="29"/>
+      <c r="S20" s="35" t="e">
         <f>S18/S19</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="T20" s="36"/>
-      <c r="U20" s="31"/>
-      <c r="V20" s="37" t="e">
+      <c r="T20" s="34"/>
+      <c r="U20" s="29"/>
+      <c r="V20" s="35" t="e">
         <f>V18/V19</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="W20" s="36"/>
-      <c r="X20" s="31"/>
-      <c r="Y20" s="37" t="e">
+      <c r="W20" s="34"/>
+      <c r="X20" s="29"/>
+      <c r="Y20" s="35" t="e">
         <f>Y18/Y19</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="Z20" s="36"/>
-      <c r="AA20" s="31"/>
-      <c r="AB20" s="37" t="e">
+      <c r="Z20" s="34"/>
+      <c r="AA20" s="29"/>
+      <c r="AB20" s="35" t="e">
         <f>AB18/AB19</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AC20" s="36"/>
-      <c r="AD20" s="31"/>
-      <c r="AE20" s="37" t="e">
+      <c r="AC20" s="34"/>
+      <c r="AD20" s="29"/>
+      <c r="AE20" s="35" t="e">
         <f>AE18/AE19</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AF20" s="36"/>
-      <c r="AG20" s="31"/>
-      <c r="AH20" s="37" t="e">
+      <c r="AF20" s="34"/>
+      <c r="AG20" s="29"/>
+      <c r="AH20" s="35" t="e">
         <f>AH18/AH19</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AI20" s="36"/>
-      <c r="AJ20" s="31"/>
-      <c r="AK20" s="37" t="e">
+      <c r="AI20" s="34"/>
+      <c r="AJ20" s="29"/>
+      <c r="AK20" s="35" t="e">
         <f>AK18/AK19</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AL20" s="36"/>
-      <c r="AM20" s="31"/>
-      <c r="AN20" s="37" t="e">
+      <c r="AL20" s="34"/>
+      <c r="AM20" s="29"/>
+      <c r="AN20" s="35" t="e">
         <f>AN18/AN19</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AO20" s="36"/>
-      <c r="AP20" s="31"/>
-      <c r="AQ20" s="37" t="e">
+      <c r="AO20" s="34"/>
+      <c r="AP20" s="29"/>
+      <c r="AQ20" s="35" t="e">
         <f>AQ18/AQ19</f>
         <v>#DIV/0!</v>
       </c>
-      <c r="AR20" s="36"/>
+      <c r="AR20" s="34"/>
     </row>
     <row r="21" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B21" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="C21" s="31"/>
-      <c r="D21" s="32"/>
-      <c r="E21" s="33"/>
-      <c r="F21" s="31"/>
-      <c r="G21" s="32"/>
-      <c r="H21" s="33"/>
-      <c r="I21" s="31"/>
-      <c r="J21" s="32"/>
-      <c r="K21" s="33"/>
-      <c r="L21" s="31"/>
-      <c r="M21" s="32"/>
-      <c r="N21" s="33"/>
-      <c r="O21" s="31"/>
-      <c r="P21" s="32"/>
-      <c r="Q21" s="33"/>
-      <c r="R21" s="31"/>
-      <c r="S21" s="32"/>
-      <c r="T21" s="33"/>
-      <c r="U21" s="31"/>
-      <c r="V21" s="32"/>
-      <c r="W21" s="33"/>
-      <c r="X21" s="31"/>
-      <c r="Y21" s="32"/>
-      <c r="Z21" s="33"/>
-      <c r="AA21" s="31"/>
-      <c r="AB21" s="32"/>
-      <c r="AC21" s="33"/>
-      <c r="AD21" s="31"/>
-      <c r="AE21" s="32"/>
-      <c r="AF21" s="33"/>
-      <c r="AG21" s="31"/>
-      <c r="AH21" s="32"/>
-      <c r="AI21" s="33"/>
-      <c r="AJ21" s="31"/>
-      <c r="AK21" s="32"/>
-      <c r="AL21" s="33"/>
-      <c r="AM21" s="31"/>
-      <c r="AN21" s="32"/>
-      <c r="AO21" s="33"/>
-      <c r="AP21" s="31"/>
-      <c r="AQ21" s="32"/>
-      <c r="AR21" s="33"/>
+      <c r="C21" s="29"/>
+      <c r="D21" s="30"/>
+      <c r="E21" s="31"/>
+      <c r="F21" s="29"/>
+      <c r="G21" s="30"/>
+      <c r="H21" s="31"/>
+      <c r="I21" s="29"/>
+      <c r="J21" s="30"/>
+      <c r="K21" s="31"/>
+      <c r="L21" s="29"/>
+      <c r="M21" s="30"/>
+      <c r="N21" s="31"/>
+      <c r="O21" s="29"/>
+      <c r="P21" s="30"/>
+      <c r="Q21" s="31"/>
+      <c r="R21" s="29"/>
+      <c r="S21" s="30"/>
+      <c r="T21" s="31"/>
+      <c r="U21" s="29"/>
+      <c r="V21" s="30"/>
+      <c r="W21" s="31"/>
+      <c r="X21" s="29"/>
+      <c r="Y21" s="30"/>
+      <c r="Z21" s="31"/>
+      <c r="AA21" s="29"/>
+      <c r="AB21" s="30"/>
+      <c r="AC21" s="31"/>
+      <c r="AD21" s="29"/>
+      <c r="AE21" s="30"/>
+      <c r="AF21" s="31"/>
+      <c r="AG21" s="29"/>
+      <c r="AH21" s="30"/>
+      <c r="AI21" s="31"/>
+      <c r="AJ21" s="29"/>
+      <c r="AK21" s="30"/>
+      <c r="AL21" s="31"/>
+      <c r="AM21" s="29"/>
+      <c r="AN21" s="30"/>
+      <c r="AO21" s="31"/>
+      <c r="AP21" s="29"/>
+      <c r="AQ21" s="30"/>
+      <c r="AR21" s="31"/>
     </row>
     <row r="22" spans="1:44" ht="61.5" x14ac:dyDescent="0.45">
       <c r="B22" s="18" t="s">
         <v>44</v>
       </c>
-      <c r="C22" s="31"/>
-      <c r="D22" s="34"/>
-      <c r="E22" s="33"/>
-      <c r="F22" s="31"/>
-      <c r="G22" s="34"/>
-      <c r="H22" s="33"/>
-      <c r="I22" s="31"/>
-      <c r="J22" s="34"/>
-      <c r="K22" s="33"/>
-      <c r="L22" s="31"/>
-      <c r="M22" s="34"/>
-      <c r="N22" s="33"/>
-      <c r="O22" s="31"/>
-      <c r="P22" s="34"/>
-      <c r="Q22" s="33"/>
-      <c r="R22" s="31"/>
-      <c r="S22" s="34"/>
-      <c r="T22" s="33"/>
-      <c r="U22" s="31"/>
-      <c r="V22" s="34"/>
-      <c r="W22" s="33"/>
-      <c r="X22" s="31"/>
-      <c r="Y22" s="34"/>
-      <c r="Z22" s="33"/>
-      <c r="AA22" s="31"/>
-      <c r="AB22" s="34"/>
-      <c r="AC22" s="33"/>
-      <c r="AD22" s="31"/>
-      <c r="AE22" s="34"/>
-      <c r="AF22" s="33"/>
-      <c r="AG22" s="31"/>
-      <c r="AH22" s="34"/>
-      <c r="AI22" s="33"/>
-      <c r="AJ22" s="31"/>
-      <c r="AK22" s="34"/>
-      <c r="AL22" s="33"/>
-      <c r="AM22" s="31"/>
-      <c r="AN22" s="34"/>
-      <c r="AO22" s="33"/>
-      <c r="AP22" s="31"/>
-      <c r="AQ22" s="34"/>
-      <c r="AR22" s="33"/>
+      <c r="C22" s="29"/>
+      <c r="D22" s="32"/>
+      <c r="E22" s="31"/>
+      <c r="F22" s="29"/>
+      <c r="G22" s="32"/>
+      <c r="H22" s="31"/>
+      <c r="I22" s="29"/>
+      <c r="J22" s="32"/>
+      <c r="K22" s="31"/>
+      <c r="L22" s="29"/>
+      <c r="M22" s="32"/>
+      <c r="N22" s="31"/>
+      <c r="O22" s="29"/>
+      <c r="P22" s="32"/>
+      <c r="Q22" s="31"/>
+      <c r="R22" s="29"/>
+      <c r="S22" s="32"/>
+      <c r="T22" s="31"/>
+      <c r="U22" s="29"/>
+      <c r="V22" s="32"/>
+      <c r="W22" s="31"/>
+      <c r="X22" s="29"/>
+      <c r="Y22" s="32"/>
+      <c r="Z22" s="31"/>
+      <c r="AA22" s="29"/>
+      <c r="AB22" s="32"/>
+      <c r="AC22" s="31"/>
+      <c r="AD22" s="29"/>
+      <c r="AE22" s="32"/>
+      <c r="AF22" s="31"/>
+      <c r="AG22" s="29"/>
+      <c r="AH22" s="32"/>
+      <c r="AI22" s="31"/>
+      <c r="AJ22" s="29"/>
+      <c r="AK22" s="32"/>
+      <c r="AL22" s="31"/>
+      <c r="AM22" s="29"/>
+      <c r="AN22" s="32"/>
+      <c r="AO22" s="31"/>
+      <c r="AP22" s="29"/>
+      <c r="AQ22" s="32"/>
+      <c r="AR22" s="31"/>
     </row>
     <row r="23" spans="1:44" ht="30.75" x14ac:dyDescent="0.45">
       <c r="B23" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="C23" s="31"/>
-      <c r="D23" s="34"/>
-      <c r="E23" s="33"/>
-      <c r="F23" s="31"/>
-      <c r="G23" s="34"/>
-      <c r="H23" s="33"/>
-      <c r="I23" s="31"/>
-      <c r="J23" s="34"/>
-      <c r="K23" s="33"/>
-      <c r="L23" s="31"/>
-      <c r="M23" s="34"/>
-      <c r="N23" s="33"/>
-      <c r="O23" s="31"/>
-      <c r="P23" s="34"/>
-      <c r="Q23" s="33"/>
-      <c r="R23" s="31"/>
-      <c r="S23" s="34"/>
-      <c r="T23" s="33"/>
-      <c r="U23" s="31"/>
-      <c r="V23" s="34"/>
-      <c r="W23" s="33"/>
-      <c r="X23" s="31"/>
-      <c r="Y23" s="34"/>
-      <c r="Z23" s="33"/>
-      <c r="AA23" s="31"/>
-      <c r="AB23" s="34"/>
-      <c r="AC23" s="33"/>
-      <c r="AD23" s="31"/>
-      <c r="AE23" s="34"/>
-      <c r="AF23" s="33"/>
-      <c r="AG23" s="31"/>
-      <c r="AH23" s="34"/>
-      <c r="AI23" s="33"/>
-      <c r="AJ23" s="31"/>
-      <c r="AK23" s="34"/>
-      <c r="AL23" s="33"/>
-      <c r="AM23" s="31"/>
-      <c r="AN23" s="34"/>
-      <c r="AO23" s="33"/>
-      <c r="AP23" s="31"/>
-      <c r="AQ23" s="34"/>
-      <c r="AR23" s="33"/>
+      <c r="C23" s="29"/>
+      <c r="D23" s="32"/>
+      <c r="E23" s="31"/>
+      <c r="F23" s="29"/>
+      <c r="G23" s="32"/>
+      <c r="H23" s="31"/>
+      <c r="I23" s="29"/>
+      <c r="J23" s="32"/>
+      <c r="K23" s="31"/>
+      <c r="L23" s="29"/>
+      <c r="M23" s="32"/>
+      <c r="N23" s="31"/>
+      <c r="O23" s="29"/>
+      <c r="P23" s="32"/>
+      <c r="Q23" s="31"/>
+      <c r="R23" s="29"/>
+      <c r="S23" s="32"/>
+      <c r="T23" s="31"/>
+      <c r="U23" s="29"/>
+      <c r="V23" s="32"/>
+      <c r="W23" s="31"/>
+      <c r="X23" s="29"/>
+      <c r="Y23" s="32"/>
+      <c r="Z23" s="31"/>
+      <c r="AA23" s="29"/>
+      <c r="AB23" s="32"/>
+      <c r="AC23" s="31"/>
+      <c r="AD23" s="29"/>
+      <c r="AE23" s="32"/>
+      <c r="AF23" s="31"/>
+      <c r="AG23" s="29"/>
+      <c r="AH23" s="32"/>
+      <c r="AI23" s="31"/>
+      <c r="AJ23" s="29"/>
+      <c r="AK23" s="32"/>
+      <c r="AL23" s="31"/>
+      <c r="AM23" s="29"/>
+      <c r="AN23" s="32"/>
+      <c r="AO23" s="31"/>
+      <c r="AP23" s="29"/>
+      <c r="AQ23" s="32"/>
+      <c r="AR23" s="31"/>
     </row>
     <row r="24" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B24" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="C24" s="31"/>
-      <c r="D24" s="32"/>
-      <c r="E24" s="33"/>
-      <c r="F24" s="31"/>
-      <c r="G24" s="32"/>
-      <c r="H24" s="33"/>
-      <c r="I24" s="31"/>
-      <c r="J24" s="32"/>
-      <c r="K24" s="33"/>
-      <c r="L24" s="31"/>
-      <c r="M24" s="32"/>
-      <c r="N24" s="33"/>
-      <c r="O24" s="31"/>
-      <c r="P24" s="32"/>
-      <c r="Q24" s="33"/>
-      <c r="R24" s="31"/>
-      <c r="S24" s="32"/>
-      <c r="T24" s="33"/>
-      <c r="U24" s="31"/>
-      <c r="V24" s="32"/>
-      <c r="W24" s="33"/>
-      <c r="X24" s="31"/>
-      <c r="Y24" s="32"/>
-      <c r="Z24" s="33"/>
-      <c r="AA24" s="31"/>
-      <c r="AB24" s="32"/>
-      <c r="AC24" s="33"/>
-      <c r="AD24" s="31"/>
-      <c r="AE24" s="32"/>
-      <c r="AF24" s="33"/>
-      <c r="AG24" s="31"/>
-      <c r="AH24" s="32"/>
-      <c r="AI24" s="33"/>
-      <c r="AJ24" s="31"/>
-      <c r="AK24" s="32"/>
-      <c r="AL24" s="33"/>
-      <c r="AM24" s="31"/>
-      <c r="AN24" s="32"/>
-      <c r="AO24" s="33"/>
-      <c r="AP24" s="31"/>
-      <c r="AQ24" s="32"/>
-      <c r="AR24" s="33"/>
+      <c r="C24" s="29"/>
+      <c r="D24" s="30"/>
+      <c r="E24" s="31"/>
+      <c r="F24" s="29"/>
+      <c r="G24" s="30"/>
+      <c r="H24" s="31"/>
+      <c r="I24" s="29"/>
+      <c r="J24" s="30"/>
+      <c r="K24" s="31"/>
+      <c r="L24" s="29"/>
+      <c r="M24" s="30"/>
+      <c r="N24" s="31"/>
+      <c r="O24" s="29"/>
+      <c r="P24" s="30"/>
+      <c r="Q24" s="31"/>
+      <c r="R24" s="29"/>
+      <c r="S24" s="30"/>
+      <c r="T24" s="31"/>
+      <c r="U24" s="29"/>
+      <c r="V24" s="30"/>
+      <c r="W24" s="31"/>
+      <c r="X24" s="29"/>
+      <c r="Y24" s="30"/>
+      <c r="Z24" s="31"/>
+      <c r="AA24" s="29"/>
+      <c r="AB24" s="30"/>
+      <c r="AC24" s="31"/>
+      <c r="AD24" s="29"/>
+      <c r="AE24" s="30"/>
+      <c r="AF24" s="31"/>
+      <c r="AG24" s="29"/>
+      <c r="AH24" s="30"/>
+      <c r="AI24" s="31"/>
+      <c r="AJ24" s="29"/>
+      <c r="AK24" s="30"/>
+      <c r="AL24" s="31"/>
+      <c r="AM24" s="29"/>
+      <c r="AN24" s="30"/>
+      <c r="AO24" s="31"/>
+      <c r="AP24" s="29"/>
+      <c r="AQ24" s="30"/>
+      <c r="AR24" s="31"/>
     </row>
     <row r="25" spans="1:44" ht="48.95" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B25" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="C25" s="31"/>
-      <c r="D25" s="32"/>
-      <c r="E25" s="33"/>
-      <c r="F25" s="31"/>
-      <c r="G25" s="32"/>
-      <c r="H25" s="33"/>
-      <c r="I25" s="31"/>
-      <c r="J25" s="32"/>
-      <c r="K25" s="33"/>
-      <c r="L25" s="31"/>
-      <c r="M25" s="32"/>
-      <c r="N25" s="33"/>
-      <c r="O25" s="31"/>
-      <c r="P25" s="32"/>
-      <c r="Q25" s="33"/>
-      <c r="R25" s="31"/>
-      <c r="S25" s="32"/>
-      <c r="T25" s="33"/>
-      <c r="U25" s="31"/>
-      <c r="V25" s="32"/>
-      <c r="W25" s="33"/>
-      <c r="X25" s="31"/>
-      <c r="Y25" s="32"/>
-      <c r="Z25" s="33"/>
-      <c r="AA25" s="31"/>
-      <c r="AB25" s="32"/>
-      <c r="AC25" s="33"/>
-      <c r="AD25" s="31"/>
-      <c r="AE25" s="32"/>
-      <c r="AF25" s="33"/>
-      <c r="AG25" s="31"/>
-      <c r="AH25" s="32"/>
-      <c r="AI25" s="33"/>
-      <c r="AJ25" s="31"/>
-      <c r="AK25" s="32"/>
-      <c r="AL25" s="33"/>
-      <c r="AM25" s="31"/>
-      <c r="AN25" s="32"/>
-      <c r="AO25" s="33"/>
-      <c r="AP25" s="31"/>
-      <c r="AQ25" s="32"/>
-      <c r="AR25" s="33"/>
+      <c r="C25" s="29"/>
+      <c r="D25" s="30"/>
+      <c r="E25" s="31"/>
+      <c r="F25" s="29"/>
+      <c r="G25" s="30"/>
+      <c r="H25" s="31"/>
+      <c r="I25" s="29"/>
+      <c r="J25" s="30"/>
+      <c r="K25" s="31"/>
+      <c r="L25" s="29"/>
+      <c r="M25" s="30"/>
+      <c r="N25" s="31"/>
+      <c r="O25" s="29"/>
+      <c r="P25" s="30"/>
+      <c r="Q25" s="31"/>
+      <c r="R25" s="29"/>
+      <c r="S25" s="30"/>
+      <c r="T25" s="31"/>
+      <c r="U25" s="29"/>
+      <c r="V25" s="30"/>
+      <c r="W25" s="31"/>
+      <c r="X25" s="29"/>
+      <c r="Y25" s="30"/>
+      <c r="Z25" s="31"/>
+      <c r="AA25" s="29"/>
+      <c r="AB25" s="30"/>
+      <c r="AC25" s="31"/>
+      <c r="AD25" s="29"/>
+      <c r="AE25" s="30"/>
+      <c r="AF25" s="31"/>
+      <c r="AG25" s="29"/>
+      <c r="AH25" s="30"/>
+      <c r="AI25" s="31"/>
+      <c r="AJ25" s="29"/>
+      <c r="AK25" s="30"/>
+      <c r="AL25" s="31"/>
+      <c r="AM25" s="29"/>
+      <c r="AN25" s="30"/>
+      <c r="AO25" s="31"/>
+      <c r="AP25" s="29"/>
+      <c r="AQ25" s="30"/>
+      <c r="AR25" s="31"/>
     </row>
     <row r="26" spans="1:44" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B26" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="C26" s="31"/>
-      <c r="D26" s="32"/>
-      <c r="E26" s="33"/>
-      <c r="F26" s="31"/>
-      <c r="G26" s="32"/>
-      <c r="H26" s="33"/>
-      <c r="I26" s="31"/>
-      <c r="J26" s="32"/>
-      <c r="K26" s="33"/>
-      <c r="L26" s="31"/>
-      <c r="M26" s="32"/>
-      <c r="N26" s="33"/>
-      <c r="O26" s="31"/>
-      <c r="P26" s="32"/>
-      <c r="Q26" s="33"/>
-      <c r="R26" s="31"/>
-      <c r="S26" s="32"/>
-      <c r="T26" s="33"/>
-      <c r="U26" s="31"/>
-      <c r="V26" s="32"/>
-      <c r="W26" s="33"/>
-      <c r="X26" s="31"/>
-      <c r="Y26" s="32"/>
-      <c r="Z26" s="33"/>
-      <c r="AA26" s="31"/>
-      <c r="AB26" s="32"/>
-      <c r="AC26" s="33"/>
-      <c r="AD26" s="31"/>
-      <c r="AE26" s="32"/>
-      <c r="AF26" s="33"/>
-      <c r="AG26" s="31"/>
-      <c r="AH26" s="32"/>
-      <c r="AI26" s="33"/>
-      <c r="AJ26" s="31"/>
-      <c r="AK26" s="32"/>
-      <c r="AL26" s="33"/>
-      <c r="AM26" s="31"/>
-      <c r="AN26" s="32"/>
-      <c r="AO26" s="33"/>
-      <c r="AP26" s="31"/>
-      <c r="AQ26" s="32"/>
-      <c r="AR26" s="33"/>
+      <c r="C26" s="29"/>
+      <c r="D26" s="30"/>
+      <c r="E26" s="31"/>
+      <c r="F26" s="29"/>
+      <c r="G26" s="30"/>
+      <c r="H26" s="31"/>
+      <c r="I26" s="29"/>
+      <c r="J26" s="30"/>
+      <c r="K26" s="31"/>
+      <c r="L26" s="29"/>
+      <c r="M26" s="30"/>
+      <c r="N26" s="31"/>
+      <c r="O26" s="29"/>
+      <c r="P26" s="30"/>
+      <c r="Q26" s="31"/>
+      <c r="R26" s="29"/>
+      <c r="S26" s="30"/>
+      <c r="T26" s="31"/>
+      <c r="U26" s="29"/>
+      <c r="V26" s="30"/>
+      <c r="W26" s="31"/>
+      <c r="X26" s="29"/>
+      <c r="Y26" s="30"/>
+      <c r="Z26" s="31"/>
+      <c r="AA26" s="29"/>
+      <c r="AB26" s="30"/>
+      <c r="AC26" s="31"/>
+      <c r="AD26" s="29"/>
+      <c r="AE26" s="30"/>
+      <c r="AF26" s="31"/>
+      <c r="AG26" s="29"/>
+      <c r="AH26" s="30"/>
+      <c r="AI26" s="31"/>
+      <c r="AJ26" s="29"/>
+      <c r="AK26" s="30"/>
+      <c r="AL26" s="31"/>
+      <c r="AM26" s="29"/>
+      <c r="AN26" s="30"/>
+      <c r="AO26" s="31"/>
+      <c r="AP26" s="29"/>
+      <c r="AQ26" s="30"/>
+      <c r="AR26" s="31"/>
     </row>
     <row r="27" spans="1:44" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
       <c r="B27" s="18" t="s">
         <v>45</v>
       </c>
-      <c r="C27" s="31"/>
-      <c r="D27" s="32"/>
-      <c r="E27" s="33"/>
-      <c r="F27" s="31"/>
-      <c r="G27" s="32"/>
-      <c r="H27" s="33"/>
-      <c r="I27" s="31"/>
-      <c r="J27" s="32"/>
-      <c r="K27" s="33"/>
-      <c r="L27" s="31"/>
-      <c r="M27" s="32"/>
-      <c r="N27" s="33"/>
-      <c r="O27" s="31"/>
-      <c r="P27" s="32"/>
-      <c r="Q27" s="33"/>
-      <c r="R27" s="31"/>
-      <c r="S27" s="32"/>
-      <c r="T27" s="33"/>
-      <c r="U27" s="31"/>
-      <c r="V27" s="32"/>
-      <c r="W27" s="33"/>
-      <c r="X27" s="31"/>
-      <c r="Y27" s="32"/>
-      <c r="Z27" s="33"/>
-      <c r="AA27" s="31"/>
-      <c r="AB27" s="32"/>
-      <c r="AC27" s="33"/>
-      <c r="AD27" s="31"/>
-      <c r="AE27" s="32"/>
-      <c r="AF27" s="33"/>
-      <c r="AG27" s="31"/>
-      <c r="AH27" s="32"/>
-      <c r="AI27" s="33"/>
-      <c r="AJ27" s="31"/>
-      <c r="AK27" s="32"/>
-      <c r="AL27" s="33"/>
-      <c r="AM27" s="31"/>
-      <c r="AN27" s="32"/>
-      <c r="AO27" s="33"/>
-      <c r="AP27" s="31"/>
-      <c r="AQ27" s="32"/>
-      <c r="AR27" s="33"/>
+      <c r="C27" s="29"/>
+      <c r="D27" s="30"/>
+      <c r="E27" s="31"/>
+      <c r="F27" s="29"/>
+      <c r="G27" s="30"/>
+      <c r="H27" s="31"/>
+      <c r="I27" s="29"/>
+      <c r="J27" s="30"/>
+      <c r="K27" s="31"/>
+      <c r="L27" s="29"/>
+      <c r="M27" s="30"/>
+      <c r="N27" s="31"/>
+      <c r="O27" s="29"/>
+      <c r="P27" s="30"/>
+      <c r="Q27" s="31"/>
+      <c r="R27" s="29"/>
+      <c r="S27" s="30"/>
+      <c r="T27" s="31"/>
+      <c r="U27" s="29"/>
+      <c r="V27" s="30"/>
+      <c r="W27" s="31"/>
+      <c r="X27" s="29"/>
+      <c r="Y27" s="30"/>
+      <c r="Z27" s="31"/>
+      <c r="AA27" s="29"/>
+      <c r="AB27" s="30"/>
+      <c r="AC27" s="31"/>
+      <c r="AD27" s="29"/>
+      <c r="AE27" s="30"/>
+      <c r="AF27" s="31"/>
+      <c r="AG27" s="29"/>
+      <c r="AH27" s="30"/>
+      <c r="AI27" s="31"/>
+      <c r="AJ27" s="29"/>
+      <c r="AK27" s="30"/>
+      <c r="AL27" s="31"/>
+      <c r="AM27" s="29"/>
+      <c r="AN27" s="30"/>
+      <c r="AO27" s="31"/>
+      <c r="AP27" s="29"/>
+      <c r="AQ27" s="30"/>
+      <c r="AR27" s="31"/>
     </row>
     <row r="28" spans="1:44" ht="76.900000000000006" x14ac:dyDescent="0.45">
       <c r="B28" s="18" t="s">
         <v>43</v>
       </c>
-      <c r="C28" s="31"/>
-      <c r="D28" s="32"/>
-      <c r="E28" s="33"/>
-      <c r="F28" s="31"/>
-      <c r="G28" s="32"/>
-      <c r="H28" s="33"/>
-      <c r="I28" s="31"/>
-      <c r="J28" s="32"/>
-      <c r="K28" s="33"/>
-      <c r="L28" s="31"/>
-      <c r="M28" s="32"/>
-      <c r="N28" s="33"/>
-      <c r="O28" s="31"/>
-      <c r="P28" s="32"/>
-      <c r="Q28" s="33"/>
-      <c r="R28" s="31"/>
-      <c r="S28" s="32"/>
-      <c r="T28" s="33"/>
-      <c r="U28" s="31"/>
-      <c r="V28" s="32"/>
-      <c r="W28" s="33"/>
-      <c r="X28" s="31"/>
-      <c r="Y28" s="32"/>
-      <c r="Z28" s="33"/>
-      <c r="AA28" s="31"/>
-      <c r="AB28" s="32"/>
-      <c r="AC28" s="33"/>
-      <c r="AD28" s="31"/>
-      <c r="AE28" s="32"/>
-      <c r="AF28" s="33"/>
-      <c r="AG28" s="31"/>
-      <c r="AH28" s="32"/>
-      <c r="AI28" s="33"/>
-      <c r="AJ28" s="31"/>
-      <c r="AK28" s="32"/>
-      <c r="AL28" s="33"/>
-      <c r="AM28" s="31"/>
-      <c r="AN28" s="32"/>
-      <c r="AO28" s="33"/>
-      <c r="AP28" s="31"/>
-      <c r="AQ28" s="32"/>
-      <c r="AR28" s="33"/>
+      <c r="C28" s="29"/>
+      <c r="D28" s="30"/>
+      <c r="E28" s="31"/>
+      <c r="F28" s="29"/>
+      <c r="G28" s="30"/>
+      <c r="H28" s="31"/>
+      <c r="I28" s="29"/>
+      <c r="J28" s="30"/>
+      <c r="K28" s="31"/>
+      <c r="L28" s="29"/>
+      <c r="M28" s="30"/>
+      <c r="N28" s="31"/>
+      <c r="O28" s="29"/>
+      <c r="P28" s="30"/>
+      <c r="Q28" s="31"/>
+      <c r="R28" s="29"/>
+      <c r="S28" s="30"/>
+      <c r="T28" s="31"/>
+      <c r="U28" s="29"/>
+      <c r="V28" s="30"/>
+      <c r="W28" s="31"/>
+      <c r="X28" s="29"/>
+      <c r="Y28" s="30"/>
+      <c r="Z28" s="31"/>
+      <c r="AA28" s="29"/>
+      <c r="AB28" s="30"/>
+      <c r="AC28" s="31"/>
+      <c r="AD28" s="29"/>
+      <c r="AE28" s="30"/>
+      <c r="AF28" s="31"/>
+      <c r="AG28" s="29"/>
+      <c r="AH28" s="30"/>
+      <c r="AI28" s="31"/>
+      <c r="AJ28" s="29"/>
+      <c r="AK28" s="30"/>
+      <c r="AL28" s="31"/>
+      <c r="AM28" s="29"/>
+      <c r="AN28" s="30"/>
+      <c r="AO28" s="31"/>
+      <c r="AP28" s="29"/>
+      <c r="AQ28" s="30"/>
+      <c r="AR28" s="31"/>
     </row>
     <row r="29" spans="1:44" x14ac:dyDescent="0.45">
-      <c r="B29" s="38"/>
-      <c r="C29" s="39"/>
-      <c r="D29" s="40"/>
-      <c r="E29" s="41"/>
-      <c r="F29" s="39"/>
-      <c r="G29" s="40"/>
-      <c r="H29" s="41"/>
-      <c r="I29" s="39"/>
-      <c r="J29" s="40"/>
-      <c r="K29" s="41"/>
-      <c r="L29" s="39"/>
-      <c r="M29" s="40"/>
-      <c r="N29" s="41"/>
-      <c r="O29" s="39"/>
-      <c r="P29" s="40"/>
-      <c r="Q29" s="41"/>
-      <c r="R29" s="39"/>
-      <c r="S29" s="40"/>
-      <c r="T29" s="41"/>
-      <c r="U29" s="39"/>
-      <c r="V29" s="40"/>
-      <c r="W29" s="41"/>
-      <c r="X29" s="39"/>
-      <c r="Y29" s="40"/>
-      <c r="Z29" s="41"/>
-      <c r="AA29" s="39"/>
-      <c r="AB29" s="40"/>
-      <c r="AC29" s="41"/>
-      <c r="AD29" s="39"/>
-      <c r="AE29" s="40"/>
-      <c r="AF29" s="41"/>
-      <c r="AG29" s="39"/>
-      <c r="AH29" s="40"/>
-      <c r="AI29" s="41"/>
-      <c r="AJ29" s="39"/>
-      <c r="AK29" s="40"/>
-      <c r="AL29" s="41"/>
-      <c r="AM29" s="39"/>
-      <c r="AN29" s="40"/>
-      <c r="AO29" s="41"/>
-      <c r="AP29" s="39"/>
-      <c r="AQ29" s="40"/>
-      <c r="AR29" s="41"/>
+      <c r="B29" s="36"/>
+      <c r="C29" s="37"/>
+      <c r="D29" s="38"/>
+      <c r="E29" s="39"/>
+      <c r="F29" s="37"/>
+      <c r="G29" s="38"/>
+      <c r="H29" s="39"/>
+      <c r="I29" s="37"/>
+      <c r="J29" s="38"/>
+      <c r="K29" s="39"/>
+      <c r="L29" s="37"/>
+      <c r="M29" s="38"/>
+      <c r="N29" s="39"/>
+      <c r="O29" s="37"/>
+      <c r="P29" s="38"/>
+      <c r="Q29" s="39"/>
+      <c r="R29" s="37"/>
+      <c r="S29" s="38"/>
+      <c r="T29" s="39"/>
+      <c r="U29" s="37"/>
+      <c r="V29" s="38"/>
+      <c r="W29" s="39"/>
+      <c r="X29" s="37"/>
+      <c r="Y29" s="38"/>
+      <c r="Z29" s="39"/>
+      <c r="AA29" s="37"/>
+      <c r="AB29" s="38"/>
+      <c r="AC29" s="39"/>
+      <c r="AD29" s="37"/>
+      <c r="AE29" s="38"/>
+      <c r="AF29" s="39"/>
+      <c r="AG29" s="37"/>
+      <c r="AH29" s="38"/>
+      <c r="AI29" s="39"/>
+      <c r="AJ29" s="37"/>
+      <c r="AK29" s="38"/>
+      <c r="AL29" s="39"/>
+      <c r="AM29" s="37"/>
+      <c r="AN29" s="38"/>
+      <c r="AO29" s="39"/>
+      <c r="AP29" s="37"/>
+      <c r="AQ29" s="38"/>
+      <c r="AR29" s="39"/>
     </row>
     <row r="30" spans="1:44" s="2" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A30" s="1"/>
-      <c r="B30" s="42" t="s">
+      <c r="B30" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="C30" s="45">
+      <c r="C30" s="49">
         <f>AVERAGE(C4:C29)</f>
         <v>0</v>
       </c>
-      <c r="D30" s="45"/>
-      <c r="E30" s="46"/>
-      <c r="F30" s="45">
+      <c r="D30" s="49"/>
+      <c r="E30" s="50"/>
+      <c r="F30" s="49">
         <f>AVERAGE(F4:F29)</f>
         <v>0</v>
       </c>
-      <c r="G30" s="45"/>
-      <c r="H30" s="46"/>
-      <c r="I30" s="45">
+      <c r="G30" s="49"/>
+      <c r="H30" s="50"/>
+      <c r="I30" s="49">
         <f>AVERAGE(I4:I29)</f>
         <v>0</v>
       </c>
-      <c r="J30" s="45"/>
-      <c r="K30" s="46"/>
-      <c r="L30" s="45">
+      <c r="J30" s="49"/>
+      <c r="K30" s="50"/>
+      <c r="L30" s="49">
         <f>AVERAGE(L4:L29)</f>
         <v>0</v>
       </c>
-      <c r="M30" s="45"/>
-      <c r="N30" s="46"/>
-      <c r="O30" s="45">
+      <c r="M30" s="49"/>
+      <c r="N30" s="50"/>
+      <c r="O30" s="49">
         <f>AVERAGE(O4:O29)</f>
         <v>0</v>
       </c>
-      <c r="P30" s="45"/>
-      <c r="Q30" s="46"/>
-      <c r="R30" s="45">
+      <c r="P30" s="49"/>
+      <c r="Q30" s="50"/>
+      <c r="R30" s="49">
         <f>AVERAGE(R4:R29)</f>
         <v>0</v>
       </c>
-      <c r="S30" s="45"/>
-      <c r="T30" s="46"/>
-      <c r="U30" s="45">
+      <c r="S30" s="49"/>
+      <c r="T30" s="50"/>
+      <c r="U30" s="49">
         <f>AVERAGE(U4:U29)</f>
         <v>0</v>
       </c>
-      <c r="V30" s="45"/>
-      <c r="W30" s="46"/>
-      <c r="X30" s="45">
+      <c r="V30" s="49"/>
+      <c r="W30" s="50"/>
+      <c r="X30" s="49">
         <f>AVERAGE(X4:X29)</f>
         <v>0</v>
       </c>
-      <c r="Y30" s="45"/>
-      <c r="Z30" s="46"/>
-      <c r="AA30" s="45">
+      <c r="Y30" s="49"/>
+      <c r="Z30" s="50"/>
+      <c r="AA30" s="49">
         <f>AVERAGE(AA4:AA29)</f>
         <v>0</v>
       </c>
-      <c r="AB30" s="45"/>
-      <c r="AC30" s="46"/>
-      <c r="AD30" s="45">
+      <c r="AB30" s="49"/>
+      <c r="AC30" s="50"/>
+      <c r="AD30" s="49">
         <f>AVERAGE(AD4:AD29)</f>
         <v>0</v>
       </c>
-      <c r="AE30" s="45"/>
-      <c r="AF30" s="46"/>
-      <c r="AG30" s="45">
+      <c r="AE30" s="49"/>
+      <c r="AF30" s="50"/>
+      <c r="AG30" s="49">
         <f>AVERAGE(AG4:AG29)</f>
         <v>0</v>
       </c>
-      <c r="AH30" s="45"/>
-      <c r="AI30" s="46"/>
-      <c r="AJ30" s="45">
+      <c r="AH30" s="49"/>
+      <c r="AI30" s="50"/>
+      <c r="AJ30" s="49">
         <f>AVERAGE(AJ4:AJ29)</f>
         <v>0</v>
       </c>
-      <c r="AK30" s="45"/>
-      <c r="AL30" s="46"/>
-      <c r="AM30" s="45">
+      <c r="AK30" s="49"/>
+      <c r="AL30" s="50"/>
+      <c r="AM30" s="49">
         <f>AVERAGE(AM4:AM29)</f>
         <v>0</v>
       </c>
-      <c r="AN30" s="45"/>
-      <c r="AO30" s="46"/>
-      <c r="AP30" s="45">
+      <c r="AN30" s="49"/>
+      <c r="AO30" s="50"/>
+      <c r="AP30" s="49">
         <f>AVERAGE(AP4:AP29)</f>
         <v>0</v>
       </c>
-      <c r="AQ30" s="45"/>
-      <c r="AR30" s="46"/>
+      <c r="AQ30" s="49"/>
+      <c r="AR30" s="50"/>
     </row>
     <row r="31" spans="1:44" s="6" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B31" s="15"/>
@@ -5735,6 +5743,19 @@
     </row>
   </sheetData>
   <mergeCells count="29">
+    <mergeCell ref="R30:T30"/>
+    <mergeCell ref="U30:W30"/>
+    <mergeCell ref="AM30:AO30"/>
+    <mergeCell ref="X30:Z30"/>
+    <mergeCell ref="AA30:AC30"/>
+    <mergeCell ref="AD30:AF30"/>
+    <mergeCell ref="AG30:AI30"/>
+    <mergeCell ref="AJ30:AL30"/>
+    <mergeCell ref="L2:N2"/>
+    <mergeCell ref="I2:K2"/>
+    <mergeCell ref="I30:K30"/>
+    <mergeCell ref="L30:N30"/>
+    <mergeCell ref="O30:Q30"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="AP2:AR2"/>
     <mergeCell ref="AP30:AR30"/>
@@ -5751,19 +5772,6 @@
     <mergeCell ref="F2:H2"/>
     <mergeCell ref="U2:W2"/>
     <mergeCell ref="R2:T2"/>
-    <mergeCell ref="L2:N2"/>
-    <mergeCell ref="I2:K2"/>
-    <mergeCell ref="I30:K30"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="O30:Q30"/>
-    <mergeCell ref="R30:T30"/>
-    <mergeCell ref="U30:W30"/>
-    <mergeCell ref="AM30:AO30"/>
-    <mergeCell ref="X30:Z30"/>
-    <mergeCell ref="AA30:AC30"/>
-    <mergeCell ref="AD30:AF30"/>
-    <mergeCell ref="AG30:AI30"/>
-    <mergeCell ref="AJ30:AL30"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>

--- a/activity/M01A10/M01A10_Sinuosidad.xlsx
+++ b/activity/M01A10/M01A10_Sinuosidad.xlsx
@@ -1,23 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29317"/>
   <workbookPr updateLinks="never" codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\R.HCMC\activity\M01A10\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4771DAF5-17FB-47CF-938C-3B51B5971EA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B80C7914-8491-4A74-8A64-55F55D039EBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" xr2:uid="{CB4A84EB-58A9-4828-A1EC-5E14AACD60D5}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="15675" activeTab="1" xr2:uid="{CB4A84EB-58A9-4828-A1EC-5E14AACD60D5}"/>
   </bookViews>
   <sheets>
     <sheet name="Calificacion" sheetId="12" r:id="rId1"/>
     <sheet name="Detalle" sheetId="10" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">Detalle!$B$1:$E$30</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">Detalle!$B$1:$E$36</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">Detalle!$1:$3</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="47">
   <si>
     <t>Observaciones</t>
   </si>
@@ -84,9 +84,6 @@
   </si>
   <si>
     <t>Rango ajustado en estimación lineal</t>
-  </si>
-  <si>
-    <t>Método 2: Factor de sinuosidad a partir de la longitud suavizada del valle.</t>
   </si>
   <si>
     <t>Método 3: Factor de sinuosidad a partir de la longitud euclidiana del tramo a reemplazar.</t>
@@ -177,6 +174,12 @@
   </si>
   <si>
     <t>Registrar los valores obtenidos en el libro de parámetros generales requeridos para el diseño y la modelación.</t>
+  </si>
+  <si>
+    <t>Método 2b: Factor de sinuosidad a partir de la longitud suavizada del valle.</t>
+  </si>
+  <si>
+    <t>Método 2a: Factor de sinuosidad a partir de la longitud simplificada del valle.</t>
   </si>
 </sst>
 </file>
@@ -665,6 +668,12 @@
     <xf numFmtId="164" fontId="6" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="2" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -674,11 +683,11 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="2" fontId="6" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -689,17 +698,11 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="10" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="2" fontId="10" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -2120,54 +2123,54 @@
   <sheetData>
     <row r="1" spans="2:6" x14ac:dyDescent="0.45">
       <c r="F1" s="27" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B2" s="41" t="s">
+      <c r="B2" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
+      <c r="C2" s="43"/>
+      <c r="D2" s="43"/>
+      <c r="E2" s="43"/>
+      <c r="F2" s="43"/>
     </row>
     <row r="3" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B3" s="42"/>
-      <c r="C3" s="42"/>
-      <c r="D3" s="42"/>
-      <c r="E3" s="42"/>
-      <c r="F3" s="42"/>
+      <c r="B3" s="44"/>
+      <c r="C3" s="44"/>
+      <c r="D3" s="44"/>
+      <c r="E3" s="44"/>
+      <c r="F3" s="44"/>
     </row>
     <row r="4" spans="2:6" ht="30.75" x14ac:dyDescent="0.45">
       <c r="B4" s="19" t="s">
         <v>2</v>
       </c>
       <c r="C4" s="20" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="20" t="s">
+        <v>23</v>
+      </c>
+      <c r="E4" s="20" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" s="21" t="s">
         <v>22</v>
-      </c>
-      <c r="D4" s="20" t="s">
-        <v>24</v>
-      </c>
-      <c r="E4" s="20" t="s">
-        <v>25</v>
-      </c>
-      <c r="F4" s="21" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="5" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B5" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" s="51">
+        <v>25</v>
+      </c>
+      <c r="C5" s="41">
         <v>5</v>
       </c>
       <c r="D5" s="22">
-        <f>Detalle!C30*C5/5</f>
-        <v>0</v>
-      </c>
-      <c r="E5" s="51"/>
+        <f>Detalle!C36*C5/5</f>
+        <v>0</v>
+      </c>
+      <c r="E5" s="41"/>
       <c r="F5" s="25">
         <f>AVERAGE(D5:E5)</f>
         <v>0</v>
@@ -2175,16 +2178,16 @@
     </row>
     <row r="6" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B6" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="C6" s="51">
+        <v>26</v>
+      </c>
+      <c r="C6" s="41">
         <v>5</v>
       </c>
       <c r="D6" s="22">
-        <f>Detalle!F30*C6/5</f>
-        <v>0</v>
-      </c>
-      <c r="E6" s="51"/>
+        <f>Detalle!F36*C6/5</f>
+        <v>0</v>
+      </c>
+      <c r="E6" s="41"/>
       <c r="F6" s="25">
         <f t="shared" ref="F6:F18" si="0">AVERAGE(D6:E6)</f>
         <v>0</v>
@@ -2192,16 +2195,16 @@
     </row>
     <row r="7" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B7" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="C7" s="51">
+        <v>27</v>
+      </c>
+      <c r="C7" s="41">
         <v>5</v>
       </c>
       <c r="D7" s="22">
-        <f>Detalle!I30*C7/5</f>
-        <v>0</v>
-      </c>
-      <c r="E7" s="51"/>
+        <f>Detalle!I36*C7/5</f>
+        <v>0</v>
+      </c>
+      <c r="E7" s="41"/>
       <c r="F7" s="25">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2209,16 +2212,16 @@
     </row>
     <row r="8" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B8" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="C8" s="51">
+        <v>28</v>
+      </c>
+      <c r="C8" s="41">
         <v>5</v>
       </c>
       <c r="D8" s="22">
-        <f>Detalle!L30*C8/5</f>
-        <v>0</v>
-      </c>
-      <c r="E8" s="51"/>
+        <f>Detalle!L36*C8/5</f>
+        <v>0</v>
+      </c>
+      <c r="E8" s="41"/>
       <c r="F8" s="25">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2226,16 +2229,16 @@
     </row>
     <row r="9" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B9" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="C9" s="51">
+        <v>29</v>
+      </c>
+      <c r="C9" s="41">
         <v>5</v>
       </c>
       <c r="D9" s="22">
-        <f>Detalle!O30*C9/5</f>
-        <v>0</v>
-      </c>
-      <c r="E9" s="51"/>
+        <f>Detalle!O36*C9/5</f>
+        <v>0</v>
+      </c>
+      <c r="E9" s="41"/>
       <c r="F9" s="25">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2243,16 +2246,16 @@
     </row>
     <row r="10" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B10" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="C10" s="51">
+        <v>31</v>
+      </c>
+      <c r="C10" s="41">
         <v>5</v>
       </c>
       <c r="D10" s="22">
-        <f>Detalle!R30*C10/5</f>
-        <v>0</v>
-      </c>
-      <c r="E10" s="51"/>
+        <f>Detalle!R36*C10/5</f>
+        <v>0</v>
+      </c>
+      <c r="E10" s="41"/>
       <c r="F10" s="25">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2260,16 +2263,16 @@
     </row>
     <row r="11" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B11" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="C11" s="51">
+        <v>32</v>
+      </c>
+      <c r="C11" s="41">
         <v>5</v>
       </c>
       <c r="D11" s="22">
-        <f>Detalle!U30*C11/5</f>
-        <v>0</v>
-      </c>
-      <c r="E11" s="51"/>
+        <f>Detalle!U36*C11/5</f>
+        <v>0</v>
+      </c>
+      <c r="E11" s="41"/>
       <c r="F11" s="25">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2277,16 +2280,16 @@
     </row>
     <row r="12" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B12" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="C12" s="51">
+        <v>33</v>
+      </c>
+      <c r="C12" s="41">
         <v>5</v>
       </c>
       <c r="D12" s="22">
-        <f>Detalle!X30*C12/5</f>
-        <v>0</v>
-      </c>
-      <c r="E12" s="51"/>
+        <f>Detalle!X36*C12/5</f>
+        <v>0</v>
+      </c>
+      <c r="E12" s="41"/>
       <c r="F12" s="25">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2294,16 +2297,16 @@
     </row>
     <row r="13" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B13" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="C13" s="51">
+        <v>34</v>
+      </c>
+      <c r="C13" s="41">
         <v>5</v>
       </c>
       <c r="D13" s="22">
-        <f>Detalle!AA30*C13/5</f>
-        <v>0</v>
-      </c>
-      <c r="E13" s="51"/>
+        <f>Detalle!AA36*C13/5</f>
+        <v>0</v>
+      </c>
+      <c r="E13" s="41"/>
       <c r="F13" s="25">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2311,16 +2314,16 @@
     </row>
     <row r="14" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B14" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="C14" s="51">
+        <v>35</v>
+      </c>
+      <c r="C14" s="41">
         <v>5</v>
       </c>
       <c r="D14" s="22">
-        <f>Detalle!AD30*C14/5</f>
-        <v>0</v>
-      </c>
-      <c r="E14" s="51"/>
+        <f>Detalle!AD36*C14/5</f>
+        <v>0</v>
+      </c>
+      <c r="E14" s="41"/>
       <c r="F14" s="25">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2328,16 +2331,16 @@
     </row>
     <row r="15" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B15" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="C15" s="51">
+        <v>36</v>
+      </c>
+      <c r="C15" s="41">
         <v>5</v>
       </c>
       <c r="D15" s="22">
-        <f>Detalle!AG30*C15/5</f>
-        <v>0</v>
-      </c>
-      <c r="E15" s="51"/>
+        <f>Detalle!AG36*C15/5</f>
+        <v>0</v>
+      </c>
+      <c r="E15" s="41"/>
       <c r="F15" s="25">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2345,16 +2348,16 @@
     </row>
     <row r="16" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B16" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="C16" s="51">
+        <v>37</v>
+      </c>
+      <c r="C16" s="41">
         <v>5</v>
       </c>
       <c r="D16" s="22">
-        <f>Detalle!AJ30*C16/5</f>
-        <v>0</v>
-      </c>
-      <c r="E16" s="51"/>
+        <f>Detalle!AJ36*C16/5</f>
+        <v>0</v>
+      </c>
+      <c r="E16" s="41"/>
       <c r="F16" s="25">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2362,16 +2365,16 @@
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B17" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="C17" s="51">
+        <v>38</v>
+      </c>
+      <c r="C17" s="41">
         <v>5</v>
       </c>
       <c r="D17" s="22">
-        <f>Detalle!AM30*C17/5</f>
-        <v>0</v>
-      </c>
-      <c r="E17" s="51"/>
+        <f>Detalle!AM36*C17/5</f>
+        <v>0</v>
+      </c>
+      <c r="E17" s="41"/>
       <c r="F17" s="25">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -2379,37 +2382,37 @@
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B18" s="13" t="s">
-        <v>40</v>
-      </c>
-      <c r="C18" s="52">
+        <v>39</v>
+      </c>
+      <c r="C18" s="42">
         <v>5</v>
       </c>
       <c r="D18" s="23">
-        <f>Detalle!AP30*C18/5</f>
-        <v>0</v>
-      </c>
-      <c r="E18" s="52"/>
+        <f>Detalle!AP36*C18/5</f>
+        <v>0</v>
+      </c>
+      <c r="E18" s="42"/>
       <c r="F18" s="26">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
     <row r="19" spans="2:6" ht="15.4" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B19" s="43" t="str">
+      <c r="B19" s="45" t="str">
         <f>HYPERLINK(_xlfn.CONCAT("https://github.com/rcfdtools/R.HCMC/blob/main/activity/",F1,"/Readme.md"),_xlfn.CONCAT("Ir a actividad ",F1," en GitHub."))</f>
         <v>Ir a actividad M01A10 en GitHub.</v>
       </c>
-      <c r="C19" s="43"/>
-      <c r="D19" s="43"/>
-      <c r="E19" s="43"/>
-      <c r="F19" s="43"/>
+      <c r="C19" s="45"/>
+      <c r="D19" s="45"/>
+      <c r="E19" s="45"/>
+      <c r="F19" s="45"/>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.45">
-      <c r="B20" s="43"/>
-      <c r="C20" s="43"/>
-      <c r="D20" s="43"/>
-      <c r="E20" s="43"/>
-      <c r="F20" s="43"/>
+      <c r="B20" s="45"/>
+      <c r="C20" s="45"/>
+      <c r="D20" s="45"/>
+      <c r="E20" s="45"/>
+      <c r="F20" s="45"/>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.45">
       <c r="B21" s="24"/>
@@ -2437,7 +2440,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A17987CE-896A-4E26-83D1-1610B3259376}">
   <sheetPr codeName="Hoja1"/>
-  <dimension ref="A1:AR66"/>
+  <dimension ref="A1:AR72"/>
   <sheetFormatPr defaultColWidth="11.3984375" defaultRowHeight="15.4" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="2.6640625" style="6" customWidth="1"/>
@@ -2524,96 +2527,96 @@
     </row>
     <row r="2" spans="1:44" s="3" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A2" s="6"/>
-      <c r="B2" s="44" t="s">
+      <c r="B2" s="51" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="46" t="str">
+      <c r="C2" s="48" t="str">
         <f>Calificacion!$B5</f>
         <v>Grupo 1</v>
       </c>
-      <c r="D2" s="47"/>
-      <c r="E2" s="48"/>
-      <c r="F2" s="46" t="str">
+      <c r="D2" s="49"/>
+      <c r="E2" s="50"/>
+      <c r="F2" s="48" t="str">
         <f>Calificacion!$B6</f>
         <v>Grupo 2</v>
       </c>
-      <c r="G2" s="47"/>
-      <c r="H2" s="48"/>
-      <c r="I2" s="46" t="str">
+      <c r="G2" s="49"/>
+      <c r="H2" s="50"/>
+      <c r="I2" s="48" t="str">
         <f>Calificacion!$B7</f>
         <v>Grupo 3</v>
       </c>
-      <c r="J2" s="47"/>
-      <c r="K2" s="48"/>
-      <c r="L2" s="46" t="str">
+      <c r="J2" s="49"/>
+      <c r="K2" s="50"/>
+      <c r="L2" s="48" t="str">
         <f>Calificacion!$B8</f>
         <v>Grupo 4</v>
       </c>
-      <c r="M2" s="47"/>
-      <c r="N2" s="48"/>
-      <c r="O2" s="46" t="str">
+      <c r="M2" s="49"/>
+      <c r="N2" s="50"/>
+      <c r="O2" s="48" t="str">
         <f>Calificacion!$B9</f>
         <v>Grupo 5</v>
       </c>
-      <c r="P2" s="47"/>
-      <c r="Q2" s="48"/>
-      <c r="R2" s="46" t="str">
+      <c r="P2" s="49"/>
+      <c r="Q2" s="50"/>
+      <c r="R2" s="48" t="str">
         <f>Calificacion!$B10</f>
         <v>Grupo 6</v>
       </c>
-      <c r="S2" s="47"/>
-      <c r="T2" s="48"/>
-      <c r="U2" s="46" t="str">
+      <c r="S2" s="49"/>
+      <c r="T2" s="50"/>
+      <c r="U2" s="48" t="str">
         <f>Calificacion!$B11</f>
         <v>Grupo 7</v>
       </c>
-      <c r="V2" s="47"/>
-      <c r="W2" s="48"/>
-      <c r="X2" s="46" t="str">
+      <c r="V2" s="49"/>
+      <c r="W2" s="50"/>
+      <c r="X2" s="48" t="str">
         <f>Calificacion!$B12</f>
         <v>Grupo 8</v>
       </c>
-      <c r="Y2" s="47"/>
-      <c r="Z2" s="48"/>
-      <c r="AA2" s="46" t="str">
+      <c r="Y2" s="49"/>
+      <c r="Z2" s="50"/>
+      <c r="AA2" s="48" t="str">
         <f>Calificacion!$B13</f>
         <v>Grupo 9</v>
       </c>
-      <c r="AB2" s="47"/>
-      <c r="AC2" s="48"/>
-      <c r="AD2" s="46" t="str">
+      <c r="AB2" s="49"/>
+      <c r="AC2" s="50"/>
+      <c r="AD2" s="48" t="str">
         <f>Calificacion!$B14</f>
         <v>Grupo 10</v>
       </c>
-      <c r="AE2" s="47"/>
-      <c r="AF2" s="48"/>
-      <c r="AG2" s="46" t="str">
+      <c r="AE2" s="49"/>
+      <c r="AF2" s="50"/>
+      <c r="AG2" s="48" t="str">
         <f>Calificacion!$B15</f>
         <v>Grupo 11</v>
       </c>
-      <c r="AH2" s="47"/>
-      <c r="AI2" s="48"/>
-      <c r="AJ2" s="46" t="str">
+      <c r="AH2" s="49"/>
+      <c r="AI2" s="50"/>
+      <c r="AJ2" s="48" t="str">
         <f>Calificacion!$B16</f>
         <v>Grupo 12</v>
       </c>
-      <c r="AK2" s="47"/>
-      <c r="AL2" s="48"/>
-      <c r="AM2" s="46" t="str">
+      <c r="AK2" s="49"/>
+      <c r="AL2" s="50"/>
+      <c r="AM2" s="48" t="str">
         <f>Calificacion!$B17</f>
         <v>Grupo 13</v>
       </c>
-      <c r="AN2" s="47"/>
-      <c r="AO2" s="48"/>
-      <c r="AP2" s="46" t="str">
+      <c r="AN2" s="49"/>
+      <c r="AO2" s="50"/>
+      <c r="AP2" s="48" t="str">
         <f>Calificacion!$B18</f>
         <v>Grupo 14</v>
       </c>
-      <c r="AQ2" s="47"/>
-      <c r="AR2" s="48"/>
+      <c r="AQ2" s="49"/>
+      <c r="AR2" s="50"/>
     </row>
     <row r="3" spans="1:44" x14ac:dyDescent="0.45">
-      <c r="B3" s="45"/>
+      <c r="B3" s="52"/>
       <c r="C3" s="7" t="s">
         <v>1</v>
       </c>
@@ -2743,7 +2746,7 @@
     </row>
     <row r="4" spans="1:44" ht="30.75" x14ac:dyDescent="0.45">
       <c r="B4" s="10" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C4" s="29">
         <v>0</v>
@@ -3053,7 +3056,7 @@
     </row>
     <row r="10" spans="1:44" ht="30.75" x14ac:dyDescent="0.45">
       <c r="B10" s="17" t="s">
-        <v>15</v>
+        <v>46</v>
       </c>
       <c r="C10" s="29"/>
       <c r="D10" s="30"/>
@@ -3100,7 +3103,7 @@
     </row>
     <row r="11" spans="1:44" x14ac:dyDescent="0.45">
       <c r="B11" s="18" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C11" s="29"/>
       <c r="D11" s="30"/>
@@ -3335,7 +3338,7 @@
     </row>
     <row r="16" spans="1:44" ht="30.75" x14ac:dyDescent="0.45">
       <c r="B16" s="17" t="s">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="C16" s="29"/>
       <c r="D16" s="30"/>
@@ -3380,56 +3383,56 @@
       <c r="AQ16" s="30"/>
       <c r="AR16" s="31"/>
     </row>
-    <row r="17" spans="1:44" x14ac:dyDescent="0.45">
+    <row r="17" spans="2:44" x14ac:dyDescent="0.45">
       <c r="B17" s="18" t="s">
-        <v>20</v>
+        <v>41</v>
       </c>
       <c r="C17" s="29"/>
-      <c r="D17" s="33"/>
+      <c r="D17" s="30"/>
       <c r="E17" s="31"/>
       <c r="F17" s="29"/>
-      <c r="G17" s="33"/>
+      <c r="G17" s="30"/>
       <c r="H17" s="31"/>
       <c r="I17" s="29"/>
-      <c r="J17" s="33"/>
+      <c r="J17" s="30"/>
       <c r="K17" s="31"/>
       <c r="L17" s="29"/>
-      <c r="M17" s="33"/>
+      <c r="M17" s="30"/>
       <c r="N17" s="31"/>
       <c r="O17" s="29"/>
-      <c r="P17" s="33"/>
+      <c r="P17" s="30"/>
       <c r="Q17" s="31"/>
       <c r="R17" s="29"/>
-      <c r="S17" s="33"/>
+      <c r="S17" s="30"/>
       <c r="T17" s="31"/>
       <c r="U17" s="29"/>
-      <c r="V17" s="33"/>
+      <c r="V17" s="30"/>
       <c r="W17" s="31"/>
       <c r="X17" s="29"/>
-      <c r="Y17" s="33"/>
+      <c r="Y17" s="30"/>
       <c r="Z17" s="31"/>
       <c r="AA17" s="29"/>
-      <c r="AB17" s="33"/>
+      <c r="AB17" s="30"/>
       <c r="AC17" s="31"/>
       <c r="AD17" s="29"/>
-      <c r="AE17" s="33"/>
+      <c r="AE17" s="30"/>
       <c r="AF17" s="31"/>
       <c r="AG17" s="29"/>
-      <c r="AH17" s="33"/>
+      <c r="AH17" s="30"/>
       <c r="AI17" s="31"/>
       <c r="AJ17" s="29"/>
-      <c r="AK17" s="33"/>
+      <c r="AK17" s="30"/>
       <c r="AL17" s="31"/>
       <c r="AM17" s="29"/>
-      <c r="AN17" s="33"/>
+      <c r="AN17" s="30"/>
       <c r="AO17" s="31"/>
       <c r="AP17" s="29"/>
-      <c r="AQ17" s="33"/>
+      <c r="AQ17" s="30"/>
       <c r="AR17" s="31"/>
     </row>
-    <row r="18" spans="1:44" x14ac:dyDescent="0.45">
+    <row r="18" spans="2:44" x14ac:dyDescent="0.45">
       <c r="B18" s="18" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C18" s="29"/>
       <c r="D18" s="30"/>
@@ -3474,9 +3477,9 @@
       <c r="AQ18" s="30"/>
       <c r="AR18" s="31"/>
     </row>
-    <row r="19" spans="1:44" x14ac:dyDescent="0.45">
+    <row r="19" spans="2:44" x14ac:dyDescent="0.45">
       <c r="B19" s="18" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C19" s="29"/>
       <c r="D19" s="30"/>
@@ -3521,98 +3524,56 @@
       <c r="AQ19" s="30"/>
       <c r="AR19" s="31"/>
     </row>
-    <row r="20" spans="1:44" x14ac:dyDescent="0.45">
+    <row r="20" spans="2:44" x14ac:dyDescent="0.45">
       <c r="B20" s="18" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="C20" s="29"/>
-      <c r="D20" s="35" t="e">
-        <f>D18/D19</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="E20" s="34"/>
+      <c r="D20" s="32"/>
+      <c r="E20" s="31"/>
       <c r="F20" s="29"/>
-      <c r="G20" s="35" t="e">
-        <f>G18/G19</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="H20" s="34"/>
+      <c r="G20" s="32"/>
+      <c r="H20" s="31"/>
       <c r="I20" s="29"/>
-      <c r="J20" s="35" t="e">
-        <f>J18/J19</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="K20" s="34"/>
+      <c r="J20" s="32"/>
+      <c r="K20" s="31"/>
       <c r="L20" s="29"/>
-      <c r="M20" s="35" t="e">
-        <f>M18/M19</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="N20" s="34"/>
+      <c r="M20" s="32"/>
+      <c r="N20" s="31"/>
       <c r="O20" s="29"/>
-      <c r="P20" s="35" t="e">
-        <f>P18/P19</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Q20" s="34"/>
+      <c r="P20" s="32"/>
+      <c r="Q20" s="31"/>
       <c r="R20" s="29"/>
-      <c r="S20" s="35" t="e">
-        <f>S18/S19</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="T20" s="34"/>
+      <c r="S20" s="32"/>
+      <c r="T20" s="31"/>
       <c r="U20" s="29"/>
-      <c r="V20" s="35" t="e">
-        <f>V18/V19</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="W20" s="34"/>
+      <c r="V20" s="32"/>
+      <c r="W20" s="31"/>
       <c r="X20" s="29"/>
-      <c r="Y20" s="35" t="e">
-        <f>Y18/Y19</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="Z20" s="34"/>
+      <c r="Y20" s="32"/>
+      <c r="Z20" s="31"/>
       <c r="AA20" s="29"/>
-      <c r="AB20" s="35" t="e">
-        <f>AB18/AB19</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AC20" s="34"/>
+      <c r="AB20" s="32"/>
+      <c r="AC20" s="31"/>
       <c r="AD20" s="29"/>
-      <c r="AE20" s="35" t="e">
-        <f>AE18/AE19</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AF20" s="34"/>
+      <c r="AE20" s="32"/>
+      <c r="AF20" s="31"/>
       <c r="AG20" s="29"/>
-      <c r="AH20" s="35" t="e">
-        <f>AH18/AH19</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AI20" s="34"/>
+      <c r="AH20" s="32"/>
+      <c r="AI20" s="31"/>
       <c r="AJ20" s="29"/>
-      <c r="AK20" s="35" t="e">
-        <f>AK18/AK19</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AL20" s="34"/>
+      <c r="AK20" s="32"/>
+      <c r="AL20" s="31"/>
       <c r="AM20" s="29"/>
-      <c r="AN20" s="35" t="e">
-        <f>AN18/AN19</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AO20" s="34"/>
+      <c r="AN20" s="32"/>
+      <c r="AO20" s="31"/>
       <c r="AP20" s="29"/>
-      <c r="AQ20" s="35" t="e">
-        <f>AQ18/AQ19</f>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="AR20" s="34"/>
-    </row>
-    <row r="21" spans="1:44" x14ac:dyDescent="0.45">
-      <c r="B21" s="17" t="s">
-        <v>17</v>
+      <c r="AQ20" s="32"/>
+      <c r="AR20" s="31"/>
+    </row>
+    <row r="21" spans="2:44" x14ac:dyDescent="0.45">
+      <c r="B21" s="18" t="s">
+        <v>14</v>
       </c>
       <c r="C21" s="29"/>
       <c r="D21" s="30"/>
@@ -3657,103 +3618,103 @@
       <c r="AQ21" s="30"/>
       <c r="AR21" s="31"/>
     </row>
-    <row r="22" spans="1:44" ht="61.5" x14ac:dyDescent="0.45">
-      <c r="B22" s="18" t="s">
-        <v>44</v>
+    <row r="22" spans="2:44" ht="30.75" x14ac:dyDescent="0.45">
+      <c r="B22" s="17" t="s">
+        <v>15</v>
       </c>
       <c r="C22" s="29"/>
-      <c r="D22" s="32"/>
+      <c r="D22" s="30"/>
       <c r="E22" s="31"/>
       <c r="F22" s="29"/>
-      <c r="G22" s="32"/>
+      <c r="G22" s="30"/>
       <c r="H22" s="31"/>
       <c r="I22" s="29"/>
-      <c r="J22" s="32"/>
+      <c r="J22" s="30"/>
       <c r="K22" s="31"/>
       <c r="L22" s="29"/>
-      <c r="M22" s="32"/>
+      <c r="M22" s="30"/>
       <c r="N22" s="31"/>
       <c r="O22" s="29"/>
-      <c r="P22" s="32"/>
+      <c r="P22" s="30"/>
       <c r="Q22" s="31"/>
       <c r="R22" s="29"/>
-      <c r="S22" s="32"/>
+      <c r="S22" s="30"/>
       <c r="T22" s="31"/>
       <c r="U22" s="29"/>
-      <c r="V22" s="32"/>
+      <c r="V22" s="30"/>
       <c r="W22" s="31"/>
       <c r="X22" s="29"/>
-      <c r="Y22" s="32"/>
+      <c r="Y22" s="30"/>
       <c r="Z22" s="31"/>
       <c r="AA22" s="29"/>
-      <c r="AB22" s="32"/>
+      <c r="AB22" s="30"/>
       <c r="AC22" s="31"/>
       <c r="AD22" s="29"/>
-      <c r="AE22" s="32"/>
+      <c r="AE22" s="30"/>
       <c r="AF22" s="31"/>
       <c r="AG22" s="29"/>
-      <c r="AH22" s="32"/>
+      <c r="AH22" s="30"/>
       <c r="AI22" s="31"/>
       <c r="AJ22" s="29"/>
-      <c r="AK22" s="32"/>
+      <c r="AK22" s="30"/>
       <c r="AL22" s="31"/>
       <c r="AM22" s="29"/>
-      <c r="AN22" s="32"/>
+      <c r="AN22" s="30"/>
       <c r="AO22" s="31"/>
       <c r="AP22" s="29"/>
-      <c r="AQ22" s="32"/>
+      <c r="AQ22" s="30"/>
       <c r="AR22" s="31"/>
     </row>
-    <row r="23" spans="1:44" ht="30.75" x14ac:dyDescent="0.45">
+    <row r="23" spans="2:44" x14ac:dyDescent="0.45">
       <c r="B23" s="18" t="s">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="C23" s="29"/>
-      <c r="D23" s="32"/>
+      <c r="D23" s="33"/>
       <c r="E23" s="31"/>
       <c r="F23" s="29"/>
-      <c r="G23" s="32"/>
+      <c r="G23" s="33"/>
       <c r="H23" s="31"/>
       <c r="I23" s="29"/>
-      <c r="J23" s="32"/>
+      <c r="J23" s="33"/>
       <c r="K23" s="31"/>
       <c r="L23" s="29"/>
-      <c r="M23" s="32"/>
+      <c r="M23" s="33"/>
       <c r="N23" s="31"/>
       <c r="O23" s="29"/>
-      <c r="P23" s="32"/>
+      <c r="P23" s="33"/>
       <c r="Q23" s="31"/>
       <c r="R23" s="29"/>
-      <c r="S23" s="32"/>
+      <c r="S23" s="33"/>
       <c r="T23" s="31"/>
       <c r="U23" s="29"/>
-      <c r="V23" s="32"/>
+      <c r="V23" s="33"/>
       <c r="W23" s="31"/>
       <c r="X23" s="29"/>
-      <c r="Y23" s="32"/>
+      <c r="Y23" s="33"/>
       <c r="Z23" s="31"/>
       <c r="AA23" s="29"/>
-      <c r="AB23" s="32"/>
+      <c r="AB23" s="33"/>
       <c r="AC23" s="31"/>
       <c r="AD23" s="29"/>
-      <c r="AE23" s="32"/>
+      <c r="AE23" s="33"/>
       <c r="AF23" s="31"/>
       <c r="AG23" s="29"/>
-      <c r="AH23" s="32"/>
+      <c r="AH23" s="33"/>
       <c r="AI23" s="31"/>
       <c r="AJ23" s="29"/>
-      <c r="AK23" s="32"/>
+      <c r="AK23" s="33"/>
       <c r="AL23" s="31"/>
       <c r="AM23" s="29"/>
-      <c r="AN23" s="32"/>
+      <c r="AN23" s="33"/>
       <c r="AO23" s="31"/>
       <c r="AP23" s="29"/>
-      <c r="AQ23" s="32"/>
+      <c r="AQ23" s="33"/>
       <c r="AR23" s="31"/>
     </row>
-    <row r="24" spans="1:44" x14ac:dyDescent="0.45">
+    <row r="24" spans="2:44" x14ac:dyDescent="0.45">
       <c r="B24" s="18" t="s">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="C24" s="29"/>
       <c r="D24" s="30"/>
@@ -3798,9 +3759,9 @@
       <c r="AQ24" s="30"/>
       <c r="AR24" s="31"/>
     </row>
-    <row r="25" spans="1:44" ht="48.95" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="2:44" x14ac:dyDescent="0.45">
       <c r="B25" s="18" t="s">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="C25" s="29"/>
       <c r="D25" s="30"/>
@@ -3845,56 +3806,98 @@
       <c r="AQ25" s="30"/>
       <c r="AR25" s="31"/>
     </row>
-    <row r="26" spans="1:44" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="2:44" x14ac:dyDescent="0.45">
       <c r="B26" s="18" t="s">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="C26" s="29"/>
-      <c r="D26" s="30"/>
-      <c r="E26" s="31"/>
+      <c r="D26" s="35" t="e">
+        <f>D24/D25</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="E26" s="34"/>
       <c r="F26" s="29"/>
-      <c r="G26" s="30"/>
-      <c r="H26" s="31"/>
+      <c r="G26" s="35" t="e">
+        <f>G24/G25</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="H26" s="34"/>
       <c r="I26" s="29"/>
-      <c r="J26" s="30"/>
-      <c r="K26" s="31"/>
+      <c r="J26" s="35" t="e">
+        <f>J24/J25</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="K26" s="34"/>
       <c r="L26" s="29"/>
-      <c r="M26" s="30"/>
-      <c r="N26" s="31"/>
+      <c r="M26" s="35" t="e">
+        <f>M24/M25</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N26" s="34"/>
       <c r="O26" s="29"/>
-      <c r="P26" s="30"/>
-      <c r="Q26" s="31"/>
+      <c r="P26" s="35" t="e">
+        <f>P24/P25</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Q26" s="34"/>
       <c r="R26" s="29"/>
-      <c r="S26" s="30"/>
-      <c r="T26" s="31"/>
+      <c r="S26" s="35" t="e">
+        <f>S24/S25</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="T26" s="34"/>
       <c r="U26" s="29"/>
-      <c r="V26" s="30"/>
-      <c r="W26" s="31"/>
+      <c r="V26" s="35" t="e">
+        <f>V24/V25</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="W26" s="34"/>
       <c r="X26" s="29"/>
-      <c r="Y26" s="30"/>
-      <c r="Z26" s="31"/>
+      <c r="Y26" s="35" t="e">
+        <f>Y24/Y25</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Z26" s="34"/>
       <c r="AA26" s="29"/>
-      <c r="AB26" s="30"/>
-      <c r="AC26" s="31"/>
+      <c r="AB26" s="35" t="e">
+        <f>AB24/AB25</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AC26" s="34"/>
       <c r="AD26" s="29"/>
-      <c r="AE26" s="30"/>
-      <c r="AF26" s="31"/>
+      <c r="AE26" s="35" t="e">
+        <f>AE24/AE25</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AF26" s="34"/>
       <c r="AG26" s="29"/>
-      <c r="AH26" s="30"/>
-      <c r="AI26" s="31"/>
+      <c r="AH26" s="35" t="e">
+        <f>AH24/AH25</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AI26" s="34"/>
       <c r="AJ26" s="29"/>
-      <c r="AK26" s="30"/>
-      <c r="AL26" s="31"/>
+      <c r="AK26" s="35" t="e">
+        <f>AK24/AK25</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AL26" s="34"/>
       <c r="AM26" s="29"/>
-      <c r="AN26" s="30"/>
-      <c r="AO26" s="31"/>
+      <c r="AN26" s="35" t="e">
+        <f>AN24/AN25</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AO26" s="34"/>
       <c r="AP26" s="29"/>
-      <c r="AQ26" s="30"/>
-      <c r="AR26" s="31"/>
-    </row>
-    <row r="27" spans="1:44" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="B27" s="18" t="s">
-        <v>45</v>
+      <c r="AQ26" s="35" t="e">
+        <f>AQ24/AQ25</f>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="AR26" s="34"/>
+    </row>
+    <row r="27" spans="2:44" x14ac:dyDescent="0.45">
+      <c r="B27" s="17" t="s">
+        <v>16</v>
       </c>
       <c r="C27" s="29"/>
       <c r="D27" s="30"/>
@@ -3939,460 +3942,472 @@
       <c r="AQ27" s="30"/>
       <c r="AR27" s="31"/>
     </row>
-    <row r="28" spans="1:44" ht="76.900000000000006" x14ac:dyDescent="0.45">
+    <row r="28" spans="2:44" ht="61.5" x14ac:dyDescent="0.45">
       <c r="B28" s="18" t="s">
         <v>43</v>
       </c>
       <c r="C28" s="29"/>
-      <c r="D28" s="30"/>
+      <c r="D28" s="32"/>
       <c r="E28" s="31"/>
       <c r="F28" s="29"/>
-      <c r="G28" s="30"/>
+      <c r="G28" s="32"/>
       <c r="H28" s="31"/>
       <c r="I28" s="29"/>
-      <c r="J28" s="30"/>
+      <c r="J28" s="32"/>
       <c r="K28" s="31"/>
       <c r="L28" s="29"/>
-      <c r="M28" s="30"/>
+      <c r="M28" s="32"/>
       <c r="N28" s="31"/>
       <c r="O28" s="29"/>
-      <c r="P28" s="30"/>
+      <c r="P28" s="32"/>
       <c r="Q28" s="31"/>
       <c r="R28" s="29"/>
-      <c r="S28" s="30"/>
+      <c r="S28" s="32"/>
       <c r="T28" s="31"/>
       <c r="U28" s="29"/>
-      <c r="V28" s="30"/>
+      <c r="V28" s="32"/>
       <c r="W28" s="31"/>
       <c r="X28" s="29"/>
-      <c r="Y28" s="30"/>
+      <c r="Y28" s="32"/>
       <c r="Z28" s="31"/>
       <c r="AA28" s="29"/>
-      <c r="AB28" s="30"/>
+      <c r="AB28" s="32"/>
       <c r="AC28" s="31"/>
       <c r="AD28" s="29"/>
-      <c r="AE28" s="30"/>
+      <c r="AE28" s="32"/>
       <c r="AF28" s="31"/>
       <c r="AG28" s="29"/>
-      <c r="AH28" s="30"/>
+      <c r="AH28" s="32"/>
       <c r="AI28" s="31"/>
       <c r="AJ28" s="29"/>
-      <c r="AK28" s="30"/>
+      <c r="AK28" s="32"/>
       <c r="AL28" s="31"/>
       <c r="AM28" s="29"/>
-      <c r="AN28" s="30"/>
+      <c r="AN28" s="32"/>
       <c r="AO28" s="31"/>
       <c r="AP28" s="29"/>
-      <c r="AQ28" s="30"/>
+      <c r="AQ28" s="32"/>
       <c r="AR28" s="31"/>
     </row>
-    <row r="29" spans="1:44" x14ac:dyDescent="0.45">
-      <c r="B29" s="36"/>
-      <c r="C29" s="37"/>
-      <c r="D29" s="38"/>
-      <c r="E29" s="39"/>
-      <c r="F29" s="37"/>
-      <c r="G29" s="38"/>
-      <c r="H29" s="39"/>
-      <c r="I29" s="37"/>
-      <c r="J29" s="38"/>
-      <c r="K29" s="39"/>
-      <c r="L29" s="37"/>
-      <c r="M29" s="38"/>
-      <c r="N29" s="39"/>
-      <c r="O29" s="37"/>
-      <c r="P29" s="38"/>
-      <c r="Q29" s="39"/>
-      <c r="R29" s="37"/>
-      <c r="S29" s="38"/>
-      <c r="T29" s="39"/>
-      <c r="U29" s="37"/>
-      <c r="V29" s="38"/>
-      <c r="W29" s="39"/>
-      <c r="X29" s="37"/>
-      <c r="Y29" s="38"/>
-      <c r="Z29" s="39"/>
-      <c r="AA29" s="37"/>
-      <c r="AB29" s="38"/>
-      <c r="AC29" s="39"/>
-      <c r="AD29" s="37"/>
-      <c r="AE29" s="38"/>
-      <c r="AF29" s="39"/>
-      <c r="AG29" s="37"/>
-      <c r="AH29" s="38"/>
-      <c r="AI29" s="39"/>
-      <c r="AJ29" s="37"/>
-      <c r="AK29" s="38"/>
-      <c r="AL29" s="39"/>
-      <c r="AM29" s="37"/>
-      <c r="AN29" s="38"/>
-      <c r="AO29" s="39"/>
-      <c r="AP29" s="37"/>
-      <c r="AQ29" s="38"/>
-      <c r="AR29" s="39"/>
-    </row>
-    <row r="30" spans="1:44" s="2" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A30" s="1"/>
-      <c r="B30" s="40" t="s">
+    <row r="29" spans="2:44" ht="30.75" x14ac:dyDescent="0.45">
+      <c r="B29" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="29"/>
+      <c r="D29" s="32"/>
+      <c r="E29" s="31"/>
+      <c r="F29" s="29"/>
+      <c r="G29" s="32"/>
+      <c r="H29" s="31"/>
+      <c r="I29" s="29"/>
+      <c r="J29" s="32"/>
+      <c r="K29" s="31"/>
+      <c r="L29" s="29"/>
+      <c r="M29" s="32"/>
+      <c r="N29" s="31"/>
+      <c r="O29" s="29"/>
+      <c r="P29" s="32"/>
+      <c r="Q29" s="31"/>
+      <c r="R29" s="29"/>
+      <c r="S29" s="32"/>
+      <c r="T29" s="31"/>
+      <c r="U29" s="29"/>
+      <c r="V29" s="32"/>
+      <c r="W29" s="31"/>
+      <c r="X29" s="29"/>
+      <c r="Y29" s="32"/>
+      <c r="Z29" s="31"/>
+      <c r="AA29" s="29"/>
+      <c r="AB29" s="32"/>
+      <c r="AC29" s="31"/>
+      <c r="AD29" s="29"/>
+      <c r="AE29" s="32"/>
+      <c r="AF29" s="31"/>
+      <c r="AG29" s="29"/>
+      <c r="AH29" s="32"/>
+      <c r="AI29" s="31"/>
+      <c r="AJ29" s="29"/>
+      <c r="AK29" s="32"/>
+      <c r="AL29" s="31"/>
+      <c r="AM29" s="29"/>
+      <c r="AN29" s="32"/>
+      <c r="AO29" s="31"/>
+      <c r="AP29" s="29"/>
+      <c r="AQ29" s="32"/>
+      <c r="AR29" s="31"/>
+    </row>
+    <row r="30" spans="2:44" x14ac:dyDescent="0.45">
+      <c r="B30" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="C30" s="29"/>
+      <c r="D30" s="30"/>
+      <c r="E30" s="31"/>
+      <c r="F30" s="29"/>
+      <c r="G30" s="30"/>
+      <c r="H30" s="31"/>
+      <c r="I30" s="29"/>
+      <c r="J30" s="30"/>
+      <c r="K30" s="31"/>
+      <c r="L30" s="29"/>
+      <c r="M30" s="30"/>
+      <c r="N30" s="31"/>
+      <c r="O30" s="29"/>
+      <c r="P30" s="30"/>
+      <c r="Q30" s="31"/>
+      <c r="R30" s="29"/>
+      <c r="S30" s="30"/>
+      <c r="T30" s="31"/>
+      <c r="U30" s="29"/>
+      <c r="V30" s="30"/>
+      <c r="W30" s="31"/>
+      <c r="X30" s="29"/>
+      <c r="Y30" s="30"/>
+      <c r="Z30" s="31"/>
+      <c r="AA30" s="29"/>
+      <c r="AB30" s="30"/>
+      <c r="AC30" s="31"/>
+      <c r="AD30" s="29"/>
+      <c r="AE30" s="30"/>
+      <c r="AF30" s="31"/>
+      <c r="AG30" s="29"/>
+      <c r="AH30" s="30"/>
+      <c r="AI30" s="31"/>
+      <c r="AJ30" s="29"/>
+      <c r="AK30" s="30"/>
+      <c r="AL30" s="31"/>
+      <c r="AM30" s="29"/>
+      <c r="AN30" s="30"/>
+      <c r="AO30" s="31"/>
+      <c r="AP30" s="29"/>
+      <c r="AQ30" s="30"/>
+      <c r="AR30" s="31"/>
+    </row>
+    <row r="31" spans="2:44" ht="48.95" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B31" s="18" t="s">
+        <v>8</v>
+      </c>
+      <c r="C31" s="29"/>
+      <c r="D31" s="30"/>
+      <c r="E31" s="31"/>
+      <c r="F31" s="29"/>
+      <c r="G31" s="30"/>
+      <c r="H31" s="31"/>
+      <c r="I31" s="29"/>
+      <c r="J31" s="30"/>
+      <c r="K31" s="31"/>
+      <c r="L31" s="29"/>
+      <c r="M31" s="30"/>
+      <c r="N31" s="31"/>
+      <c r="O31" s="29"/>
+      <c r="P31" s="30"/>
+      <c r="Q31" s="31"/>
+      <c r="R31" s="29"/>
+      <c r="S31" s="30"/>
+      <c r="T31" s="31"/>
+      <c r="U31" s="29"/>
+      <c r="V31" s="30"/>
+      <c r="W31" s="31"/>
+      <c r="X31" s="29"/>
+      <c r="Y31" s="30"/>
+      <c r="Z31" s="31"/>
+      <c r="AA31" s="29"/>
+      <c r="AB31" s="30"/>
+      <c r="AC31" s="31"/>
+      <c r="AD31" s="29"/>
+      <c r="AE31" s="30"/>
+      <c r="AF31" s="31"/>
+      <c r="AG31" s="29"/>
+      <c r="AH31" s="30"/>
+      <c r="AI31" s="31"/>
+      <c r="AJ31" s="29"/>
+      <c r="AK31" s="30"/>
+      <c r="AL31" s="31"/>
+      <c r="AM31" s="29"/>
+      <c r="AN31" s="30"/>
+      <c r="AO31" s="31"/>
+      <c r="AP31" s="29"/>
+      <c r="AQ31" s="30"/>
+      <c r="AR31" s="31"/>
+    </row>
+    <row r="32" spans="2:44" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B32" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="C32" s="29"/>
+      <c r="D32" s="30"/>
+      <c r="E32" s="31"/>
+      <c r="F32" s="29"/>
+      <c r="G32" s="30"/>
+      <c r="H32" s="31"/>
+      <c r="I32" s="29"/>
+      <c r="J32" s="30"/>
+      <c r="K32" s="31"/>
+      <c r="L32" s="29"/>
+      <c r="M32" s="30"/>
+      <c r="N32" s="31"/>
+      <c r="O32" s="29"/>
+      <c r="P32" s="30"/>
+      <c r="Q32" s="31"/>
+      <c r="R32" s="29"/>
+      <c r="S32" s="30"/>
+      <c r="T32" s="31"/>
+      <c r="U32" s="29"/>
+      <c r="V32" s="30"/>
+      <c r="W32" s="31"/>
+      <c r="X32" s="29"/>
+      <c r="Y32" s="30"/>
+      <c r="Z32" s="31"/>
+      <c r="AA32" s="29"/>
+      <c r="AB32" s="30"/>
+      <c r="AC32" s="31"/>
+      <c r="AD32" s="29"/>
+      <c r="AE32" s="30"/>
+      <c r="AF32" s="31"/>
+      <c r="AG32" s="29"/>
+      <c r="AH32" s="30"/>
+      <c r="AI32" s="31"/>
+      <c r="AJ32" s="29"/>
+      <c r="AK32" s="30"/>
+      <c r="AL32" s="31"/>
+      <c r="AM32" s="29"/>
+      <c r="AN32" s="30"/>
+      <c r="AO32" s="31"/>
+      <c r="AP32" s="29"/>
+      <c r="AQ32" s="30"/>
+      <c r="AR32" s="31"/>
+    </row>
+    <row r="33" spans="1:44" ht="33.950000000000003" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="B33" s="18" t="s">
+        <v>44</v>
+      </c>
+      <c r="C33" s="29"/>
+      <c r="D33" s="30"/>
+      <c r="E33" s="31"/>
+      <c r="F33" s="29"/>
+      <c r="G33" s="30"/>
+      <c r="H33" s="31"/>
+      <c r="I33" s="29"/>
+      <c r="J33" s="30"/>
+      <c r="K33" s="31"/>
+      <c r="L33" s="29"/>
+      <c r="M33" s="30"/>
+      <c r="N33" s="31"/>
+      <c r="O33" s="29"/>
+      <c r="P33" s="30"/>
+      <c r="Q33" s="31"/>
+      <c r="R33" s="29"/>
+      <c r="S33" s="30"/>
+      <c r="T33" s="31"/>
+      <c r="U33" s="29"/>
+      <c r="V33" s="30"/>
+      <c r="W33" s="31"/>
+      <c r="X33" s="29"/>
+      <c r="Y33" s="30"/>
+      <c r="Z33" s="31"/>
+      <c r="AA33" s="29"/>
+      <c r="AB33" s="30"/>
+      <c r="AC33" s="31"/>
+      <c r="AD33" s="29"/>
+      <c r="AE33" s="30"/>
+      <c r="AF33" s="31"/>
+      <c r="AG33" s="29"/>
+      <c r="AH33" s="30"/>
+      <c r="AI33" s="31"/>
+      <c r="AJ33" s="29"/>
+      <c r="AK33" s="30"/>
+      <c r="AL33" s="31"/>
+      <c r="AM33" s="29"/>
+      <c r="AN33" s="30"/>
+      <c r="AO33" s="31"/>
+      <c r="AP33" s="29"/>
+      <c r="AQ33" s="30"/>
+      <c r="AR33" s="31"/>
+    </row>
+    <row r="34" spans="1:44" ht="76.900000000000006" x14ac:dyDescent="0.45">
+      <c r="B34" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="C34" s="29"/>
+      <c r="D34" s="30"/>
+      <c r="E34" s="31"/>
+      <c r="F34" s="29"/>
+      <c r="G34" s="30"/>
+      <c r="H34" s="31"/>
+      <c r="I34" s="29"/>
+      <c r="J34" s="30"/>
+      <c r="K34" s="31"/>
+      <c r="L34" s="29"/>
+      <c r="M34" s="30"/>
+      <c r="N34" s="31"/>
+      <c r="O34" s="29"/>
+      <c r="P34" s="30"/>
+      <c r="Q34" s="31"/>
+      <c r="R34" s="29"/>
+      <c r="S34" s="30"/>
+      <c r="T34" s="31"/>
+      <c r="U34" s="29"/>
+      <c r="V34" s="30"/>
+      <c r="W34" s="31"/>
+      <c r="X34" s="29"/>
+      <c r="Y34" s="30"/>
+      <c r="Z34" s="31"/>
+      <c r="AA34" s="29"/>
+      <c r="AB34" s="30"/>
+      <c r="AC34" s="31"/>
+      <c r="AD34" s="29"/>
+      <c r="AE34" s="30"/>
+      <c r="AF34" s="31"/>
+      <c r="AG34" s="29"/>
+      <c r="AH34" s="30"/>
+      <c r="AI34" s="31"/>
+      <c r="AJ34" s="29"/>
+      <c r="AK34" s="30"/>
+      <c r="AL34" s="31"/>
+      <c r="AM34" s="29"/>
+      <c r="AN34" s="30"/>
+      <c r="AO34" s="31"/>
+      <c r="AP34" s="29"/>
+      <c r="AQ34" s="30"/>
+      <c r="AR34" s="31"/>
+    </row>
+    <row r="35" spans="1:44" x14ac:dyDescent="0.45">
+      <c r="B35" s="36"/>
+      <c r="C35" s="37"/>
+      <c r="D35" s="38"/>
+      <c r="E35" s="39"/>
+      <c r="F35" s="37"/>
+      <c r="G35" s="38"/>
+      <c r="H35" s="39"/>
+      <c r="I35" s="37"/>
+      <c r="J35" s="38"/>
+      <c r="K35" s="39"/>
+      <c r="L35" s="37"/>
+      <c r="M35" s="38"/>
+      <c r="N35" s="39"/>
+      <c r="O35" s="37"/>
+      <c r="P35" s="38"/>
+      <c r="Q35" s="39"/>
+      <c r="R35" s="37"/>
+      <c r="S35" s="38"/>
+      <c r="T35" s="39"/>
+      <c r="U35" s="37"/>
+      <c r="V35" s="38"/>
+      <c r="W35" s="39"/>
+      <c r="X35" s="37"/>
+      <c r="Y35" s="38"/>
+      <c r="Z35" s="39"/>
+      <c r="AA35" s="37"/>
+      <c r="AB35" s="38"/>
+      <c r="AC35" s="39"/>
+      <c r="AD35" s="37"/>
+      <c r="AE35" s="38"/>
+      <c r="AF35" s="39"/>
+      <c r="AG35" s="37"/>
+      <c r="AH35" s="38"/>
+      <c r="AI35" s="39"/>
+      <c r="AJ35" s="37"/>
+      <c r="AK35" s="38"/>
+      <c r="AL35" s="39"/>
+      <c r="AM35" s="37"/>
+      <c r="AN35" s="38"/>
+      <c r="AO35" s="39"/>
+      <c r="AP35" s="37"/>
+      <c r="AQ35" s="38"/>
+      <c r="AR35" s="39"/>
+    </row>
+    <row r="36" spans="1:44" s="2" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A36" s="1"/>
+      <c r="B36" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="C30" s="49">
-        <f>AVERAGE(C4:C29)</f>
-        <v>0</v>
-      </c>
-      <c r="D30" s="49"/>
-      <c r="E30" s="50"/>
-      <c r="F30" s="49">
-        <f>AVERAGE(F4:F29)</f>
-        <v>0</v>
-      </c>
-      <c r="G30" s="49"/>
-      <c r="H30" s="50"/>
-      <c r="I30" s="49">
-        <f>AVERAGE(I4:I29)</f>
-        <v>0</v>
-      </c>
-      <c r="J30" s="49"/>
-      <c r="K30" s="50"/>
-      <c r="L30" s="49">
-        <f>AVERAGE(L4:L29)</f>
-        <v>0</v>
-      </c>
-      <c r="M30" s="49"/>
-      <c r="N30" s="50"/>
-      <c r="O30" s="49">
-        <f>AVERAGE(O4:O29)</f>
-        <v>0</v>
-      </c>
-      <c r="P30" s="49"/>
-      <c r="Q30" s="50"/>
-      <c r="R30" s="49">
-        <f>AVERAGE(R4:R29)</f>
-        <v>0</v>
-      </c>
-      <c r="S30" s="49"/>
-      <c r="T30" s="50"/>
-      <c r="U30" s="49">
-        <f>AVERAGE(U4:U29)</f>
-        <v>0</v>
-      </c>
-      <c r="V30" s="49"/>
-      <c r="W30" s="50"/>
-      <c r="X30" s="49">
-        <f>AVERAGE(X4:X29)</f>
-        <v>0</v>
-      </c>
-      <c r="Y30" s="49"/>
-      <c r="Z30" s="50"/>
-      <c r="AA30" s="49">
-        <f>AVERAGE(AA4:AA29)</f>
-        <v>0</v>
-      </c>
-      <c r="AB30" s="49"/>
-      <c r="AC30" s="50"/>
-      <c r="AD30" s="49">
-        <f>AVERAGE(AD4:AD29)</f>
-        <v>0</v>
-      </c>
-      <c r="AE30" s="49"/>
-      <c r="AF30" s="50"/>
-      <c r="AG30" s="49">
-        <f>AVERAGE(AG4:AG29)</f>
-        <v>0</v>
-      </c>
-      <c r="AH30" s="49"/>
-      <c r="AI30" s="50"/>
-      <c r="AJ30" s="49">
-        <f>AVERAGE(AJ4:AJ29)</f>
-        <v>0</v>
-      </c>
-      <c r="AK30" s="49"/>
-      <c r="AL30" s="50"/>
-      <c r="AM30" s="49">
-        <f>AVERAGE(AM4:AM29)</f>
-        <v>0</v>
-      </c>
-      <c r="AN30" s="49"/>
-      <c r="AO30" s="50"/>
-      <c r="AP30" s="49">
-        <f>AVERAGE(AP4:AP29)</f>
-        <v>0</v>
-      </c>
-      <c r="AQ30" s="49"/>
-      <c r="AR30" s="50"/>
-    </row>
-    <row r="31" spans="1:44" s="6" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="B31" s="15"/>
-      <c r="C31" s="4"/>
-      <c r="D31" s="4"/>
-      <c r="E31" s="4"/>
-      <c r="F31" s="4"/>
-      <c r="G31" s="4"/>
-      <c r="H31" s="4"/>
-      <c r="I31" s="4"/>
-      <c r="J31" s="4"/>
-      <c r="K31" s="4"/>
-      <c r="L31" s="4"/>
-      <c r="M31" s="4"/>
-      <c r="N31" s="4"/>
-      <c r="O31" s="4"/>
-      <c r="P31" s="4"/>
-      <c r="Q31" s="4"/>
-      <c r="R31" s="4"/>
-      <c r="S31" s="4"/>
-      <c r="T31" s="4"/>
-      <c r="U31" s="4"/>
-      <c r="V31" s="4"/>
-      <c r="W31" s="4"/>
-      <c r="X31" s="4"/>
-      <c r="Y31" s="4"/>
-      <c r="Z31" s="4"/>
-      <c r="AA31" s="4"/>
-      <c r="AB31" s="4"/>
-      <c r="AC31" s="4"/>
-      <c r="AD31" s="4"/>
-      <c r="AE31" s="4"/>
-      <c r="AF31" s="4"/>
-      <c r="AG31" s="4"/>
-      <c r="AH31" s="4"/>
-      <c r="AI31" s="4"/>
-      <c r="AJ31" s="4"/>
-      <c r="AK31" s="4"/>
-      <c r="AL31" s="4"/>
-      <c r="AM31" s="4"/>
-      <c r="AN31" s="4"/>
-      <c r="AO31" s="4"/>
-      <c r="AP31" s="4"/>
-      <c r="AQ31" s="4"/>
-      <c r="AR31" s="4"/>
-    </row>
-    <row r="32" spans="1:44" s="6" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="B32" s="5"/>
-      <c r="C32" s="4"/>
-      <c r="D32" s="4"/>
-      <c r="E32" s="4"/>
-      <c r="F32" s="4"/>
-      <c r="G32" s="4"/>
-      <c r="H32" s="4"/>
-      <c r="I32" s="4"/>
-      <c r="J32" s="4"/>
-      <c r="K32" s="4"/>
-      <c r="L32" s="4"/>
-      <c r="M32" s="4"/>
-      <c r="N32" s="4"/>
-      <c r="O32" s="4"/>
-      <c r="P32" s="4"/>
-      <c r="Q32" s="4"/>
-      <c r="R32" s="4"/>
-      <c r="S32" s="4"/>
-      <c r="T32" s="4"/>
-      <c r="U32" s="4"/>
-      <c r="V32" s="4"/>
-      <c r="W32" s="4"/>
-      <c r="X32" s="4"/>
-      <c r="Y32" s="4"/>
-      <c r="Z32" s="4"/>
-      <c r="AA32" s="4"/>
-      <c r="AB32" s="4"/>
-      <c r="AC32" s="4"/>
-      <c r="AD32" s="4"/>
-      <c r="AE32" s="4"/>
-      <c r="AF32" s="4"/>
-      <c r="AG32" s="4"/>
-      <c r="AH32" s="4"/>
-      <c r="AI32" s="4"/>
-      <c r="AJ32" s="4"/>
-      <c r="AK32" s="4"/>
-      <c r="AL32" s="4"/>
-      <c r="AM32" s="4"/>
-      <c r="AN32" s="4"/>
-      <c r="AO32" s="4"/>
-      <c r="AP32" s="4"/>
-      <c r="AQ32" s="4"/>
-      <c r="AR32" s="4"/>
-    </row>
-    <row r="33" spans="2:44" s="6" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="B33" s="5"/>
-      <c r="C33" s="4"/>
-      <c r="D33" s="4"/>
-      <c r="E33" s="4"/>
-      <c r="F33" s="4"/>
-      <c r="G33" s="4"/>
-      <c r="H33" s="4"/>
-      <c r="I33" s="4"/>
-      <c r="J33" s="4"/>
-      <c r="K33" s="4"/>
-      <c r="L33" s="4"/>
-      <c r="M33" s="4"/>
-      <c r="N33" s="4"/>
-      <c r="O33" s="4"/>
-      <c r="P33" s="4"/>
-      <c r="Q33" s="4"/>
-      <c r="R33" s="4"/>
-      <c r="S33" s="4"/>
-      <c r="T33" s="4"/>
-      <c r="U33" s="4"/>
-      <c r="V33" s="4"/>
-      <c r="W33" s="4"/>
-      <c r="X33" s="4"/>
-      <c r="Y33" s="4"/>
-      <c r="Z33" s="4"/>
-      <c r="AA33" s="4"/>
-      <c r="AB33" s="4"/>
-      <c r="AC33" s="4"/>
-      <c r="AD33" s="4"/>
-      <c r="AE33" s="4"/>
-      <c r="AF33" s="4"/>
-      <c r="AG33" s="4"/>
-      <c r="AH33" s="4"/>
-      <c r="AI33" s="4"/>
-      <c r="AJ33" s="4"/>
-      <c r="AK33" s="4"/>
-      <c r="AL33" s="4"/>
-      <c r="AM33" s="4"/>
-      <c r="AN33" s="4"/>
-      <c r="AO33" s="4"/>
-      <c r="AP33" s="4"/>
-      <c r="AQ33" s="4"/>
-      <c r="AR33" s="4"/>
-    </row>
-    <row r="34" spans="2:44" s="6" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="B34" s="5"/>
-      <c r="C34" s="4"/>
-      <c r="D34" s="4"/>
-      <c r="E34" s="4"/>
-      <c r="F34" s="4"/>
-      <c r="G34" s="4"/>
-      <c r="H34" s="4"/>
-      <c r="I34" s="4"/>
-      <c r="J34" s="4"/>
-      <c r="K34" s="4"/>
-      <c r="L34" s="4"/>
-      <c r="M34" s="4"/>
-      <c r="N34" s="4"/>
-      <c r="O34" s="4"/>
-      <c r="P34" s="4"/>
-      <c r="Q34" s="4"/>
-      <c r="R34" s="4"/>
-      <c r="S34" s="4"/>
-      <c r="T34" s="4"/>
-      <c r="U34" s="4"/>
-      <c r="V34" s="4"/>
-      <c r="W34" s="4"/>
-      <c r="X34" s="4"/>
-      <c r="Y34" s="4"/>
-      <c r="Z34" s="4"/>
-      <c r="AA34" s="4"/>
-      <c r="AB34" s="4"/>
-      <c r="AC34" s="4"/>
-      <c r="AD34" s="4"/>
-      <c r="AE34" s="4"/>
-      <c r="AF34" s="4"/>
-      <c r="AG34" s="4"/>
-      <c r="AH34" s="4"/>
-      <c r="AI34" s="4"/>
-      <c r="AJ34" s="4"/>
-      <c r="AK34" s="4"/>
-      <c r="AL34" s="4"/>
-      <c r="AM34" s="4"/>
-      <c r="AN34" s="4"/>
-      <c r="AO34" s="4"/>
-      <c r="AP34" s="4"/>
-      <c r="AQ34" s="4"/>
-      <c r="AR34" s="4"/>
-    </row>
-    <row r="35" spans="2:44" s="6" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="B35" s="5"/>
-      <c r="C35" s="4"/>
-      <c r="D35" s="4"/>
-      <c r="E35" s="4"/>
-      <c r="F35" s="4"/>
-      <c r="G35" s="4"/>
-      <c r="H35" s="4"/>
-      <c r="I35" s="4"/>
-      <c r="J35" s="4"/>
-      <c r="K35" s="4"/>
-      <c r="L35" s="4"/>
-      <c r="M35" s="4"/>
-      <c r="N35" s="4"/>
-      <c r="O35" s="4"/>
-      <c r="P35" s="4"/>
-      <c r="Q35" s="4"/>
-      <c r="R35" s="4"/>
-      <c r="S35" s="4"/>
-      <c r="T35" s="4"/>
-      <c r="U35" s="4"/>
-      <c r="V35" s="4"/>
-      <c r="W35" s="4"/>
-      <c r="X35" s="4"/>
-      <c r="Y35" s="4"/>
-      <c r="Z35" s="4"/>
-      <c r="AA35" s="4"/>
-      <c r="AB35" s="4"/>
-      <c r="AC35" s="4"/>
-      <c r="AD35" s="4"/>
-      <c r="AE35" s="4"/>
-      <c r="AF35" s="4"/>
-      <c r="AG35" s="4"/>
-      <c r="AH35" s="4"/>
-      <c r="AI35" s="4"/>
-      <c r="AJ35" s="4"/>
-      <c r="AK35" s="4"/>
-      <c r="AL35" s="4"/>
-      <c r="AM35" s="4"/>
-      <c r="AN35" s="4"/>
-      <c r="AO35" s="4"/>
-      <c r="AP35" s="4"/>
-      <c r="AQ35" s="4"/>
-      <c r="AR35" s="4"/>
-    </row>
-    <row r="36" spans="2:44" s="6" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="B36" s="5"/>
-      <c r="C36" s="4"/>
-      <c r="D36" s="4"/>
-      <c r="E36" s="4"/>
-      <c r="F36" s="4"/>
-      <c r="G36" s="4"/>
-      <c r="H36" s="4"/>
-      <c r="I36" s="4"/>
-      <c r="J36" s="4"/>
-      <c r="K36" s="4"/>
-      <c r="L36" s="4"/>
-      <c r="M36" s="4"/>
-      <c r="N36" s="4"/>
-      <c r="O36" s="4"/>
-      <c r="P36" s="4"/>
-      <c r="Q36" s="4"/>
-      <c r="R36" s="4"/>
-      <c r="S36" s="4"/>
-      <c r="T36" s="4"/>
-      <c r="U36" s="4"/>
-      <c r="V36" s="4"/>
-      <c r="W36" s="4"/>
-      <c r="X36" s="4"/>
-      <c r="Y36" s="4"/>
-      <c r="Z36" s="4"/>
-      <c r="AA36" s="4"/>
-      <c r="AB36" s="4"/>
-      <c r="AC36" s="4"/>
-      <c r="AD36" s="4"/>
-      <c r="AE36" s="4"/>
-      <c r="AF36" s="4"/>
-      <c r="AG36" s="4"/>
-      <c r="AH36" s="4"/>
-      <c r="AI36" s="4"/>
-      <c r="AJ36" s="4"/>
-      <c r="AK36" s="4"/>
-      <c r="AL36" s="4"/>
-      <c r="AM36" s="4"/>
-      <c r="AN36" s="4"/>
-      <c r="AO36" s="4"/>
-      <c r="AP36" s="4"/>
-      <c r="AQ36" s="4"/>
-      <c r="AR36" s="4"/>
-    </row>
-    <row r="37" spans="2:44" s="6" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="B37" s="5"/>
+      <c r="C36" s="46">
+        <f>AVERAGE(C4:C35)</f>
+        <v>0</v>
+      </c>
+      <c r="D36" s="46"/>
+      <c r="E36" s="47"/>
+      <c r="F36" s="46">
+        <f>AVERAGE(F4:F35)</f>
+        <v>0</v>
+      </c>
+      <c r="G36" s="46"/>
+      <c r="H36" s="47"/>
+      <c r="I36" s="46">
+        <f>AVERAGE(I4:I35)</f>
+        <v>0</v>
+      </c>
+      <c r="J36" s="46"/>
+      <c r="K36" s="47"/>
+      <c r="L36" s="46">
+        <f>AVERAGE(L4:L35)</f>
+        <v>0</v>
+      </c>
+      <c r="M36" s="46"/>
+      <c r="N36" s="47"/>
+      <c r="O36" s="46">
+        <f>AVERAGE(O4:O35)</f>
+        <v>0</v>
+      </c>
+      <c r="P36" s="46"/>
+      <c r="Q36" s="47"/>
+      <c r="R36" s="46">
+        <f>AVERAGE(R4:R35)</f>
+        <v>0</v>
+      </c>
+      <c r="S36" s="46"/>
+      <c r="T36" s="47"/>
+      <c r="U36" s="46">
+        <f>AVERAGE(U4:U35)</f>
+        <v>0</v>
+      </c>
+      <c r="V36" s="46"/>
+      <c r="W36" s="47"/>
+      <c r="X36" s="46">
+        <f>AVERAGE(X4:X35)</f>
+        <v>0</v>
+      </c>
+      <c r="Y36" s="46"/>
+      <c r="Z36" s="47"/>
+      <c r="AA36" s="46">
+        <f>AVERAGE(AA4:AA35)</f>
+        <v>0</v>
+      </c>
+      <c r="AB36" s="46"/>
+      <c r="AC36" s="47"/>
+      <c r="AD36" s="46">
+        <f>AVERAGE(AD4:AD35)</f>
+        <v>0</v>
+      </c>
+      <c r="AE36" s="46"/>
+      <c r="AF36" s="47"/>
+      <c r="AG36" s="46">
+        <f>AVERAGE(AG4:AG35)</f>
+        <v>0</v>
+      </c>
+      <c r="AH36" s="46"/>
+      <c r="AI36" s="47"/>
+      <c r="AJ36" s="46">
+        <f>AVERAGE(AJ4:AJ35)</f>
+        <v>0</v>
+      </c>
+      <c r="AK36" s="46"/>
+      <c r="AL36" s="47"/>
+      <c r="AM36" s="46">
+        <f>AVERAGE(AM4:AM35)</f>
+        <v>0</v>
+      </c>
+      <c r="AN36" s="46"/>
+      <c r="AO36" s="47"/>
+      <c r="AP36" s="46">
+        <f>AVERAGE(AP4:AP35)</f>
+        <v>0</v>
+      </c>
+      <c r="AQ36" s="46"/>
+      <c r="AR36" s="47"/>
+    </row>
+    <row r="37" spans="1:44" s="6" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="B37" s="15"/>
       <c r="C37" s="4"/>
       <c r="D37" s="4"/>
       <c r="E37" s="4"/>
@@ -4436,7 +4451,7 @@
       <c r="AQ37" s="4"/>
       <c r="AR37" s="4"/>
     </row>
-    <row r="38" spans="2:44" s="6" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:44" s="6" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B38" s="5"/>
       <c r="C38" s="4"/>
       <c r="D38" s="4"/>
@@ -4481,7 +4496,7 @@
       <c r="AQ38" s="4"/>
       <c r="AR38" s="4"/>
     </row>
-    <row r="39" spans="2:44" s="6" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:44" s="6" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B39" s="5"/>
       <c r="C39" s="4"/>
       <c r="D39" s="4"/>
@@ -4526,7 +4541,7 @@
       <c r="AQ39" s="4"/>
       <c r="AR39" s="4"/>
     </row>
-    <row r="40" spans="2:44" s="6" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:44" s="6" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B40" s="5"/>
       <c r="C40" s="4"/>
       <c r="D40" s="4"/>
@@ -4571,7 +4586,7 @@
       <c r="AQ40" s="4"/>
       <c r="AR40" s="4"/>
     </row>
-    <row r="41" spans="2:44" s="6" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:44" s="6" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B41" s="5"/>
       <c r="C41" s="4"/>
       <c r="D41" s="4"/>
@@ -4616,7 +4631,7 @@
       <c r="AQ41" s="4"/>
       <c r="AR41" s="4"/>
     </row>
-    <row r="42" spans="2:44" s="6" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:44" s="6" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B42" s="5"/>
       <c r="C42" s="4"/>
       <c r="D42" s="4"/>
@@ -4661,7 +4676,7 @@
       <c r="AQ42" s="4"/>
       <c r="AR42" s="4"/>
     </row>
-    <row r="43" spans="2:44" s="6" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:44" s="6" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B43" s="5"/>
       <c r="C43" s="4"/>
       <c r="D43" s="4"/>
@@ -4706,7 +4721,7 @@
       <c r="AQ43" s="4"/>
       <c r="AR43" s="4"/>
     </row>
-    <row r="44" spans="2:44" s="6" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:44" s="6" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B44" s="5"/>
       <c r="C44" s="4"/>
       <c r="D44" s="4"/>
@@ -4751,7 +4766,7 @@
       <c r="AQ44" s="4"/>
       <c r="AR44" s="4"/>
     </row>
-    <row r="45" spans="2:44" s="6" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:44" s="6" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B45" s="5"/>
       <c r="C45" s="4"/>
       <c r="D45" s="4"/>
@@ -4796,7 +4811,7 @@
       <c r="AQ45" s="4"/>
       <c r="AR45" s="4"/>
     </row>
-    <row r="46" spans="2:44" s="6" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:44" s="6" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B46" s="5"/>
       <c r="C46" s="4"/>
       <c r="D46" s="4"/>
@@ -4841,7 +4856,7 @@
       <c r="AQ46" s="4"/>
       <c r="AR46" s="4"/>
     </row>
-    <row r="47" spans="2:44" s="6" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:44" s="6" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B47" s="5"/>
       <c r="C47" s="4"/>
       <c r="D47" s="4"/>
@@ -4886,7 +4901,7 @@
       <c r="AQ47" s="4"/>
       <c r="AR47" s="4"/>
     </row>
-    <row r="48" spans="2:44" s="6" customFormat="1" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:44" s="6" customFormat="1" x14ac:dyDescent="0.45">
       <c r="B48" s="5"/>
       <c r="C48" s="4"/>
       <c r="D48" s="4"/>
@@ -5741,27 +5756,284 @@
       <c r="AQ66" s="4"/>
       <c r="AR66" s="4"/>
     </row>
+    <row r="67" spans="2:44" s="6" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="B67" s="5"/>
+      <c r="C67" s="4"/>
+      <c r="D67" s="4"/>
+      <c r="E67" s="4"/>
+      <c r="F67" s="4"/>
+      <c r="G67" s="4"/>
+      <c r="H67" s="4"/>
+      <c r="I67" s="4"/>
+      <c r="J67" s="4"/>
+      <c r="K67" s="4"/>
+      <c r="L67" s="4"/>
+      <c r="M67" s="4"/>
+      <c r="N67" s="4"/>
+      <c r="O67" s="4"/>
+      <c r="P67" s="4"/>
+      <c r="Q67" s="4"/>
+      <c r="R67" s="4"/>
+      <c r="S67" s="4"/>
+      <c r="T67" s="4"/>
+      <c r="U67" s="4"/>
+      <c r="V67" s="4"/>
+      <c r="W67" s="4"/>
+      <c r="X67" s="4"/>
+      <c r="Y67" s="4"/>
+      <c r="Z67" s="4"/>
+      <c r="AA67" s="4"/>
+      <c r="AB67" s="4"/>
+      <c r="AC67" s="4"/>
+      <c r="AD67" s="4"/>
+      <c r="AE67" s="4"/>
+      <c r="AF67" s="4"/>
+      <c r="AG67" s="4"/>
+      <c r="AH67" s="4"/>
+      <c r="AI67" s="4"/>
+      <c r="AJ67" s="4"/>
+      <c r="AK67" s="4"/>
+      <c r="AL67" s="4"/>
+      <c r="AM67" s="4"/>
+      <c r="AN67" s="4"/>
+      <c r="AO67" s="4"/>
+      <c r="AP67" s="4"/>
+      <c r="AQ67" s="4"/>
+      <c r="AR67" s="4"/>
+    </row>
+    <row r="68" spans="2:44" s="6" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="B68" s="5"/>
+      <c r="C68" s="4"/>
+      <c r="D68" s="4"/>
+      <c r="E68" s="4"/>
+      <c r="F68" s="4"/>
+      <c r="G68" s="4"/>
+      <c r="H68" s="4"/>
+      <c r="I68" s="4"/>
+      <c r="J68" s="4"/>
+      <c r="K68" s="4"/>
+      <c r="L68" s="4"/>
+      <c r="M68" s="4"/>
+      <c r="N68" s="4"/>
+      <c r="O68" s="4"/>
+      <c r="P68" s="4"/>
+      <c r="Q68" s="4"/>
+      <c r="R68" s="4"/>
+      <c r="S68" s="4"/>
+      <c r="T68" s="4"/>
+      <c r="U68" s="4"/>
+      <c r="V68" s="4"/>
+      <c r="W68" s="4"/>
+      <c r="X68" s="4"/>
+      <c r="Y68" s="4"/>
+      <c r="Z68" s="4"/>
+      <c r="AA68" s="4"/>
+      <c r="AB68" s="4"/>
+      <c r="AC68" s="4"/>
+      <c r="AD68" s="4"/>
+      <c r="AE68" s="4"/>
+      <c r="AF68" s="4"/>
+      <c r="AG68" s="4"/>
+      <c r="AH68" s="4"/>
+      <c r="AI68" s="4"/>
+      <c r="AJ68" s="4"/>
+      <c r="AK68" s="4"/>
+      <c r="AL68" s="4"/>
+      <c r="AM68" s="4"/>
+      <c r="AN68" s="4"/>
+      <c r="AO68" s="4"/>
+      <c r="AP68" s="4"/>
+      <c r="AQ68" s="4"/>
+      <c r="AR68" s="4"/>
+    </row>
+    <row r="69" spans="2:44" s="6" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="B69" s="5"/>
+      <c r="C69" s="4"/>
+      <c r="D69" s="4"/>
+      <c r="E69" s="4"/>
+      <c r="F69" s="4"/>
+      <c r="G69" s="4"/>
+      <c r="H69" s="4"/>
+      <c r="I69" s="4"/>
+      <c r="J69" s="4"/>
+      <c r="K69" s="4"/>
+      <c r="L69" s="4"/>
+      <c r="M69" s="4"/>
+      <c r="N69" s="4"/>
+      <c r="O69" s="4"/>
+      <c r="P69" s="4"/>
+      <c r="Q69" s="4"/>
+      <c r="R69" s="4"/>
+      <c r="S69" s="4"/>
+      <c r="T69" s="4"/>
+      <c r="U69" s="4"/>
+      <c r="V69" s="4"/>
+      <c r="W69" s="4"/>
+      <c r="X69" s="4"/>
+      <c r="Y69" s="4"/>
+      <c r="Z69" s="4"/>
+      <c r="AA69" s="4"/>
+      <c r="AB69" s="4"/>
+      <c r="AC69" s="4"/>
+      <c r="AD69" s="4"/>
+      <c r="AE69" s="4"/>
+      <c r="AF69" s="4"/>
+      <c r="AG69" s="4"/>
+      <c r="AH69" s="4"/>
+      <c r="AI69" s="4"/>
+      <c r="AJ69" s="4"/>
+      <c r="AK69" s="4"/>
+      <c r="AL69" s="4"/>
+      <c r="AM69" s="4"/>
+      <c r="AN69" s="4"/>
+      <c r="AO69" s="4"/>
+      <c r="AP69" s="4"/>
+      <c r="AQ69" s="4"/>
+      <c r="AR69" s="4"/>
+    </row>
+    <row r="70" spans="2:44" s="6" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="B70" s="5"/>
+      <c r="C70" s="4"/>
+      <c r="D70" s="4"/>
+      <c r="E70" s="4"/>
+      <c r="F70" s="4"/>
+      <c r="G70" s="4"/>
+      <c r="H70" s="4"/>
+      <c r="I70" s="4"/>
+      <c r="J70" s="4"/>
+      <c r="K70" s="4"/>
+      <c r="L70" s="4"/>
+      <c r="M70" s="4"/>
+      <c r="N70" s="4"/>
+      <c r="O70" s="4"/>
+      <c r="P70" s="4"/>
+      <c r="Q70" s="4"/>
+      <c r="R70" s="4"/>
+      <c r="S70" s="4"/>
+      <c r="T70" s="4"/>
+      <c r="U70" s="4"/>
+      <c r="V70" s="4"/>
+      <c r="W70" s="4"/>
+      <c r="X70" s="4"/>
+      <c r="Y70" s="4"/>
+      <c r="Z70" s="4"/>
+      <c r="AA70" s="4"/>
+      <c r="AB70" s="4"/>
+      <c r="AC70" s="4"/>
+      <c r="AD70" s="4"/>
+      <c r="AE70" s="4"/>
+      <c r="AF70" s="4"/>
+      <c r="AG70" s="4"/>
+      <c r="AH70" s="4"/>
+      <c r="AI70" s="4"/>
+      <c r="AJ70" s="4"/>
+      <c r="AK70" s="4"/>
+      <c r="AL70" s="4"/>
+      <c r="AM70" s="4"/>
+      <c r="AN70" s="4"/>
+      <c r="AO70" s="4"/>
+      <c r="AP70" s="4"/>
+      <c r="AQ70" s="4"/>
+      <c r="AR70" s="4"/>
+    </row>
+    <row r="71" spans="2:44" s="6" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="B71" s="5"/>
+      <c r="C71" s="4"/>
+      <c r="D71" s="4"/>
+      <c r="E71" s="4"/>
+      <c r="F71" s="4"/>
+      <c r="G71" s="4"/>
+      <c r="H71" s="4"/>
+      <c r="I71" s="4"/>
+      <c r="J71" s="4"/>
+      <c r="K71" s="4"/>
+      <c r="L71" s="4"/>
+      <c r="M71" s="4"/>
+      <c r="N71" s="4"/>
+      <c r="O71" s="4"/>
+      <c r="P71" s="4"/>
+      <c r="Q71" s="4"/>
+      <c r="R71" s="4"/>
+      <c r="S71" s="4"/>
+      <c r="T71" s="4"/>
+      <c r="U71" s="4"/>
+      <c r="V71" s="4"/>
+      <c r="W71" s="4"/>
+      <c r="X71" s="4"/>
+      <c r="Y71" s="4"/>
+      <c r="Z71" s="4"/>
+      <c r="AA71" s="4"/>
+      <c r="AB71" s="4"/>
+      <c r="AC71" s="4"/>
+      <c r="AD71" s="4"/>
+      <c r="AE71" s="4"/>
+      <c r="AF71" s="4"/>
+      <c r="AG71" s="4"/>
+      <c r="AH71" s="4"/>
+      <c r="AI71" s="4"/>
+      <c r="AJ71" s="4"/>
+      <c r="AK71" s="4"/>
+      <c r="AL71" s="4"/>
+      <c r="AM71" s="4"/>
+      <c r="AN71" s="4"/>
+      <c r="AO71" s="4"/>
+      <c r="AP71" s="4"/>
+      <c r="AQ71" s="4"/>
+      <c r="AR71" s="4"/>
+    </row>
+    <row r="72" spans="2:44" s="6" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="B72" s="5"/>
+      <c r="C72" s="4"/>
+      <c r="D72" s="4"/>
+      <c r="E72" s="4"/>
+      <c r="F72" s="4"/>
+      <c r="G72" s="4"/>
+      <c r="H72" s="4"/>
+      <c r="I72" s="4"/>
+      <c r="J72" s="4"/>
+      <c r="K72" s="4"/>
+      <c r="L72" s="4"/>
+      <c r="M72" s="4"/>
+      <c r="N72" s="4"/>
+      <c r="O72" s="4"/>
+      <c r="P72" s="4"/>
+      <c r="Q72" s="4"/>
+      <c r="R72" s="4"/>
+      <c r="S72" s="4"/>
+      <c r="T72" s="4"/>
+      <c r="U72" s="4"/>
+      <c r="V72" s="4"/>
+      <c r="W72" s="4"/>
+      <c r="X72" s="4"/>
+      <c r="Y72" s="4"/>
+      <c r="Z72" s="4"/>
+      <c r="AA72" s="4"/>
+      <c r="AB72" s="4"/>
+      <c r="AC72" s="4"/>
+      <c r="AD72" s="4"/>
+      <c r="AE72" s="4"/>
+      <c r="AF72" s="4"/>
+      <c r="AG72" s="4"/>
+      <c r="AH72" s="4"/>
+      <c r="AI72" s="4"/>
+      <c r="AJ72" s="4"/>
+      <c r="AK72" s="4"/>
+      <c r="AL72" s="4"/>
+      <c r="AM72" s="4"/>
+      <c r="AN72" s="4"/>
+      <c r="AO72" s="4"/>
+      <c r="AP72" s="4"/>
+      <c r="AQ72" s="4"/>
+      <c r="AR72" s="4"/>
+    </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="R30:T30"/>
-    <mergeCell ref="U30:W30"/>
-    <mergeCell ref="AM30:AO30"/>
-    <mergeCell ref="X30:Z30"/>
-    <mergeCell ref="AA30:AC30"/>
-    <mergeCell ref="AD30:AF30"/>
-    <mergeCell ref="AG30:AI30"/>
-    <mergeCell ref="AJ30:AL30"/>
-    <mergeCell ref="L2:N2"/>
-    <mergeCell ref="I2:K2"/>
-    <mergeCell ref="I30:K30"/>
-    <mergeCell ref="L30:N30"/>
-    <mergeCell ref="O30:Q30"/>
     <mergeCell ref="B2:B3"/>
     <mergeCell ref="AP2:AR2"/>
-    <mergeCell ref="AP30:AR30"/>
+    <mergeCell ref="AP36:AR36"/>
     <mergeCell ref="C2:E2"/>
-    <mergeCell ref="C30:E30"/>
-    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="C36:E36"/>
+    <mergeCell ref="F36:H36"/>
     <mergeCell ref="AJ2:AL2"/>
     <mergeCell ref="AM2:AO2"/>
     <mergeCell ref="AG2:AI2"/>
@@ -5772,6 +6044,19 @@
     <mergeCell ref="F2:H2"/>
     <mergeCell ref="U2:W2"/>
     <mergeCell ref="R2:T2"/>
+    <mergeCell ref="L2:N2"/>
+    <mergeCell ref="I2:K2"/>
+    <mergeCell ref="I36:K36"/>
+    <mergeCell ref="L36:N36"/>
+    <mergeCell ref="O36:Q36"/>
+    <mergeCell ref="R36:T36"/>
+    <mergeCell ref="U36:W36"/>
+    <mergeCell ref="AM36:AO36"/>
+    <mergeCell ref="X36:Z36"/>
+    <mergeCell ref="AA36:AC36"/>
+    <mergeCell ref="AD36:AF36"/>
+    <mergeCell ref="AG36:AI36"/>
+    <mergeCell ref="AJ36:AL36"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
